--- a/datasets/dict/dict 코드북 260430.xlsx
+++ b/datasets/dict/dict 코드북 260430.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/Library/Mobile Documents/com~apple~CloudDocs/DeskTop/coding_main/HanTalk/규칙_및_예문_자동화/datasets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83A52688-7B82-ED42-84BB-2D0A36100229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F40B7E-0114-7146-9D49-3DED38CF4151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" xr2:uid="{F4A985C0-B43D-2244-AB7C-DBFAE8B9580A}"/>
   </bookViews>
@@ -4903,9 +4903,12 @@
   </si>
   <si>
     <t>정규식으로 작성함.</t>
-  </si>
-  <si>
-    <t>정규식으로 작성함.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a: 오탐제거가 필요 없는 문법항목
+b: 오탐제거가 필요하지만 다의의미 분별이 필요 없는 문법항목
+c: 오탐제거 및 다의의미 분별이 필요한 문법항목</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5733,6 +5736,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5772,77 +5778,74 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6301,7 +6304,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:50" ht="19">
+    <row r="5" spans="1:50" ht="84" customHeight="1">
       <c r="A5" s="9"/>
       <c r="B5" s="12" t="s">
         <v>1</v>
@@ -6316,12 +6319,12 @@
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:50" ht="40" customHeight="1">
-      <c r="A6" s="68"/>
-      <c r="B6" s="75" t="s">
+      <c r="A6" s="69"/>
+      <c r="B6" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="71" t="s">
-        <v>523</v>
+      <c r="C6" s="72" t="s">
+        <v>524</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>6</v>
@@ -6332,9 +6335,9 @@
       <c r="H6" s="9"/>
     </row>
     <row r="7" spans="1:50" ht="40" customHeight="1">
-      <c r="A7" s="69"/>
-      <c r="B7" s="76"/>
-      <c r="C7" s="72"/>
+      <c r="A7" s="70"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="73"/>
       <c r="D7" s="13" t="s">
         <v>5</v>
       </c>
@@ -6344,9 +6347,9 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:50" ht="40" customHeight="1">
-      <c r="A8" s="70"/>
-      <c r="B8" s="77"/>
-      <c r="C8" s="73"/>
+      <c r="A8" s="71"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="74"/>
       <c r="D8" s="13" t="s">
         <v>505</v>
       </c>
@@ -6505,10 +6508,10 @@
     </row>
     <row r="19" spans="1:8" ht="40" customHeight="1">
       <c r="A19" s="9"/>
-      <c r="B19" s="74" t="s">
+      <c r="B19" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="78" t="s">
+      <c r="C19" s="79" t="s">
         <v>485</v>
       </c>
       <c r="D19" s="13" t="s">
@@ -6521,8 +6524,8 @@
     </row>
     <row r="20" spans="1:8" ht="40" customHeight="1">
       <c r="A20" s="9"/>
-      <c r="B20" s="74"/>
-      <c r="C20" s="78"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="79"/>
       <c r="D20" s="13" t="s">
         <v>3</v>
       </c>
@@ -6684,7 +6687,7 @@
       <c r="B31" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="104" t="s">
+      <c r="C31" s="68" t="s">
         <v>521</v>
       </c>
       <c r="D31" s="13"/>
@@ -6699,7 +6702,7 @@
         <v>25</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="13" t="s">
@@ -8589,23 +8592,23 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="90" customHeight="1">
-      <c r="B16" s="79" t="s">
+      <c r="B16" s="80" t="s">
         <v>226</v>
       </c>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="79"/>
+      <c r="C16" s="80"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="80"/>
+      <c r="F16" s="80"/>
+      <c r="G16" s="80"/>
+      <c r="H16" s="80"/>
     </row>
     <row r="18" spans="2:5" ht="114" customHeight="1">
-      <c r="B18" s="80" t="s">
+      <c r="B18" s="81" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="80"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8646,10 +8649,10 @@
       <c r="B4" t="s">
         <v>163</v>
       </c>
-      <c r="F4" s="81" t="s">
+      <c r="F4" s="104" t="s">
         <v>186</v>
       </c>
-      <c r="G4" s="81"/>
+      <c r="G4" s="104"/>
       <c r="I4" s="57" t="s">
         <v>221</v>
       </c>
@@ -8676,10 +8679,10 @@
       <c r="I5" s="58"/>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="85" t="s">
+      <c r="B6" s="101" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="84" t="s">
+      <c r="C6" s="88" t="s">
         <v>51</v>
       </c>
       <c r="D6" s="44" t="s">
@@ -8697,8 +8700,8 @@
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="86"/>
-      <c r="C7" s="82"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="89"/>
       <c r="D7" s="13" t="s">
         <v>61</v>
       </c>
@@ -8714,8 +8717,8 @@
       </c>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="86"/>
-      <c r="C8" s="82"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="89"/>
       <c r="D8" s="13" t="s">
         <v>63</v>
       </c>
@@ -8731,7 +8734,7 @@
       </c>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="86"/>
+      <c r="B9" s="102"/>
       <c r="C9" s="13" t="s">
         <v>65</v>
       </c>
@@ -8750,7 +8753,7 @@
       </c>
     </row>
     <row r="10" spans="2:10" ht="19" thickBot="1">
-      <c r="B10" s="87"/>
+      <c r="B10" s="103"/>
       <c r="C10" s="48" t="s">
         <v>67</v>
       </c>
@@ -8769,7 +8772,7 @@
       </c>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="85" t="s">
+      <c r="B11" s="101" t="s">
         <v>52</v>
       </c>
       <c r="C11" s="44" t="s">
@@ -8785,7 +8788,7 @@
       <c r="G11" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="H11" s="94" t="s">
+      <c r="H11" s="90" t="s">
         <v>220</v>
       </c>
       <c r="I11" s="59" t="s">
@@ -8793,7 +8796,7 @@
       </c>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="86"/>
+      <c r="B12" s="102"/>
       <c r="C12" s="13" t="s">
         <v>71</v>
       </c>
@@ -8807,13 +8810,13 @@
       <c r="G12" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="H12" s="95"/>
+      <c r="H12" s="91"/>
       <c r="I12" s="60" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="19" thickBot="1">
-      <c r="B13" s="86"/>
+      <c r="B13" s="102"/>
       <c r="C13" s="13" t="s">
         <v>73</v>
       </c>
@@ -8827,15 +8830,15 @@
       <c r="G13" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="H13" s="96"/>
+      <c r="H13" s="92"/>
       <c r="I13" s="60" t="s">
         <v>74</v>
       </c>
       <c r="J13" s="5"/>
     </row>
     <row r="14" spans="2:10">
-      <c r="B14" s="86"/>
-      <c r="C14" s="82" t="s">
+      <c r="B14" s="102"/>
+      <c r="C14" s="89" t="s">
         <v>75</v>
       </c>
       <c r="D14" s="13" t="s">
@@ -8853,8 +8856,8 @@
       </c>
     </row>
     <row r="15" spans="2:10" ht="19" thickBot="1">
-      <c r="B15" s="87"/>
-      <c r="C15" s="83"/>
+      <c r="B15" s="103"/>
+      <c r="C15" s="100"/>
       <c r="D15" s="48" t="s">
         <v>78</v>
       </c>
@@ -8870,10 +8873,10 @@
       </c>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="85" t="s">
+      <c r="B16" s="101" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="84" t="s">
+      <c r="C16" s="88" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="44" t="s">
@@ -8882,43 +8885,43 @@
       <c r="E16" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="F16" s="84" t="s">
+      <c r="F16" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="102" t="s">
+      <c r="G16" s="98" t="s">
         <v>188</v>
       </c>
       <c r="I16" s="56"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="86"/>
-      <c r="C17" s="82"/>
+      <c r="B17" s="102"/>
+      <c r="C17" s="89"/>
       <c r="D17" s="13" t="s">
         <v>108</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="F17" s="82"/>
-      <c r="G17" s="103"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="99"/>
       <c r="I17" s="56"/>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="86"/>
-      <c r="C18" s="82"/>
+      <c r="B18" s="102"/>
+      <c r="C18" s="89"/>
       <c r="D18" s="13" t="s">
         <v>111</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="82"/>
-      <c r="G18" s="103"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="99"/>
       <c r="I18" s="56"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="86"/>
-      <c r="C19" s="82" t="s">
+      <c r="B19" s="102"/>
+      <c r="C19" s="89" t="s">
         <v>83</v>
       </c>
       <c r="D19" s="13" t="s">
@@ -8936,8 +8939,8 @@
       </c>
     </row>
     <row r="20" spans="2:9" ht="19" thickBot="1">
-      <c r="B20" s="87"/>
-      <c r="C20" s="83"/>
+      <c r="B20" s="103"/>
+      <c r="C20" s="100"/>
       <c r="D20" s="48" t="s">
         <v>86</v>
       </c>
@@ -8974,10 +8977,10 @@
       </c>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="85" t="s">
+      <c r="B22" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="84" t="s">
+      <c r="C22" s="88" t="s">
         <v>56</v>
       </c>
       <c r="D22" s="44" t="s">
@@ -8995,8 +8998,8 @@
       </c>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="86"/>
-      <c r="C23" s="82"/>
+      <c r="B23" s="102"/>
+      <c r="C23" s="89"/>
       <c r="D23" s="13" t="s">
         <v>93</v>
       </c>
@@ -9012,8 +9015,8 @@
       </c>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="86"/>
-      <c r="C24" s="82"/>
+      <c r="B24" s="102"/>
+      <c r="C24" s="89"/>
       <c r="D24" s="13" t="s">
         <v>95</v>
       </c>
@@ -9029,8 +9032,8 @@
       </c>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="86"/>
-      <c r="C25" s="82"/>
+      <c r="B25" s="102"/>
+      <c r="C25" s="89"/>
       <c r="D25" s="13" t="s">
         <v>97</v>
       </c>
@@ -9046,8 +9049,8 @@
       </c>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="86"/>
-      <c r="C26" s="82"/>
+      <c r="B26" s="102"/>
+      <c r="C26" s="89"/>
       <c r="D26" s="13" t="s">
         <v>109</v>
       </c>
@@ -9063,8 +9066,8 @@
       </c>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="86"/>
-      <c r="C27" s="82"/>
+      <c r="B27" s="102"/>
+      <c r="C27" s="89"/>
       <c r="D27" s="13" t="s">
         <v>112</v>
       </c>
@@ -9080,8 +9083,8 @@
       </c>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="86"/>
-      <c r="C28" s="82"/>
+      <c r="B28" s="102"/>
+      <c r="C28" s="89"/>
       <c r="D28" s="13" t="s">
         <v>101</v>
       </c>
@@ -9097,7 +9100,7 @@
       </c>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="86"/>
+      <c r="B29" s="102"/>
       <c r="C29" s="13" t="s">
         <v>103</v>
       </c>
@@ -9116,7 +9119,7 @@
       </c>
     </row>
     <row r="30" spans="2:9" ht="19" thickBot="1">
-      <c r="B30" s="87"/>
+      <c r="B30" s="103"/>
       <c r="C30" s="48" t="s">
         <v>105</v>
       </c>
@@ -9135,10 +9138,10 @@
       </c>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="85" t="s">
+      <c r="B31" s="101" t="s">
         <v>113</v>
       </c>
-      <c r="C31" s="84" t="s">
+      <c r="C31" s="88" t="s">
         <v>114</v>
       </c>
       <c r="D31" s="44" t="s">
@@ -9156,8 +9159,8 @@
       </c>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="86"/>
-      <c r="C32" s="82"/>
+      <c r="B32" s="102"/>
+      <c r="C32" s="89"/>
       <c r="D32" s="13" t="s">
         <v>117</v>
       </c>
@@ -9173,8 +9176,8 @@
       </c>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="86"/>
-      <c r="C33" s="82"/>
+      <c r="B33" s="102"/>
+      <c r="C33" s="89"/>
       <c r="D33" s="13" t="s">
         <v>119</v>
       </c>
@@ -9190,8 +9193,8 @@
       </c>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="86"/>
-      <c r="C34" s="82"/>
+      <c r="B34" s="102"/>
+      <c r="C34" s="89"/>
       <c r="D34" s="13" t="s">
         <v>121</v>
       </c>
@@ -9207,8 +9210,8 @@
       </c>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="86"/>
-      <c r="C35" s="82"/>
+      <c r="B35" s="102"/>
+      <c r="C35" s="89"/>
       <c r="D35" s="13" t="s">
         <v>123</v>
       </c>
@@ -9224,7 +9227,7 @@
       </c>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="86"/>
+      <c r="B36" s="102"/>
       <c r="C36" s="13" t="s">
         <v>125</v>
       </c>
@@ -9243,8 +9246,8 @@
       </c>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="86"/>
-      <c r="C37" s="82" t="s">
+      <c r="B37" s="102"/>
+      <c r="C37" s="89" t="s">
         <v>128</v>
       </c>
       <c r="D37" s="13" t="s">
@@ -9262,8 +9265,8 @@
       </c>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="86"/>
-      <c r="C38" s="82"/>
+      <c r="B38" s="102"/>
+      <c r="C38" s="89"/>
       <c r="D38" s="13" t="s">
         <v>130</v>
       </c>
@@ -9279,8 +9282,8 @@
       </c>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="86"/>
-      <c r="C39" s="82"/>
+      <c r="B39" s="102"/>
+      <c r="C39" s="89"/>
       <c r="D39" s="13" t="s">
         <v>132</v>
       </c>
@@ -9296,7 +9299,7 @@
       </c>
     </row>
     <row r="40" spans="2:9" ht="19">
-      <c r="B40" s="86"/>
+      <c r="B40" s="102"/>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
@@ -9311,7 +9314,7 @@
       </c>
     </row>
     <row r="41" spans="2:9" ht="19" thickBot="1">
-      <c r="B41" s="87"/>
+      <c r="B41" s="103"/>
       <c r="C41" s="48" t="s">
         <v>134</v>
       </c>
@@ -9330,10 +9333,10 @@
       </c>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="85" t="s">
+      <c r="B42" s="101" t="s">
         <v>136</v>
       </c>
-      <c r="C42" s="84" t="s">
+      <c r="C42" s="88" t="s">
         <v>137</v>
       </c>
       <c r="D42" s="44" t="s">
@@ -9351,8 +9354,8 @@
       </c>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="86"/>
-      <c r="C43" s="82"/>
+      <c r="B43" s="102"/>
+      <c r="C43" s="89"/>
       <c r="D43" s="13" t="s">
         <v>159</v>
       </c>
@@ -9368,8 +9371,8 @@
       </c>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="86"/>
-      <c r="C44" s="82"/>
+      <c r="B44" s="102"/>
+      <c r="C44" s="89"/>
       <c r="D44" s="13" t="s">
         <v>141</v>
       </c>
@@ -9380,13 +9383,13 @@
       <c r="G44" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="I44" s="97" t="s">
+      <c r="I44" s="93" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="19">
-      <c r="B45" s="86"/>
-      <c r="C45" s="82"/>
+      <c r="B45" s="102"/>
+      <c r="C45" s="89"/>
       <c r="D45" s="13"/>
       <c r="E45" s="13"/>
       <c r="F45" s="40" t="s">
@@ -9395,11 +9398,11 @@
       <c r="G45" s="51" t="s">
         <v>193</v>
       </c>
-      <c r="I45" s="98"/>
+      <c r="I45" s="94"/>
     </row>
     <row r="46" spans="2:9" ht="19">
-      <c r="B46" s="86"/>
-      <c r="C46" s="82"/>
+      <c r="B46" s="102"/>
+      <c r="C46" s="89"/>
       <c r="D46" s="13"/>
       <c r="E46" s="13"/>
       <c r="F46" s="40" t="s">
@@ -9408,11 +9411,11 @@
       <c r="G46" s="51" t="s">
         <v>194</v>
       </c>
-      <c r="I46" s="99"/>
+      <c r="I46" s="95"/>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="86"/>
-      <c r="C47" s="82"/>
+      <c r="B47" s="102"/>
+      <c r="C47" s="89"/>
       <c r="D47" s="13" t="s">
         <v>143</v>
       </c>
@@ -9428,8 +9431,8 @@
       </c>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="86"/>
-      <c r="C48" s="82"/>
+      <c r="B48" s="102"/>
+      <c r="C48" s="89"/>
       <c r="D48" s="35" t="s">
         <v>160</v>
       </c>
@@ -9445,8 +9448,8 @@
       </c>
     </row>
     <row r="49" spans="2:9">
-      <c r="B49" s="86"/>
-      <c r="C49" s="82"/>
+      <c r="B49" s="102"/>
+      <c r="C49" s="89"/>
       <c r="D49" s="13" t="s">
         <v>161</v>
       </c>
@@ -9462,7 +9465,7 @@
       </c>
     </row>
     <row r="50" spans="2:9">
-      <c r="B50" s="86"/>
+      <c r="B50" s="102"/>
       <c r="C50" s="13" t="s">
         <v>147</v>
       </c>
@@ -9481,7 +9484,7 @@
       </c>
     </row>
     <row r="51" spans="2:9">
-      <c r="B51" s="86"/>
+      <c r="B51" s="102"/>
       <c r="C51" s="13" t="s">
         <v>149</v>
       </c>
@@ -9500,7 +9503,7 @@
       </c>
     </row>
     <row r="52" spans="2:9" ht="19" thickBot="1">
-      <c r="B52" s="86"/>
+      <c r="B52" s="102"/>
       <c r="C52" s="13" t="s">
         <v>151</v>
       </c>
@@ -9519,7 +9522,7 @@
       </c>
     </row>
     <row r="53" spans="2:9" ht="57">
-      <c r="B53" s="86"/>
+      <c r="B53" s="102"/>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
       <c r="E53" s="13"/>
@@ -9529,12 +9532,12 @@
       <c r="G53" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="I53" s="100" t="s">
+      <c r="I53" s="96" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="54" spans="2:9" ht="19">
-      <c r="B54" s="86"/>
+      <c r="B54" s="102"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
       <c r="E54" s="13"/>
@@ -9544,10 +9547,10 @@
       <c r="G54" s="51" t="s">
         <v>199</v>
       </c>
-      <c r="I54" s="98"/>
+      <c r="I54" s="94"/>
     </row>
     <row r="55" spans="2:9" ht="19">
-      <c r="B55" s="86"/>
+      <c r="B55" s="102"/>
       <c r="C55" s="13"/>
       <c r="D55" s="13"/>
       <c r="E55" s="13"/>
@@ -9557,10 +9560,10 @@
       <c r="G55" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="I55" s="98"/>
+      <c r="I55" s="94"/>
     </row>
     <row r="56" spans="2:9" ht="19">
-      <c r="B56" s="86"/>
+      <c r="B56" s="102"/>
       <c r="C56" s="13"/>
       <c r="D56" s="13"/>
       <c r="E56" s="13"/>
@@ -9570,10 +9573,10 @@
       <c r="G56" s="51" t="s">
         <v>201</v>
       </c>
-      <c r="I56" s="98"/>
+      <c r="I56" s="94"/>
     </row>
     <row r="57" spans="2:9" ht="19">
-      <c r="B57" s="86"/>
+      <c r="B57" s="102"/>
       <c r="C57" s="13"/>
       <c r="D57" s="13"/>
       <c r="E57" s="13"/>
@@ -9583,10 +9586,10 @@
       <c r="G57" s="51" t="s">
         <v>202</v>
       </c>
-      <c r="I57" s="98"/>
+      <c r="I57" s="94"/>
     </row>
     <row r="58" spans="2:9" ht="38">
-      <c r="B58" s="86"/>
+      <c r="B58" s="102"/>
       <c r="C58" s="13"/>
       <c r="D58" s="13"/>
       <c r="E58" s="13"/>
@@ -9596,10 +9599,10 @@
       <c r="G58" s="51" t="s">
         <v>203</v>
       </c>
-      <c r="I58" s="98"/>
+      <c r="I58" s="94"/>
     </row>
     <row r="59" spans="2:9" ht="20" thickBot="1">
-      <c r="B59" s="86"/>
+      <c r="B59" s="102"/>
       <c r="C59" s="13"/>
       <c r="D59" s="13"/>
       <c r="E59" s="13"/>
@@ -9609,10 +9612,10 @@
       <c r="G59" s="51" t="s">
         <v>204</v>
       </c>
-      <c r="I59" s="101"/>
+      <c r="I59" s="97"/>
     </row>
     <row r="60" spans="2:9" ht="19">
-      <c r="B60" s="86"/>
+      <c r="B60" s="102"/>
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
       <c r="E60" s="13"/>
@@ -9622,12 +9625,12 @@
       <c r="G60" s="51" t="s">
         <v>205</v>
       </c>
-      <c r="I60" s="100" t="s">
+      <c r="I60" s="96" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="61" spans="2:9" ht="20" thickBot="1">
-      <c r="B61" s="86"/>
+      <c r="B61" s="102"/>
       <c r="C61" s="13"/>
       <c r="D61" s="13"/>
       <c r="E61" s="13"/>
@@ -9637,10 +9640,10 @@
       <c r="G61" s="51" t="s">
         <v>206</v>
       </c>
-      <c r="I61" s="98"/>
+      <c r="I61" s="94"/>
     </row>
     <row r="62" spans="2:9" ht="20" thickBot="1">
-      <c r="B62" s="86"/>
+      <c r="B62" s="102"/>
       <c r="C62" s="13"/>
       <c r="D62" s="13"/>
       <c r="E62" s="13"/>
@@ -9655,8 +9658,8 @@
       </c>
     </row>
     <row r="63" spans="2:9" ht="19" customHeight="1">
-      <c r="B63" s="86"/>
-      <c r="C63" s="82" t="s">
+      <c r="B63" s="102"/>
+      <c r="C63" s="89" t="s">
         <v>153</v>
       </c>
       <c r="D63" s="13" t="s">
@@ -9665,41 +9668,41 @@
       <c r="E63" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="F63" s="88" t="s">
+      <c r="F63" s="82" t="s">
         <v>198</v>
       </c>
-      <c r="G63" s="91" t="s">
+      <c r="G63" s="85" t="s">
         <v>197</v>
       </c>
-      <c r="I63" s="100" t="s">
+      <c r="I63" s="96" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="64" spans="2:9" ht="19" customHeight="1">
-      <c r="B64" s="86"/>
-      <c r="C64" s="82"/>
+      <c r="B64" s="102"/>
+      <c r="C64" s="89"/>
       <c r="D64" s="13" t="s">
         <v>155</v>
       </c>
       <c r="E64" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="F64" s="89"/>
-      <c r="G64" s="92"/>
-      <c r="I64" s="98"/>
+      <c r="F64" s="83"/>
+      <c r="G64" s="86"/>
+      <c r="I64" s="94"/>
     </row>
     <row r="65" spans="2:9" ht="19" customHeight="1" thickBot="1">
-      <c r="B65" s="87"/>
-      <c r="C65" s="83"/>
+      <c r="B65" s="103"/>
+      <c r="C65" s="100"/>
       <c r="D65" s="48" t="s">
         <v>162</v>
       </c>
       <c r="E65" s="48" t="s">
         <v>157</v>
       </c>
-      <c r="F65" s="90"/>
-      <c r="G65" s="93"/>
-      <c r="I65" s="101"/>
+      <c r="F65" s="84"/>
+      <c r="G65" s="87"/>
+      <c r="I65" s="97"/>
     </row>
     <row r="67" spans="2:9">
       <c r="E67" s="1" t="s">
@@ -9711,6 +9714,22 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C42:C49"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="B16:B20"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="B42:B65"/>
+    <mergeCell ref="C22:C28"/>
+    <mergeCell ref="B22:B30"/>
+    <mergeCell ref="B31:B41"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="C37:C39"/>
     <mergeCell ref="F63:F65"/>
     <mergeCell ref="G63:G65"/>
     <mergeCell ref="F16:F18"/>
@@ -9720,22 +9739,6 @@
     <mergeCell ref="I60:I61"/>
     <mergeCell ref="I63:I65"/>
     <mergeCell ref="G16:G18"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="B42:B65"/>
-    <mergeCell ref="C22:C28"/>
-    <mergeCell ref="B22:B30"/>
-    <mergeCell ref="B31:B41"/>
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C42:C49"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="B16:B20"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/dict/dict 코드북 260430.xlsx
+++ b/datasets/dict/dict 코드북 260430.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F40B7E-0114-7146-9D49-3DED38CF4151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA3D03A9-B271-0F47-90B4-CF61913C9485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" xr2:uid="{F4A985C0-B43D-2244-AB7C-DBFAE8B9580A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="528">
   <si>
     <t>e_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4909,6 +4909,18 @@
     <t>a: 오탐제거가 필요 없는 문법항목
 b: 오탐제거가 필요하지만 다의의미 분별이 필요 없는 문법항목
 c: 오탐제거 및 다의의미 분별이 필요한 문법항목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bridge_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문법요소 중 'ㄴ/은'에는 adnominal_n. 주의: 'ㄴ/은/는'은 안 됨.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5778,6 +5790,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5796,12 +5829,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5830,21 +5857,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6181,11 +6193,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E809B31-950A-8043-B762-4F555FA10734}">
-  <dimension ref="A1:AX63"/>
+  <dimension ref="A1:AX65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="6.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" style="5" customWidth="1"/>
     <col min="3" max="3" width="80.42578125" style="2" customWidth="1"/>
     <col min="4" max="4" width="6.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="9.85546875" style="1" customWidth="1"/>
@@ -6384,50 +6396,46 @@
       <c r="G10" s="38"/>
       <c r="H10" s="9"/>
     </row>
-    <row r="11" spans="1:50" ht="57">
+    <row r="11" spans="1:50" ht="67" customHeight="1">
       <c r="A11" s="9"/>
-      <c r="B11" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>43</v>
-      </c>
+      <c r="B11" s="37" t="s">
+        <v>525</v>
+      </c>
+      <c r="C11" s="9"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
-      <c r="F11" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="10"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="38"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:50" ht="108" customHeight="1">
+    <row r="12" spans="1:50" ht="57">
       <c r="A12" s="9"/>
       <c r="B12" s="12" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>483</v>
+        <v>43</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="11" t="s">
-        <v>183</v>
+        <v>24</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:50" ht="19">
+    <row r="13" spans="1:50" ht="108" customHeight="1">
       <c r="A13" s="9"/>
       <c r="B13" s="12" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>507</v>
+        <v>483</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="9"/>
@@ -6435,15 +6443,15 @@
     <row r="14" spans="1:50" ht="19">
       <c r="A14" s="9"/>
       <c r="B14" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="11" t="s">
-        <v>47</v>
+        <v>184</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="9"/>
@@ -6451,24 +6459,26 @@
     <row r="15" spans="1:50" ht="19">
       <c r="A15" s="9"/>
       <c r="B15" s="12" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
-      <c r="F15" s="11"/>
+      <c r="F15" s="11" t="s">
+        <v>47</v>
+      </c>
       <c r="G15" s="10"/>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="1:50" ht="40" customHeight="1">
+    <row r="16" spans="1:50" ht="19">
       <c r="A16" s="9"/>
-      <c r="B16" s="66" t="s">
-        <v>510</v>
+      <c r="B16" s="12" t="s">
+        <v>10</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
@@ -6476,13 +6486,13 @@
       <c r="G16" s="10"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" ht="40" customHeight="1">
       <c r="A17" s="9"/>
-      <c r="B17" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" s="34" t="s">
-        <v>484</v>
+      <c r="B17" s="66" t="s">
+        <v>510</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>511</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
@@ -6490,163 +6500,163 @@
       <c r="G17" s="10"/>
       <c r="H17" s="9"/>
     </row>
-    <row r="18" spans="1:8" ht="19">
+    <row r="18" spans="1:8">
       <c r="A18" s="9"/>
       <c r="B18" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>512</v>
+        <v>0</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>484</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
-      <c r="F18" s="11" t="s">
-        <v>27</v>
-      </c>
+      <c r="F18" s="11"/>
       <c r="G18" s="10"/>
       <c r="H18" s="9"/>
     </row>
-    <row r="19" spans="1:8" ht="40" customHeight="1">
+    <row r="19" spans="1:8" ht="19">
       <c r="A19" s="9"/>
-      <c r="B19" s="75" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="79" t="s">
-        <v>485</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>2</v>
-      </c>
+      <c r="B19" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="D19" s="13"/>
       <c r="E19" s="13"/>
-      <c r="F19" s="11"/>
+      <c r="F19" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="G19" s="10"/>
       <c r="H19" s="9"/>
     </row>
-    <row r="20" spans="1:8" ht="40" customHeight="1">
+    <row r="20" spans="1:8" ht="19">
       <c r="A20" s="9"/>
-      <c r="B20" s="75"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="13" t="s">
-        <v>3</v>
-      </c>
+      <c r="B20" s="14" t="s">
+        <v>526</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="D20" s="13"/>
       <c r="E20" s="13"/>
       <c r="F20" s="11"/>
       <c r="G20" s="10"/>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="1:8" ht="178" customHeight="1">
+    <row r="21" spans="1:8" ht="40" customHeight="1">
       <c r="A21" s="9"/>
-      <c r="B21" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="D21" s="13"/>
+      <c r="B21" s="75" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="79" t="s">
+        <v>485</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>2</v>
+      </c>
       <c r="E21" s="13"/>
       <c r="F21" s="11"/>
       <c r="G21" s="10"/>
-      <c r="H21" s="9" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="38">
+      <c r="H21" s="9"/>
+    </row>
+    <row r="22" spans="1:8" ht="40" customHeight="1">
       <c r="A22" s="9"/>
-      <c r="B22" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>486</v>
-      </c>
-      <c r="D22" s="13"/>
+      <c r="B22" s="75"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="13" t="s">
+        <v>3</v>
+      </c>
       <c r="E22" s="13"/>
       <c r="F22" s="11"/>
       <c r="G22" s="10"/>
       <c r="H22" s="9"/>
     </row>
-    <row r="23" spans="1:8" ht="76">
+    <row r="23" spans="1:8" ht="178" customHeight="1">
       <c r="A23" s="9"/>
       <c r="B23" s="15" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
-      <c r="F23" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="F23" s="11"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8" ht="199" customHeight="1">
+      <c r="H23" s="9" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="38">
       <c r="A24" s="9"/>
       <c r="B24" s="15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>522</v>
+        <v>486</v>
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
-      <c r="F24" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="F24" s="11"/>
       <c r="G24" s="10"/>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="1:8" ht="60" customHeight="1">
+    <row r="25" spans="1:8" ht="76">
       <c r="A25" s="9"/>
       <c r="B25" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>49</v>
+        <v>515</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
       <c r="F25" s="11" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="9"/>
     </row>
-    <row r="26" spans="1:8" ht="145" customHeight="1">
+    <row r="26" spans="1:8" ht="199" customHeight="1">
       <c r="A26" s="9"/>
-      <c r="B26" s="65" t="s">
-        <v>516</v>
+      <c r="B26" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
-      <c r="F26" s="11"/>
+      <c r="F26" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="G26" s="10"/>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" ht="60" customHeight="1">
       <c r="A27" s="9"/>
-      <c r="B27" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" s="34" t="s">
-        <v>484</v>
+      <c r="B27" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
-      <c r="F27" s="11"/>
+      <c r="F27" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="G27" s="10"/>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" ht="145" customHeight="1">
       <c r="A28" s="9"/>
-      <c r="B28" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="34" t="s">
-        <v>517</v>
+      <c r="B28" s="65" t="s">
+        <v>516</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>519</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
@@ -6657,10 +6667,10 @@
     <row r="29" spans="1:8">
       <c r="A29" s="9"/>
       <c r="B29" s="17" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>518</v>
+        <v>484</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
@@ -6668,13 +6678,13 @@
       <c r="G29" s="10"/>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8" ht="183" customHeight="1">
+    <row r="30" spans="1:8">
       <c r="A30" s="9"/>
       <c r="B30" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" s="64" t="s">
-        <v>520</v>
+        <v>41</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>517</v>
       </c>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
@@ -6682,13 +6692,13 @@
       <c r="G30" s="10"/>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8" ht="117" customHeight="1">
+    <row r="31" spans="1:8">
       <c r="A31" s="9"/>
       <c r="B31" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="68" t="s">
-        <v>521</v>
+        <v>26</v>
+      </c>
+      <c r="C31" s="34" t="s">
+        <v>518</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
@@ -6696,49 +6706,45 @@
       <c r="G31" s="10"/>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8" ht="108" customHeight="1">
+    <row r="32" spans="1:8" ht="183" customHeight="1">
       <c r="A32" s="9"/>
       <c r="B32" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>523</v>
+        <v>29</v>
+      </c>
+      <c r="C32" s="64" t="s">
+        <v>520</v>
       </c>
       <c r="D32" s="13"/>
-      <c r="E32" s="13" t="s">
-        <v>30</v>
-      </c>
+      <c r="E32" s="13"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
       <c r="H32" s="9"/>
     </row>
-    <row r="33" spans="1:8" ht="19">
+    <row r="33" spans="1:8" ht="117" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>182</v>
+        <v>31</v>
+      </c>
+      <c r="C33" s="68" t="s">
+        <v>521</v>
       </c>
       <c r="D33" s="13"/>
-      <c r="E33" s="13" t="s">
-        <v>33</v>
-      </c>
+      <c r="E33" s="13"/>
       <c r="F33" s="11"/>
       <c r="G33" s="10"/>
       <c r="H33" s="9"/>
     </row>
-    <row r="34" spans="1:8" ht="19">
+    <row r="34" spans="1:8" ht="108" customHeight="1">
       <c r="A34" s="9"/>
       <c r="B34" s="17" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>36</v>
+        <v>523</v>
       </c>
       <c r="D34" s="13"/>
       <c r="E34" s="13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -6747,34 +6753,47 @@
     <row r="35" spans="1:8" ht="19">
       <c r="A35" s="9"/>
       <c r="B35" s="17" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>38</v>
+        <v>182</v>
       </c>
       <c r="D35" s="13"/>
       <c r="E35" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
       <c r="H35" s="9"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" ht="19">
       <c r="A36" s="9"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="9"/>
+      <c r="B36" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
+      <c r="E36" s="13" t="s">
+        <v>35</v>
+      </c>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
       <c r="H36" s="9"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" ht="19">
       <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
+      <c r="B37" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>38</v>
+      </c>
       <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
+      <c r="E37" s="13" t="s">
+        <v>30</v>
+      </c>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
       <c r="H37" s="9"/>
@@ -6791,8 +6810,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="9"/>
-      <c r="B39" s="16"/>
-      <c r="C39" s="9"/>
+      <c r="B39" s="9"/>
       <c r="D39" s="13"/>
       <c r="E39" s="13"/>
       <c r="F39" s="11"/>
@@ -7039,13 +7057,33 @@
       <c r="G63" s="10"/>
       <c r="H63" s="9"/>
     </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="9"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="10"/>
+      <c r="H64" s="9"/>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="9"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="10"/>
+      <c r="H65" s="9"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="C6:C8"/>
-    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B21:B22"/>
     <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="C21:C22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8649,10 +8687,10 @@
       <c r="B4" t="s">
         <v>163</v>
       </c>
-      <c r="F4" s="104" t="s">
+      <c r="F4" s="82" t="s">
         <v>186</v>
       </c>
-      <c r="G4" s="104"/>
+      <c r="G4" s="82"/>
       <c r="I4" s="57" t="s">
         <v>221</v>
       </c>
@@ -8679,10 +8717,10 @@
       <c r="I5" s="58"/>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="101" t="s">
+      <c r="B6" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="88" t="s">
+      <c r="C6" s="85" t="s">
         <v>51</v>
       </c>
       <c r="D6" s="44" t="s">
@@ -8700,8 +8738,8 @@
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="102"/>
-      <c r="C7" s="89"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="83"/>
       <c r="D7" s="13" t="s">
         <v>61</v>
       </c>
@@ -8717,8 +8755,8 @@
       </c>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="102"/>
-      <c r="C8" s="89"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="83"/>
       <c r="D8" s="13" t="s">
         <v>63</v>
       </c>
@@ -8734,7 +8772,7 @@
       </c>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="102"/>
+      <c r="B9" s="87"/>
       <c r="C9" s="13" t="s">
         <v>65</v>
       </c>
@@ -8753,7 +8791,7 @@
       </c>
     </row>
     <row r="10" spans="2:10" ht="19" thickBot="1">
-      <c r="B10" s="103"/>
+      <c r="B10" s="88"/>
       <c r="C10" s="48" t="s">
         <v>67</v>
       </c>
@@ -8772,7 +8810,7 @@
       </c>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="101" t="s">
+      <c r="B11" s="86" t="s">
         <v>52</v>
       </c>
       <c r="C11" s="44" t="s">
@@ -8788,7 +8826,7 @@
       <c r="G11" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="H11" s="90" t="s">
+      <c r="H11" s="95" t="s">
         <v>220</v>
       </c>
       <c r="I11" s="59" t="s">
@@ -8796,7 +8834,7 @@
       </c>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="102"/>
+      <c r="B12" s="87"/>
       <c r="C12" s="13" t="s">
         <v>71</v>
       </c>
@@ -8810,13 +8848,13 @@
       <c r="G12" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="H12" s="91"/>
+      <c r="H12" s="96"/>
       <c r="I12" s="60" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="19" thickBot="1">
-      <c r="B13" s="102"/>
+      <c r="B13" s="87"/>
       <c r="C13" s="13" t="s">
         <v>73</v>
       </c>
@@ -8830,15 +8868,15 @@
       <c r="G13" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="H13" s="92"/>
+      <c r="H13" s="97"/>
       <c r="I13" s="60" t="s">
         <v>74</v>
       </c>
       <c r="J13" s="5"/>
     </row>
     <row r="14" spans="2:10">
-      <c r="B14" s="102"/>
-      <c r="C14" s="89" t="s">
+      <c r="B14" s="87"/>
+      <c r="C14" s="83" t="s">
         <v>75</v>
       </c>
       <c r="D14" s="13" t="s">
@@ -8856,8 +8894,8 @@
       </c>
     </row>
     <row r="15" spans="2:10" ht="19" thickBot="1">
-      <c r="B15" s="103"/>
-      <c r="C15" s="100"/>
+      <c r="B15" s="88"/>
+      <c r="C15" s="84"/>
       <c r="D15" s="48" t="s">
         <v>78</v>
       </c>
@@ -8873,10 +8911,10 @@
       </c>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="101" t="s">
+      <c r="B16" s="86" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="88" t="s">
+      <c r="C16" s="85" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="44" t="s">
@@ -8885,43 +8923,43 @@
       <c r="E16" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="F16" s="88" t="s">
+      <c r="F16" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="98" t="s">
+      <c r="G16" s="103" t="s">
         <v>188</v>
       </c>
       <c r="I16" s="56"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="102"/>
-      <c r="C17" s="89"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="83"/>
       <c r="D17" s="13" t="s">
         <v>108</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="F17" s="89"/>
-      <c r="G17" s="99"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="104"/>
       <c r="I17" s="56"/>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="102"/>
-      <c r="C18" s="89"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="83"/>
       <c r="D18" s="13" t="s">
         <v>111</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="89"/>
-      <c r="G18" s="99"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="104"/>
       <c r="I18" s="56"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="102"/>
-      <c r="C19" s="89" t="s">
+      <c r="B19" s="87"/>
+      <c r="C19" s="83" t="s">
         <v>83</v>
       </c>
       <c r="D19" s="13" t="s">
@@ -8939,8 +8977,8 @@
       </c>
     </row>
     <row r="20" spans="2:9" ht="19" thickBot="1">
-      <c r="B20" s="103"/>
-      <c r="C20" s="100"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="84"/>
       <c r="D20" s="48" t="s">
         <v>86</v>
       </c>
@@ -8977,10 +9015,10 @@
       </c>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="101" t="s">
+      <c r="B22" s="86" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="88" t="s">
+      <c r="C22" s="85" t="s">
         <v>56</v>
       </c>
       <c r="D22" s="44" t="s">
@@ -8998,8 +9036,8 @@
       </c>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="102"/>
-      <c r="C23" s="89"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="83"/>
       <c r="D23" s="13" t="s">
         <v>93</v>
       </c>
@@ -9015,8 +9053,8 @@
       </c>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="102"/>
-      <c r="C24" s="89"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="83"/>
       <c r="D24" s="13" t="s">
         <v>95</v>
       </c>
@@ -9032,8 +9070,8 @@
       </c>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="102"/>
-      <c r="C25" s="89"/>
+      <c r="B25" s="87"/>
+      <c r="C25" s="83"/>
       <c r="D25" s="13" t="s">
         <v>97</v>
       </c>
@@ -9049,8 +9087,8 @@
       </c>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="102"/>
-      <c r="C26" s="89"/>
+      <c r="B26" s="87"/>
+      <c r="C26" s="83"/>
       <c r="D26" s="13" t="s">
         <v>109</v>
       </c>
@@ -9066,8 +9104,8 @@
       </c>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="102"/>
-      <c r="C27" s="89"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="83"/>
       <c r="D27" s="13" t="s">
         <v>112</v>
       </c>
@@ -9083,8 +9121,8 @@
       </c>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="102"/>
-      <c r="C28" s="89"/>
+      <c r="B28" s="87"/>
+      <c r="C28" s="83"/>
       <c r="D28" s="13" t="s">
         <v>101</v>
       </c>
@@ -9100,7 +9138,7 @@
       </c>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="102"/>
+      <c r="B29" s="87"/>
       <c r="C29" s="13" t="s">
         <v>103</v>
       </c>
@@ -9119,7 +9157,7 @@
       </c>
     </row>
     <row r="30" spans="2:9" ht="19" thickBot="1">
-      <c r="B30" s="103"/>
+      <c r="B30" s="88"/>
       <c r="C30" s="48" t="s">
         <v>105</v>
       </c>
@@ -9138,10 +9176,10 @@
       </c>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="101" t="s">
+      <c r="B31" s="86" t="s">
         <v>113</v>
       </c>
-      <c r="C31" s="88" t="s">
+      <c r="C31" s="85" t="s">
         <v>114</v>
       </c>
       <c r="D31" s="44" t="s">
@@ -9159,8 +9197,8 @@
       </c>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="102"/>
-      <c r="C32" s="89"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="83"/>
       <c r="D32" s="13" t="s">
         <v>117</v>
       </c>
@@ -9176,8 +9214,8 @@
       </c>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="102"/>
-      <c r="C33" s="89"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="83"/>
       <c r="D33" s="13" t="s">
         <v>119</v>
       </c>
@@ -9193,8 +9231,8 @@
       </c>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="102"/>
-      <c r="C34" s="89"/>
+      <c r="B34" s="87"/>
+      <c r="C34" s="83"/>
       <c r="D34" s="13" t="s">
         <v>121</v>
       </c>
@@ -9210,8 +9248,8 @@
       </c>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="102"/>
-      <c r="C35" s="89"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="83"/>
       <c r="D35" s="13" t="s">
         <v>123</v>
       </c>
@@ -9227,7 +9265,7 @@
       </c>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="102"/>
+      <c r="B36" s="87"/>
       <c r="C36" s="13" t="s">
         <v>125</v>
       </c>
@@ -9246,8 +9284,8 @@
       </c>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="102"/>
-      <c r="C37" s="89" t="s">
+      <c r="B37" s="87"/>
+      <c r="C37" s="83" t="s">
         <v>128</v>
       </c>
       <c r="D37" s="13" t="s">
@@ -9265,8 +9303,8 @@
       </c>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="102"/>
-      <c r="C38" s="89"/>
+      <c r="B38" s="87"/>
+      <c r="C38" s="83"/>
       <c r="D38" s="13" t="s">
         <v>130</v>
       </c>
@@ -9282,8 +9320,8 @@
       </c>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="102"/>
-      <c r="C39" s="89"/>
+      <c r="B39" s="87"/>
+      <c r="C39" s="83"/>
       <c r="D39" s="13" t="s">
         <v>132</v>
       </c>
@@ -9299,7 +9337,7 @@
       </c>
     </row>
     <row r="40" spans="2:9" ht="19">
-      <c r="B40" s="102"/>
+      <c r="B40" s="87"/>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
@@ -9314,7 +9352,7 @@
       </c>
     </row>
     <row r="41" spans="2:9" ht="19" thickBot="1">
-      <c r="B41" s="103"/>
+      <c r="B41" s="88"/>
       <c r="C41" s="48" t="s">
         <v>134</v>
       </c>
@@ -9333,10 +9371,10 @@
       </c>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="101" t="s">
+      <c r="B42" s="86" t="s">
         <v>136</v>
       </c>
-      <c r="C42" s="88" t="s">
+      <c r="C42" s="85" t="s">
         <v>137</v>
       </c>
       <c r="D42" s="44" t="s">
@@ -9354,8 +9392,8 @@
       </c>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="102"/>
-      <c r="C43" s="89"/>
+      <c r="B43" s="87"/>
+      <c r="C43" s="83"/>
       <c r="D43" s="13" t="s">
         <v>159</v>
       </c>
@@ -9371,8 +9409,8 @@
       </c>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="102"/>
-      <c r="C44" s="89"/>
+      <c r="B44" s="87"/>
+      <c r="C44" s="83"/>
       <c r="D44" s="13" t="s">
         <v>141</v>
       </c>
@@ -9383,13 +9421,13 @@
       <c r="G44" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="I44" s="93" t="s">
+      <c r="I44" s="98" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="19">
-      <c r="B45" s="102"/>
-      <c r="C45" s="89"/>
+      <c r="B45" s="87"/>
+      <c r="C45" s="83"/>
       <c r="D45" s="13"/>
       <c r="E45" s="13"/>
       <c r="F45" s="40" t="s">
@@ -9398,11 +9436,11 @@
       <c r="G45" s="51" t="s">
         <v>193</v>
       </c>
-      <c r="I45" s="94"/>
+      <c r="I45" s="99"/>
     </row>
     <row r="46" spans="2:9" ht="19">
-      <c r="B46" s="102"/>
-      <c r="C46" s="89"/>
+      <c r="B46" s="87"/>
+      <c r="C46" s="83"/>
       <c r="D46" s="13"/>
       <c r="E46" s="13"/>
       <c r="F46" s="40" t="s">
@@ -9411,11 +9449,11 @@
       <c r="G46" s="51" t="s">
         <v>194</v>
       </c>
-      <c r="I46" s="95"/>
+      <c r="I46" s="100"/>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="102"/>
-      <c r="C47" s="89"/>
+      <c r="B47" s="87"/>
+      <c r="C47" s="83"/>
       <c r="D47" s="13" t="s">
         <v>143</v>
       </c>
@@ -9431,8 +9469,8 @@
       </c>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="102"/>
-      <c r="C48" s="89"/>
+      <c r="B48" s="87"/>
+      <c r="C48" s="83"/>
       <c r="D48" s="35" t="s">
         <v>160</v>
       </c>
@@ -9448,8 +9486,8 @@
       </c>
     </row>
     <row r="49" spans="2:9">
-      <c r="B49" s="102"/>
-      <c r="C49" s="89"/>
+      <c r="B49" s="87"/>
+      <c r="C49" s="83"/>
       <c r="D49" s="13" t="s">
         <v>161</v>
       </c>
@@ -9465,7 +9503,7 @@
       </c>
     </row>
     <row r="50" spans="2:9">
-      <c r="B50" s="102"/>
+      <c r="B50" s="87"/>
       <c r="C50" s="13" t="s">
         <v>147</v>
       </c>
@@ -9484,7 +9522,7 @@
       </c>
     </row>
     <row r="51" spans="2:9">
-      <c r="B51" s="102"/>
+      <c r="B51" s="87"/>
       <c r="C51" s="13" t="s">
         <v>149</v>
       </c>
@@ -9503,7 +9541,7 @@
       </c>
     </row>
     <row r="52" spans="2:9" ht="19" thickBot="1">
-      <c r="B52" s="102"/>
+      <c r="B52" s="87"/>
       <c r="C52" s="13" t="s">
         <v>151</v>
       </c>
@@ -9522,7 +9560,7 @@
       </c>
     </row>
     <row r="53" spans="2:9" ht="57">
-      <c r="B53" s="102"/>
+      <c r="B53" s="87"/>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
       <c r="E53" s="13"/>
@@ -9532,12 +9570,12 @@
       <c r="G53" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="I53" s="96" t="s">
+      <c r="I53" s="101" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="54" spans="2:9" ht="19">
-      <c r="B54" s="102"/>
+      <c r="B54" s="87"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
       <c r="E54" s="13"/>
@@ -9547,10 +9585,10 @@
       <c r="G54" s="51" t="s">
         <v>199</v>
       </c>
-      <c r="I54" s="94"/>
+      <c r="I54" s="99"/>
     </row>
     <row r="55" spans="2:9" ht="19">
-      <c r="B55" s="102"/>
+      <c r="B55" s="87"/>
       <c r="C55" s="13"/>
       <c r="D55" s="13"/>
       <c r="E55" s="13"/>
@@ -9560,10 +9598,10 @@
       <c r="G55" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="I55" s="94"/>
+      <c r="I55" s="99"/>
     </row>
     <row r="56" spans="2:9" ht="19">
-      <c r="B56" s="102"/>
+      <c r="B56" s="87"/>
       <c r="C56" s="13"/>
       <c r="D56" s="13"/>
       <c r="E56" s="13"/>
@@ -9573,10 +9611,10 @@
       <c r="G56" s="51" t="s">
         <v>201</v>
       </c>
-      <c r="I56" s="94"/>
+      <c r="I56" s="99"/>
     </row>
     <row r="57" spans="2:9" ht="19">
-      <c r="B57" s="102"/>
+      <c r="B57" s="87"/>
       <c r="C57" s="13"/>
       <c r="D57" s="13"/>
       <c r="E57" s="13"/>
@@ -9586,10 +9624,10 @@
       <c r="G57" s="51" t="s">
         <v>202</v>
       </c>
-      <c r="I57" s="94"/>
+      <c r="I57" s="99"/>
     </row>
     <row r="58" spans="2:9" ht="38">
-      <c r="B58" s="102"/>
+      <c r="B58" s="87"/>
       <c r="C58" s="13"/>
       <c r="D58" s="13"/>
       <c r="E58" s="13"/>
@@ -9599,10 +9637,10 @@
       <c r="G58" s="51" t="s">
         <v>203</v>
       </c>
-      <c r="I58" s="94"/>
+      <c r="I58" s="99"/>
     </row>
     <row r="59" spans="2:9" ht="20" thickBot="1">
-      <c r="B59" s="102"/>
+      <c r="B59" s="87"/>
       <c r="C59" s="13"/>
       <c r="D59" s="13"/>
       <c r="E59" s="13"/>
@@ -9612,10 +9650,10 @@
       <c r="G59" s="51" t="s">
         <v>204</v>
       </c>
-      <c r="I59" s="97"/>
+      <c r="I59" s="102"/>
     </row>
     <row r="60" spans="2:9" ht="19">
-      <c r="B60" s="102"/>
+      <c r="B60" s="87"/>
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
       <c r="E60" s="13"/>
@@ -9625,12 +9663,12 @@
       <c r="G60" s="51" t="s">
         <v>205</v>
       </c>
-      <c r="I60" s="96" t="s">
+      <c r="I60" s="101" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="61" spans="2:9" ht="20" thickBot="1">
-      <c r="B61" s="102"/>
+      <c r="B61" s="87"/>
       <c r="C61" s="13"/>
       <c r="D61" s="13"/>
       <c r="E61" s="13"/>
@@ -9640,10 +9678,10 @@
       <c r="G61" s="51" t="s">
         <v>206</v>
       </c>
-      <c r="I61" s="94"/>
+      <c r="I61" s="99"/>
     </row>
     <row r="62" spans="2:9" ht="20" thickBot="1">
-      <c r="B62" s="102"/>
+      <c r="B62" s="87"/>
       <c r="C62" s="13"/>
       <c r="D62" s="13"/>
       <c r="E62" s="13"/>
@@ -9658,8 +9696,8 @@
       </c>
     </row>
     <row r="63" spans="2:9" ht="19" customHeight="1">
-      <c r="B63" s="102"/>
-      <c r="C63" s="89" t="s">
+      <c r="B63" s="87"/>
+      <c r="C63" s="83" t="s">
         <v>153</v>
       </c>
       <c r="D63" s="13" t="s">
@@ -9668,41 +9706,41 @@
       <c r="E63" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="F63" s="82" t="s">
+      <c r="F63" s="89" t="s">
         <v>198</v>
       </c>
-      <c r="G63" s="85" t="s">
+      <c r="G63" s="92" t="s">
         <v>197</v>
       </c>
-      <c r="I63" s="96" t="s">
+      <c r="I63" s="101" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="64" spans="2:9" ht="19" customHeight="1">
-      <c r="B64" s="102"/>
-      <c r="C64" s="89"/>
+      <c r="B64" s="87"/>
+      <c r="C64" s="83"/>
       <c r="D64" s="13" t="s">
         <v>155</v>
       </c>
       <c r="E64" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="F64" s="83"/>
-      <c r="G64" s="86"/>
-      <c r="I64" s="94"/>
+      <c r="F64" s="90"/>
+      <c r="G64" s="93"/>
+      <c r="I64" s="99"/>
     </row>
     <row r="65" spans="2:9" ht="19" customHeight="1" thickBot="1">
-      <c r="B65" s="103"/>
-      <c r="C65" s="100"/>
+      <c r="B65" s="88"/>
+      <c r="C65" s="84"/>
       <c r="D65" s="48" t="s">
         <v>162</v>
       </c>
       <c r="E65" s="48" t="s">
         <v>157</v>
       </c>
-      <c r="F65" s="84"/>
-      <c r="G65" s="87"/>
-      <c r="I65" s="97"/>
+      <c r="F65" s="91"/>
+      <c r="G65" s="94"/>
+      <c r="I65" s="102"/>
     </row>
     <row r="67" spans="2:9">
       <c r="E67" s="1" t="s">
@@ -9714,6 +9752,22 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="F63:F65"/>
+    <mergeCell ref="G63:G65"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="I44:I46"/>
+    <mergeCell ref="I53:I59"/>
+    <mergeCell ref="I60:I61"/>
+    <mergeCell ref="I63:I65"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="B42:B65"/>
+    <mergeCell ref="C22:C28"/>
+    <mergeCell ref="B22:B30"/>
+    <mergeCell ref="B31:B41"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="C37:C39"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="C42:C49"/>
@@ -9723,22 +9777,6 @@
     <mergeCell ref="C16:C18"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="B16:B20"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="B42:B65"/>
-    <mergeCell ref="C22:C28"/>
-    <mergeCell ref="B22:B30"/>
-    <mergeCell ref="B31:B41"/>
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="F63:F65"/>
-    <mergeCell ref="G63:G65"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="I44:I46"/>
-    <mergeCell ref="I53:I59"/>
-    <mergeCell ref="I60:I61"/>
-    <mergeCell ref="I63:I65"/>
-    <mergeCell ref="G16:G18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/dict/dict 코드북 260430.xlsx
+++ b/datasets/dict/dict 코드북 260430.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA3D03A9-B271-0F47-90B4-CF61913C9485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233DA852-2893-4F46-8CF0-2DAC778D5D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" xr2:uid="{F4A985C0-B43D-2244-AB7C-DBFAE8B9580A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="530">
   <si>
     <t>e_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4887,12 +4887,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>stage'가 'detect'인 경우 'target'은 항상 'raw_sentence'여야 함.
-'stage'가 'verify'인 경우 'target'은 'raw_sentence' 혹은 'token_window'가능함.
-'token_window'는 문법 항목 스팬의 앞 뒤 10char 안으로 설정되어 있음. 즉, 이 범위 안에서 verify 정규식 조건을 찾아서 hard fail시킴.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>인접한 성분 간 gap 허용치의 최소값. 해당 성분과 다음 성분 사이 gap.
 참고로 우리 코딩에는 'min_gap_to_next', 'max_gap_to_next' 외에도 문법항목 구성 요소를 찾는 범위가 하나 더 있음. 아래와 같음.
 1. detect 정규식 match 발생
@@ -4921,6 +4915,22 @@
   </si>
   <si>
     <t>문법요소 중 'ㄴ/은'에는 adnominal_n. 주의: 'ㄴ/은/는'은 안 됨.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>component_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">target'의 'component_right_context' 범주에 사용되는 열 항목. 
+'target'열 항목이 'component_right_context'일 경우 'component_id'의 오른쪽 char 조건을 'pattern'에 기록한다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage'가 'detect'인 경우 'target'은 항상 'raw_sentence'여야 함.
+'stage'가 'verify'인 경우 'target'은 'raw_sentence' 혹은 'token_window'가능함.
+token_window: 문법 항목 스팬의 앞 뒤 10char 안으로 설정되어 있음. 즉, 이 범위 안에서 verify 정규식 조건을 찾아서 hard fail시킴.
+component_right_context: 'component_id'열의 component 오른쪽 char에 대한 조건을 'pattern'열 항목에 기록한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5790,18 +5800,63 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5811,52 +5866,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6336,7 +6346,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="72" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>6</v>
@@ -6399,7 +6409,7 @@
     <row r="11" spans="1:50" ht="67" customHeight="1">
       <c r="A11" s="9"/>
       <c r="B11" s="37" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="13"/>
@@ -6533,10 +6543,10 @@
     <row r="20" spans="1:8" ht="19">
       <c r="A20" s="9"/>
       <c r="B20" s="14" t="s">
+        <v>525</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>526</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>527</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
@@ -6624,7 +6634,7 @@
         <v>19</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
@@ -6720,13 +6730,13 @@
       <c r="G32" s="10"/>
       <c r="H32" s="9"/>
     </row>
-    <row r="33" spans="1:8" ht="117" customHeight="1">
+    <row r="33" spans="1:8" ht="162" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="17" t="s">
         <v>31</v>
       </c>
       <c r="C33" s="68" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
@@ -6734,33 +6744,31 @@
       <c r="G33" s="10"/>
       <c r="H33" s="9"/>
     </row>
-    <row r="34" spans="1:8" ht="108" customHeight="1">
+    <row r="34" spans="1:8" ht="57">
       <c r="A34" s="9"/>
       <c r="B34" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>523</v>
+        <v>527</v>
+      </c>
+      <c r="C34" s="68" t="s">
+        <v>528</v>
       </c>
       <c r="D34" s="13"/>
-      <c r="E34" s="13" t="s">
-        <v>30</v>
-      </c>
+      <c r="E34" s="13"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
       <c r="H34" s="9"/>
     </row>
-    <row r="35" spans="1:8" ht="19">
+    <row r="35" spans="1:8" ht="108" customHeight="1">
       <c r="A35" s="9"/>
       <c r="B35" s="17" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>182</v>
+        <v>522</v>
       </c>
       <c r="D35" s="13"/>
       <c r="E35" s="13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -6769,14 +6777,14 @@
     <row r="36" spans="1:8" ht="19">
       <c r="A36" s="9"/>
       <c r="B36" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>36</v>
+        <v>182</v>
       </c>
       <c r="D36" s="13"/>
       <c r="E36" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -6785,25 +6793,31 @@
     <row r="37" spans="1:8" ht="19">
       <c r="A37" s="9"/>
       <c r="B37" s="17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D37" s="13"/>
       <c r="E37" s="13" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
       <c r="H37" s="9"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" ht="19">
       <c r="A38" s="9"/>
-      <c r="B38" s="16"/>
-      <c r="C38" s="9"/>
+      <c r="B38" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>38</v>
+      </c>
       <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
+      <c r="E38" s="13" t="s">
+        <v>30</v>
+      </c>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
       <c r="H38" s="9"/>
@@ -8687,10 +8701,10 @@
       <c r="B4" t="s">
         <v>163</v>
       </c>
-      <c r="F4" s="82" t="s">
+      <c r="F4" s="104" t="s">
         <v>186</v>
       </c>
-      <c r="G4" s="82"/>
+      <c r="G4" s="104"/>
       <c r="I4" s="57" t="s">
         <v>221</v>
       </c>
@@ -8717,10 +8731,10 @@
       <c r="I5" s="58"/>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="101" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="85" t="s">
+      <c r="C6" s="88" t="s">
         <v>51</v>
       </c>
       <c r="D6" s="44" t="s">
@@ -8738,8 +8752,8 @@
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="87"/>
-      <c r="C7" s="83"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="89"/>
       <c r="D7" s="13" t="s">
         <v>61</v>
       </c>
@@ -8755,8 +8769,8 @@
       </c>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="87"/>
-      <c r="C8" s="83"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="89"/>
       <c r="D8" s="13" t="s">
         <v>63</v>
       </c>
@@ -8772,7 +8786,7 @@
       </c>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="87"/>
+      <c r="B9" s="102"/>
       <c r="C9" s="13" t="s">
         <v>65</v>
       </c>
@@ -8791,7 +8805,7 @@
       </c>
     </row>
     <row r="10" spans="2:10" ht="19" thickBot="1">
-      <c r="B10" s="88"/>
+      <c r="B10" s="103"/>
       <c r="C10" s="48" t="s">
         <v>67</v>
       </c>
@@ -8810,7 +8824,7 @@
       </c>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="86" t="s">
+      <c r="B11" s="101" t="s">
         <v>52</v>
       </c>
       <c r="C11" s="44" t="s">
@@ -8826,7 +8840,7 @@
       <c r="G11" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="H11" s="95" t="s">
+      <c r="H11" s="90" t="s">
         <v>220</v>
       </c>
       <c r="I11" s="59" t="s">
@@ -8834,7 +8848,7 @@
       </c>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="87"/>
+      <c r="B12" s="102"/>
       <c r="C12" s="13" t="s">
         <v>71</v>
       </c>
@@ -8848,13 +8862,13 @@
       <c r="G12" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="H12" s="96"/>
+      <c r="H12" s="91"/>
       <c r="I12" s="60" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="19" thickBot="1">
-      <c r="B13" s="87"/>
+      <c r="B13" s="102"/>
       <c r="C13" s="13" t="s">
         <v>73</v>
       </c>
@@ -8868,15 +8882,15 @@
       <c r="G13" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="H13" s="97"/>
+      <c r="H13" s="92"/>
       <c r="I13" s="60" t="s">
         <v>74</v>
       </c>
       <c r="J13" s="5"/>
     </row>
     <row r="14" spans="2:10">
-      <c r="B14" s="87"/>
-      <c r="C14" s="83" t="s">
+      <c r="B14" s="102"/>
+      <c r="C14" s="89" t="s">
         <v>75</v>
       </c>
       <c r="D14" s="13" t="s">
@@ -8894,8 +8908,8 @@
       </c>
     </row>
     <row r="15" spans="2:10" ht="19" thickBot="1">
-      <c r="B15" s="88"/>
-      <c r="C15" s="84"/>
+      <c r="B15" s="103"/>
+      <c r="C15" s="100"/>
       <c r="D15" s="48" t="s">
         <v>78</v>
       </c>
@@ -8911,10 +8925,10 @@
       </c>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="86" t="s">
+      <c r="B16" s="101" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="85" t="s">
+      <c r="C16" s="88" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="44" t="s">
@@ -8923,43 +8937,43 @@
       <c r="E16" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="F16" s="85" t="s">
+      <c r="F16" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="103" t="s">
+      <c r="G16" s="98" t="s">
         <v>188</v>
       </c>
       <c r="I16" s="56"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="87"/>
-      <c r="C17" s="83"/>
+      <c r="B17" s="102"/>
+      <c r="C17" s="89"/>
       <c r="D17" s="13" t="s">
         <v>108</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="F17" s="83"/>
-      <c r="G17" s="104"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="99"/>
       <c r="I17" s="56"/>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="87"/>
-      <c r="C18" s="83"/>
+      <c r="B18" s="102"/>
+      <c r="C18" s="89"/>
       <c r="D18" s="13" t="s">
         <v>111</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="83"/>
-      <c r="G18" s="104"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="99"/>
       <c r="I18" s="56"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="87"/>
-      <c r="C19" s="83" t="s">
+      <c r="B19" s="102"/>
+      <c r="C19" s="89" t="s">
         <v>83</v>
       </c>
       <c r="D19" s="13" t="s">
@@ -8977,8 +8991,8 @@
       </c>
     </row>
     <row r="20" spans="2:9" ht="19" thickBot="1">
-      <c r="B20" s="88"/>
-      <c r="C20" s="84"/>
+      <c r="B20" s="103"/>
+      <c r="C20" s="100"/>
       <c r="D20" s="48" t="s">
         <v>86</v>
       </c>
@@ -9015,10 +9029,10 @@
       </c>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="86" t="s">
+      <c r="B22" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="85" t="s">
+      <c r="C22" s="88" t="s">
         <v>56</v>
       </c>
       <c r="D22" s="44" t="s">
@@ -9036,8 +9050,8 @@
       </c>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="87"/>
-      <c r="C23" s="83"/>
+      <c r="B23" s="102"/>
+      <c r="C23" s="89"/>
       <c r="D23" s="13" t="s">
         <v>93</v>
       </c>
@@ -9053,8 +9067,8 @@
       </c>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="87"/>
-      <c r="C24" s="83"/>
+      <c r="B24" s="102"/>
+      <c r="C24" s="89"/>
       <c r="D24" s="13" t="s">
         <v>95</v>
       </c>
@@ -9070,8 +9084,8 @@
       </c>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="87"/>
-      <c r="C25" s="83"/>
+      <c r="B25" s="102"/>
+      <c r="C25" s="89"/>
       <c r="D25" s="13" t="s">
         <v>97</v>
       </c>
@@ -9087,8 +9101,8 @@
       </c>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="87"/>
-      <c r="C26" s="83"/>
+      <c r="B26" s="102"/>
+      <c r="C26" s="89"/>
       <c r="D26" s="13" t="s">
         <v>109</v>
       </c>
@@ -9104,8 +9118,8 @@
       </c>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="87"/>
-      <c r="C27" s="83"/>
+      <c r="B27" s="102"/>
+      <c r="C27" s="89"/>
       <c r="D27" s="13" t="s">
         <v>112</v>
       </c>
@@ -9121,8 +9135,8 @@
       </c>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="87"/>
-      <c r="C28" s="83"/>
+      <c r="B28" s="102"/>
+      <c r="C28" s="89"/>
       <c r="D28" s="13" t="s">
         <v>101</v>
       </c>
@@ -9138,7 +9152,7 @@
       </c>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="87"/>
+      <c r="B29" s="102"/>
       <c r="C29" s="13" t="s">
         <v>103</v>
       </c>
@@ -9157,7 +9171,7 @@
       </c>
     </row>
     <row r="30" spans="2:9" ht="19" thickBot="1">
-      <c r="B30" s="88"/>
+      <c r="B30" s="103"/>
       <c r="C30" s="48" t="s">
         <v>105</v>
       </c>
@@ -9176,10 +9190,10 @@
       </c>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="86" t="s">
+      <c r="B31" s="101" t="s">
         <v>113</v>
       </c>
-      <c r="C31" s="85" t="s">
+      <c r="C31" s="88" t="s">
         <v>114</v>
       </c>
       <c r="D31" s="44" t="s">
@@ -9197,8 +9211,8 @@
       </c>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="87"/>
-      <c r="C32" s="83"/>
+      <c r="B32" s="102"/>
+      <c r="C32" s="89"/>
       <c r="D32" s="13" t="s">
         <v>117</v>
       </c>
@@ -9214,8 +9228,8 @@
       </c>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="87"/>
-      <c r="C33" s="83"/>
+      <c r="B33" s="102"/>
+      <c r="C33" s="89"/>
       <c r="D33" s="13" t="s">
         <v>119</v>
       </c>
@@ -9231,8 +9245,8 @@
       </c>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="87"/>
-      <c r="C34" s="83"/>
+      <c r="B34" s="102"/>
+      <c r="C34" s="89"/>
       <c r="D34" s="13" t="s">
         <v>121</v>
       </c>
@@ -9248,8 +9262,8 @@
       </c>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="87"/>
-      <c r="C35" s="83"/>
+      <c r="B35" s="102"/>
+      <c r="C35" s="89"/>
       <c r="D35" s="13" t="s">
         <v>123</v>
       </c>
@@ -9265,7 +9279,7 @@
       </c>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="87"/>
+      <c r="B36" s="102"/>
       <c r="C36" s="13" t="s">
         <v>125</v>
       </c>
@@ -9284,8 +9298,8 @@
       </c>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="87"/>
-      <c r="C37" s="83" t="s">
+      <c r="B37" s="102"/>
+      <c r="C37" s="89" t="s">
         <v>128</v>
       </c>
       <c r="D37" s="13" t="s">
@@ -9303,8 +9317,8 @@
       </c>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="87"/>
-      <c r="C38" s="83"/>
+      <c r="B38" s="102"/>
+      <c r="C38" s="89"/>
       <c r="D38" s="13" t="s">
         <v>130</v>
       </c>
@@ -9320,8 +9334,8 @@
       </c>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="87"/>
-      <c r="C39" s="83"/>
+      <c r="B39" s="102"/>
+      <c r="C39" s="89"/>
       <c r="D39" s="13" t="s">
         <v>132</v>
       </c>
@@ -9337,7 +9351,7 @@
       </c>
     </row>
     <row r="40" spans="2:9" ht="19">
-      <c r="B40" s="87"/>
+      <c r="B40" s="102"/>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
@@ -9352,7 +9366,7 @@
       </c>
     </row>
     <row r="41" spans="2:9" ht="19" thickBot="1">
-      <c r="B41" s="88"/>
+      <c r="B41" s="103"/>
       <c r="C41" s="48" t="s">
         <v>134</v>
       </c>
@@ -9371,10 +9385,10 @@
       </c>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="86" t="s">
+      <c r="B42" s="101" t="s">
         <v>136</v>
       </c>
-      <c r="C42" s="85" t="s">
+      <c r="C42" s="88" t="s">
         <v>137</v>
       </c>
       <c r="D42" s="44" t="s">
@@ -9392,8 +9406,8 @@
       </c>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="87"/>
-      <c r="C43" s="83"/>
+      <c r="B43" s="102"/>
+      <c r="C43" s="89"/>
       <c r="D43" s="13" t="s">
         <v>159</v>
       </c>
@@ -9409,8 +9423,8 @@
       </c>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="87"/>
-      <c r="C44" s="83"/>
+      <c r="B44" s="102"/>
+      <c r="C44" s="89"/>
       <c r="D44" s="13" t="s">
         <v>141</v>
       </c>
@@ -9421,13 +9435,13 @@
       <c r="G44" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="I44" s="98" t="s">
+      <c r="I44" s="93" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="19">
-      <c r="B45" s="87"/>
-      <c r="C45" s="83"/>
+      <c r="B45" s="102"/>
+      <c r="C45" s="89"/>
       <c r="D45" s="13"/>
       <c r="E45" s="13"/>
       <c r="F45" s="40" t="s">
@@ -9436,11 +9450,11 @@
       <c r="G45" s="51" t="s">
         <v>193</v>
       </c>
-      <c r="I45" s="99"/>
+      <c r="I45" s="94"/>
     </row>
     <row r="46" spans="2:9" ht="19">
-      <c r="B46" s="87"/>
-      <c r="C46" s="83"/>
+      <c r="B46" s="102"/>
+      <c r="C46" s="89"/>
       <c r="D46" s="13"/>
       <c r="E46" s="13"/>
       <c r="F46" s="40" t="s">
@@ -9449,11 +9463,11 @@
       <c r="G46" s="51" t="s">
         <v>194</v>
       </c>
-      <c r="I46" s="100"/>
+      <c r="I46" s="95"/>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="87"/>
-      <c r="C47" s="83"/>
+      <c r="B47" s="102"/>
+      <c r="C47" s="89"/>
       <c r="D47" s="13" t="s">
         <v>143</v>
       </c>
@@ -9469,8 +9483,8 @@
       </c>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="87"/>
-      <c r="C48" s="83"/>
+      <c r="B48" s="102"/>
+      <c r="C48" s="89"/>
       <c r="D48" s="35" t="s">
         <v>160</v>
       </c>
@@ -9486,8 +9500,8 @@
       </c>
     </row>
     <row r="49" spans="2:9">
-      <c r="B49" s="87"/>
-      <c r="C49" s="83"/>
+      <c r="B49" s="102"/>
+      <c r="C49" s="89"/>
       <c r="D49" s="13" t="s">
         <v>161</v>
       </c>
@@ -9503,7 +9517,7 @@
       </c>
     </row>
     <row r="50" spans="2:9">
-      <c r="B50" s="87"/>
+      <c r="B50" s="102"/>
       <c r="C50" s="13" t="s">
         <v>147</v>
       </c>
@@ -9522,7 +9536,7 @@
       </c>
     </row>
     <row r="51" spans="2:9">
-      <c r="B51" s="87"/>
+      <c r="B51" s="102"/>
       <c r="C51" s="13" t="s">
         <v>149</v>
       </c>
@@ -9541,7 +9555,7 @@
       </c>
     </row>
     <row r="52" spans="2:9" ht="19" thickBot="1">
-      <c r="B52" s="87"/>
+      <c r="B52" s="102"/>
       <c r="C52" s="13" t="s">
         <v>151</v>
       </c>
@@ -9560,7 +9574,7 @@
       </c>
     </row>
     <row r="53" spans="2:9" ht="57">
-      <c r="B53" s="87"/>
+      <c r="B53" s="102"/>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
       <c r="E53" s="13"/>
@@ -9570,12 +9584,12 @@
       <c r="G53" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="I53" s="101" t="s">
+      <c r="I53" s="96" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="54" spans="2:9" ht="19">
-      <c r="B54" s="87"/>
+      <c r="B54" s="102"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
       <c r="E54" s="13"/>
@@ -9585,10 +9599,10 @@
       <c r="G54" s="51" t="s">
         <v>199</v>
       </c>
-      <c r="I54" s="99"/>
+      <c r="I54" s="94"/>
     </row>
     <row r="55" spans="2:9" ht="19">
-      <c r="B55" s="87"/>
+      <c r="B55" s="102"/>
       <c r="C55" s="13"/>
       <c r="D55" s="13"/>
       <c r="E55" s="13"/>
@@ -9598,10 +9612,10 @@
       <c r="G55" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="I55" s="99"/>
+      <c r="I55" s="94"/>
     </row>
     <row r="56" spans="2:9" ht="19">
-      <c r="B56" s="87"/>
+      <c r="B56" s="102"/>
       <c r="C56" s="13"/>
       <c r="D56" s="13"/>
       <c r="E56" s="13"/>
@@ -9611,10 +9625,10 @@
       <c r="G56" s="51" t="s">
         <v>201</v>
       </c>
-      <c r="I56" s="99"/>
+      <c r="I56" s="94"/>
     </row>
     <row r="57" spans="2:9" ht="19">
-      <c r="B57" s="87"/>
+      <c r="B57" s="102"/>
       <c r="C57" s="13"/>
       <c r="D57" s="13"/>
       <c r="E57" s="13"/>
@@ -9624,10 +9638,10 @@
       <c r="G57" s="51" t="s">
         <v>202</v>
       </c>
-      <c r="I57" s="99"/>
+      <c r="I57" s="94"/>
     </row>
     <row r="58" spans="2:9" ht="38">
-      <c r="B58" s="87"/>
+      <c r="B58" s="102"/>
       <c r="C58" s="13"/>
       <c r="D58" s="13"/>
       <c r="E58" s="13"/>
@@ -9637,10 +9651,10 @@
       <c r="G58" s="51" t="s">
         <v>203</v>
       </c>
-      <c r="I58" s="99"/>
+      <c r="I58" s="94"/>
     </row>
     <row r="59" spans="2:9" ht="20" thickBot="1">
-      <c r="B59" s="87"/>
+      <c r="B59" s="102"/>
       <c r="C59" s="13"/>
       <c r="D59" s="13"/>
       <c r="E59" s="13"/>
@@ -9650,10 +9664,10 @@
       <c r="G59" s="51" t="s">
         <v>204</v>
       </c>
-      <c r="I59" s="102"/>
+      <c r="I59" s="97"/>
     </row>
     <row r="60" spans="2:9" ht="19">
-      <c r="B60" s="87"/>
+      <c r="B60" s="102"/>
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
       <c r="E60" s="13"/>
@@ -9663,12 +9677,12 @@
       <c r="G60" s="51" t="s">
         <v>205</v>
       </c>
-      <c r="I60" s="101" t="s">
+      <c r="I60" s="96" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="61" spans="2:9" ht="20" thickBot="1">
-      <c r="B61" s="87"/>
+      <c r="B61" s="102"/>
       <c r="C61" s="13"/>
       <c r="D61" s="13"/>
       <c r="E61" s="13"/>
@@ -9678,10 +9692,10 @@
       <c r="G61" s="51" t="s">
         <v>206</v>
       </c>
-      <c r="I61" s="99"/>
+      <c r="I61" s="94"/>
     </row>
     <row r="62" spans="2:9" ht="20" thickBot="1">
-      <c r="B62" s="87"/>
+      <c r="B62" s="102"/>
       <c r="C62" s="13"/>
       <c r="D62" s="13"/>
       <c r="E62" s="13"/>
@@ -9696,8 +9710,8 @@
       </c>
     </row>
     <row r="63" spans="2:9" ht="19" customHeight="1">
-      <c r="B63" s="87"/>
-      <c r="C63" s="83" t="s">
+      <c r="B63" s="102"/>
+      <c r="C63" s="89" t="s">
         <v>153</v>
       </c>
       <c r="D63" s="13" t="s">
@@ -9706,41 +9720,41 @@
       <c r="E63" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="F63" s="89" t="s">
+      <c r="F63" s="82" t="s">
         <v>198</v>
       </c>
-      <c r="G63" s="92" t="s">
+      <c r="G63" s="85" t="s">
         <v>197</v>
       </c>
-      <c r="I63" s="101" t="s">
+      <c r="I63" s="96" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="64" spans="2:9" ht="19" customHeight="1">
-      <c r="B64" s="87"/>
-      <c r="C64" s="83"/>
+      <c r="B64" s="102"/>
+      <c r="C64" s="89"/>
       <c r="D64" s="13" t="s">
         <v>155</v>
       </c>
       <c r="E64" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="F64" s="90"/>
-      <c r="G64" s="93"/>
-      <c r="I64" s="99"/>
+      <c r="F64" s="83"/>
+      <c r="G64" s="86"/>
+      <c r="I64" s="94"/>
     </row>
     <row r="65" spans="2:9" ht="19" customHeight="1" thickBot="1">
-      <c r="B65" s="88"/>
-      <c r="C65" s="84"/>
+      <c r="B65" s="103"/>
+      <c r="C65" s="100"/>
       <c r="D65" s="48" t="s">
         <v>162</v>
       </c>
       <c r="E65" s="48" t="s">
         <v>157</v>
       </c>
-      <c r="F65" s="91"/>
-      <c r="G65" s="94"/>
-      <c r="I65" s="102"/>
+      <c r="F65" s="84"/>
+      <c r="G65" s="87"/>
+      <c r="I65" s="97"/>
     </row>
     <row r="67" spans="2:9">
       <c r="E67" s="1" t="s">
@@ -9752,6 +9766,22 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C42:C49"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="B16:B20"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="B42:B65"/>
+    <mergeCell ref="C22:C28"/>
+    <mergeCell ref="B22:B30"/>
+    <mergeCell ref="B31:B41"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="C37:C39"/>
     <mergeCell ref="F63:F65"/>
     <mergeCell ref="G63:G65"/>
     <mergeCell ref="F16:F18"/>
@@ -9761,22 +9791,6 @@
     <mergeCell ref="I60:I61"/>
     <mergeCell ref="I63:I65"/>
     <mergeCell ref="G16:G18"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="B42:B65"/>
-    <mergeCell ref="C22:C28"/>
-    <mergeCell ref="B22:B30"/>
-    <mergeCell ref="B31:B41"/>
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C42:C49"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="B16:B20"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/dict/dict 코드북 260430.xlsx
+++ b/datasets/dict/dict 코드북 260430.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233DA852-2893-4F46-8CF0-2DAC778D5D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6441943F-DCBF-9145-B349-1DC22EA1462F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" xr2:uid="{F4A985C0-B43D-2244-AB7C-DBFAE8B9580A}"/>
   </bookViews>
@@ -191,10 +191,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>note</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>작성자용 메모</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4931,6 +4927,10 @@
 'stage'가 'verify'인 경우 'target'은 'raw_sentence' 혹은 'token_window'가능함.
 token_window: 문법 항목 스팬의 앞 뒤 10char 안으로 설정되어 있음. 즉, 이 범위 안에서 verify 정규식 조건을 찾아서 hard fail시킴.
 component_right_context: 'component_id'열의 component 오른쪽 char에 대한 조건을 'pattern'열 항목에 기록한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rule_note</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6225,7 +6225,7 @@
         <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>11</v>
@@ -6240,7 +6240,7 @@
         <v>9</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I1" s="8"/>
     </row>
@@ -6301,7 +6301,7 @@
     <row r="3" spans="1:50" ht="40" customHeight="1" thickBot="1">
       <c r="A3" s="26"/>
       <c r="B3" s="67" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C3" s="27"/>
       <c r="D3" s="27"/>
@@ -6316,14 +6316,14 @@
         <v>0</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
       <c r="F4" s="24"/>
       <c r="G4" s="25"/>
       <c r="H4" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:50" ht="84" customHeight="1">
@@ -6332,7 +6332,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -6346,7 +6346,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="72" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>6</v>
@@ -6373,7 +6373,7 @@
       <c r="B8" s="78"/>
       <c r="C8" s="74"/>
       <c r="D8" s="13" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="11"/>
@@ -6383,10 +6383,10 @@
     <row r="9" spans="1:50" ht="165" customHeight="1">
       <c r="A9" s="9"/>
       <c r="B9" s="37" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
@@ -6397,7 +6397,7 @@
     <row r="10" spans="1:50" ht="67" customHeight="1">
       <c r="A10" s="9"/>
       <c r="B10" s="37" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="13"/>
@@ -6409,7 +6409,7 @@
     <row r="11" spans="1:50" ht="67" customHeight="1">
       <c r="A11" s="9"/>
       <c r="B11" s="37" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="13"/>
@@ -6424,7 +6424,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
@@ -6440,12 +6440,12 @@
         <v>14</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="9"/>
@@ -6453,15 +6453,15 @@
     <row r="14" spans="1:50" ht="19">
       <c r="A14" s="9"/>
       <c r="B14" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="9"/>
@@ -6469,15 +6469,15 @@
     <row r="15" spans="1:50" ht="19">
       <c r="A15" s="9"/>
       <c r="B15" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
       <c r="F15" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="9"/>
@@ -6488,7 +6488,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
@@ -6499,10 +6499,10 @@
     <row r="17" spans="1:8" ht="40" customHeight="1">
       <c r="A17" s="9"/>
       <c r="B17" s="66" t="s">
+        <v>509</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>510</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>511</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
@@ -6516,7 +6516,7 @@
         <v>0</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
@@ -6530,7 +6530,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
@@ -6543,10 +6543,10 @@
     <row r="20" spans="1:8" ht="19">
       <c r="A20" s="9"/>
       <c r="B20" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>525</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>526</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
@@ -6560,7 +6560,7 @@
         <v>15</v>
       </c>
       <c r="C21" s="79" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>2</v>
@@ -6588,14 +6588,14 @@
         <v>18</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
       <c r="F23" s="11"/>
       <c r="G23" s="10"/>
       <c r="H23" s="9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="38">
@@ -6604,7 +6604,7 @@
         <v>17</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
@@ -6618,12 +6618,12 @@
         <v>21</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
       <c r="F25" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="9"/>
@@ -6634,7 +6634,7 @@
         <v>19</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
@@ -6650,7 +6650,7 @@
         <v>20</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
@@ -6663,10 +6663,10 @@
     <row r="28" spans="1:8" ht="145" customHeight="1">
       <c r="A28" s="9"/>
       <c r="B28" s="65" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
@@ -6680,7 +6680,7 @@
         <v>0</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
@@ -6691,10 +6691,10 @@
     <row r="30" spans="1:8">
       <c r="A30" s="9"/>
       <c r="B30" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
@@ -6708,7 +6708,7 @@
         <v>26</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
@@ -6722,7 +6722,7 @@
         <v>29</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
@@ -6736,7 +6736,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="68" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
@@ -6747,10 +6747,10 @@
     <row r="34" spans="1:8" ht="57">
       <c r="A34" s="9"/>
       <c r="B34" s="17" t="s">
+        <v>526</v>
+      </c>
+      <c r="C34" s="68" t="s">
         <v>527</v>
-      </c>
-      <c r="C34" s="68" t="s">
-        <v>528</v>
       </c>
       <c r="D34" s="13"/>
       <c r="E34" s="13"/>
@@ -6764,7 +6764,7 @@
         <v>25</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D35" s="13"/>
       <c r="E35" s="13" t="s">
@@ -6780,7 +6780,7 @@
         <v>32</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D36" s="13"/>
       <c r="E36" s="13" t="s">
@@ -6809,10 +6809,10 @@
     <row r="38" spans="1:8" ht="19">
       <c r="A38" s="9"/>
       <c r="B38" s="17" t="s">
+        <v>529</v>
+      </c>
+      <c r="C38" s="9" t="s">
         <v>37</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>38</v>
       </c>
       <c r="D38" s="13"/>
       <c r="E38" s="13" t="s">
@@ -7115,7 +7115,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B1">
         <v>260222</v>
@@ -7123,207 +7123,207 @@
     </row>
     <row r="2" spans="1:2">
       <c r="B2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="27">
       <c r="B6" s="31" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" s="33" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="B12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="33" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="27">
       <c r="B26" s="31" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="20">
       <c r="B28" s="32" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" s="33" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" s="33" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" s="33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="72" spans="2:2">
       <c r="B72" s="33" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" s="33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="82" spans="2:2">
       <c r="B82" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="84" spans="2:2">
       <c r="B84" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="88" spans="2:2" ht="20">
       <c r="B88" s="32" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="89" spans="2:2" ht="20">
@@ -7331,532 +7331,532 @@
     </row>
     <row r="90" spans="2:2">
       <c r="B90" s="5" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="92" spans="2:2">
       <c r="B92" s="33" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="94" spans="2:2">
       <c r="B94" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="95" spans="2:2">
       <c r="B95" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="101" spans="2:2">
       <c r="B101" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" s="33" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" s="33" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="119" spans="2:2">
       <c r="B119" s="33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" s="33" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="127" spans="2:2">
       <c r="B127" s="33" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="129" spans="2:2">
       <c r="B129" s="33" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="131" spans="2:2">
       <c r="B131" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="133" spans="2:2">
       <c r="B133" s="33" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="135" spans="2:2">
       <c r="B135" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="137" spans="2:2">
       <c r="B137" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="141" spans="2:2" ht="20">
       <c r="B141" s="32" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="143" spans="2:2">
       <c r="B143" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="145" spans="2:2">
       <c r="B145" s="33" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="147" spans="2:2">
       <c r="B147" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="149" spans="2:2">
       <c r="B149" s="33" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="151" spans="2:2">
       <c r="B151" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="153" spans="2:2">
       <c r="B153" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="155" spans="2:2">
       <c r="B155" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="157" spans="2:2">
       <c r="B157" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="159" spans="2:2">
       <c r="B159" s="33" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="160" spans="2:2">
       <c r="B160" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="162" spans="2:2">
       <c r="B162" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="164" spans="2:2">
       <c r="B164" s="33" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="165" spans="2:2">
       <c r="B165" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="167" spans="2:2">
       <c r="B167" s="33" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="169" spans="2:2">
       <c r="B169" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="171" spans="2:2">
       <c r="B171" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="173" spans="2:2">
       <c r="B173" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="177" spans="2:2" ht="20">
       <c r="B177" s="32" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="179" spans="2:2">
       <c r="B179" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="181" spans="2:2">
       <c r="B181" s="33" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="183" spans="2:2">
       <c r="B183" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="185" spans="2:2">
       <c r="B185" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="187" spans="2:2">
       <c r="B187" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="189" spans="2:2">
       <c r="B189" s="33" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="191" spans="2:2">
       <c r="B191" s="33" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="33" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="199" spans="2:2">
       <c r="B199" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="201" spans="2:2">
       <c r="B201" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="203" spans="2:2">
       <c r="B203" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="205" spans="2:2">
       <c r="B205" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="207" spans="2:2">
       <c r="B207" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="211" spans="2:2" ht="27">
       <c r="B211" s="31" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="213" spans="2:2" ht="20">
       <c r="B213" s="32" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="215" spans="2:2">
       <c r="B215" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="217" spans="2:2">
       <c r="B217" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="219" spans="2:2">
       <c r="B219" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="221" spans="2:2">
       <c r="B221" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="223" spans="2:2">
       <c r="B223" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="225" spans="2:2" ht="20">
       <c r="B225" s="32" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="227" spans="2:2">
       <c r="B227" s="33" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="229" spans="2:2">
       <c r="B229" s="33" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="231" spans="2:2">
       <c r="B231" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="233" spans="2:2" ht="20">
       <c r="B233" s="32" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="235" spans="2:2">
       <c r="B235" s="33" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="237" spans="2:2">
       <c r="B237" s="33" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="239" spans="2:2">
       <c r="B239" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="241" spans="2:2">
       <c r="B241" s="33" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="243" spans="2:2">
       <c r="B243" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="245" spans="2:2" ht="20">
       <c r="B245" s="32" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="247" spans="2:2">
       <c r="B247" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="249" spans="2:2">
       <c r="B249" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="251" spans="2:2">
       <c r="B251" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="253" spans="2:2" ht="20">
       <c r="B253" s="32" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="255" spans="2:2">
       <c r="B255" s="33" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="257" spans="2:2">
       <c r="B257" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="259" spans="2:2" ht="20">
       <c r="B259" s="32" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="261" spans="2:2">
       <c r="B261" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="263" spans="2:2">
       <c r="B263" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="267" spans="2:2" ht="27">
       <c r="B267" s="31" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="269" spans="2:2">
       <c r="B269" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="271" spans="2:2">
       <c r="B271" s="33" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="273" spans="2:2">
       <c r="B273" s="33" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="279" spans="2:2">
       <c r="B279" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="281" spans="2:2">
       <c r="B281" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="283" spans="2:2">
       <c r="B283" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="287" spans="2:2" ht="27">
       <c r="B287" s="31" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="289" spans="2:2">
       <c r="B289" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="291" spans="2:2">
       <c r="B291" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="293" spans="2:2">
       <c r="B293" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="295" spans="2:2">
       <c r="B295" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="300" spans="2:2">
       <c r="B300" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="302" spans="2:2">
       <c r="B302" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="304" spans="2:2">
       <c r="B304" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="305" spans="2:2">
       <c r="B305" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -7873,7 +7873,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B1">
         <v>260222</v>
@@ -7881,667 +7881,667 @@
     </row>
     <row r="2" spans="1:2">
       <c r="B2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="27">
       <c r="B6" s="31" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="B12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="27">
       <c r="B20" s="31" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="20">
       <c r="B22" s="32" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" s="33" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="30" spans="2:2" ht="20">
       <c r="B30" s="32" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="46" spans="2:2" ht="20">
       <c r="B46" s="32" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="69" spans="2:2" ht="20">
       <c r="B69" s="32" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="81" spans="2:2" ht="20">
       <c r="B81" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="85" spans="2:2">
       <c r="B85" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="87" spans="2:2">
       <c r="B87" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="91" spans="2:2">
       <c r="B91" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="93" spans="2:2">
       <c r="B93" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="97" spans="2:2" ht="27">
       <c r="B97" s="31" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="101" spans="2:2" ht="20">
       <c r="B101" s="32" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="117" spans="2:2" ht="20">
       <c r="B117" s="32" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="119" spans="2:2">
       <c r="B119" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="127" spans="2:2">
       <c r="B127" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="129" spans="2:2" ht="20">
       <c r="B129" s="32" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="131" spans="2:2">
       <c r="B131" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="133" spans="2:2">
       <c r="B133" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="135" spans="2:2">
       <c r="B135" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="137" spans="2:2">
       <c r="B137" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="139" spans="2:2" ht="20">
       <c r="B139" s="32" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="141" spans="2:2">
       <c r="B141" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="143" spans="2:2">
       <c r="B143" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="145" spans="2:2">
       <c r="B145" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="149" spans="2:2" ht="27">
       <c r="B149" s="31" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="151" spans="2:2" ht="20">
       <c r="B151" s="32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="153" spans="2:2">
       <c r="B153" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="155" spans="2:2">
       <c r="B155" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="2:2">
       <c r="B157" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="2:2">
       <c r="B159" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="2:2">
       <c r="B161" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="2:2">
       <c r="B163" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="165" spans="2:2">
       <c r="B165" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="167" spans="2:2" ht="20">
       <c r="B167" s="32" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="169" spans="2:2">
       <c r="B169" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="171" spans="2:2">
       <c r="B171" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="173" spans="2:2">
       <c r="B173" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="175" spans="2:2">
       <c r="B175" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="177" spans="2:2">
       <c r="B177" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="179" spans="2:2">
       <c r="B179" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="180" spans="2:2">
       <c r="B180" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="182" spans="2:2">
       <c r="B182" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="184" spans="2:2">
       <c r="B184" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="186" spans="2:2" ht="20">
       <c r="B186" s="32" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="188" spans="2:2">
       <c r="B188" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="190" spans="2:2">
       <c r="B190" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="192" spans="2:2">
       <c r="B192" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="198" spans="2:2">
       <c r="B198" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="200" spans="2:2" ht="20">
       <c r="B200" s="32" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="202" spans="2:2">
       <c r="B202" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="204" spans="2:2">
       <c r="B204" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="206" spans="2:2">
       <c r="B206" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="208" spans="2:2">
       <c r="B208" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="210" spans="2:2">
       <c r="B210" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="212" spans="2:2">
       <c r="B212" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="213" spans="2:2">
       <c r="B213" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="215" spans="2:2">
       <c r="B215" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="219" spans="2:2" ht="27">
       <c r="B219" s="31" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="221" spans="2:2">
       <c r="B221" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="223" spans="2:2">
       <c r="B223" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="225" spans="2:2">
       <c r="B225" s="5" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="227" spans="2:2">
       <c r="B227" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="229" spans="2:2">
       <c r="B229" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="231" spans="2:2">
       <c r="B231" s="33" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="233" spans="2:2">
       <c r="B233" s="33" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="235" spans="2:2">
       <c r="B235" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="237" spans="2:2">
       <c r="B237" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="239" spans="2:2">
       <c r="B239" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="241" spans="2:2">
       <c r="B241" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="245" spans="2:2" ht="27">
       <c r="B245" s="31" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="247" spans="2:2" ht="20">
       <c r="B247" s="32" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="249" spans="2:2">
       <c r="B249" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="250" spans="2:2">
       <c r="B250" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="251" spans="2:2">
       <c r="B251" s="5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="253" spans="2:2" ht="20">
       <c r="B253" s="32" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="255" spans="2:2">
       <c r="B255" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="256" spans="2:2">
       <c r="B256" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="258" spans="2:2" ht="20">
       <c r="B258" s="32" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="260" spans="2:2">
       <c r="B260" s="33" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="261" spans="2:2">
       <c r="B261" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="262" spans="2:2">
       <c r="B262" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -8563,89 +8563,89 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>165</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>168</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>170</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="10" spans="2:8">
       <c r="B10" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="2:8">
       <c r="B11" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="90" customHeight="1">
       <c r="B16" s="80" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C16" s="80"/>
       <c r="D16" s="80"/>
@@ -8656,7 +8656,7 @@
     </row>
     <row r="18" spans="2:5" ht="114" customHeight="1">
       <c r="B18" s="81" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C18" s="81"/>
       <c r="D18" s="81"/>
@@ -8693,255 +8693,255 @@
   <sheetData>
     <row r="2" spans="2:10">
       <c r="B2" s="33" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="19" thickBot="1"/>
     <row r="4" spans="2:10">
       <c r="B4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F4" s="104" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G4" s="104"/>
       <c r="I4" s="57" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="20" thickBot="1">
       <c r="B5" s="42" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C5" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="E5" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="42" t="s">
-        <v>59</v>
-      </c>
       <c r="F5" s="43" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G5" s="42" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I5" s="58"/>
     </row>
     <row r="6" spans="2:10">
       <c r="B6" s="101" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="88" t="s">
-        <v>51</v>
-      </c>
       <c r="D6" s="44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F6" s="45"/>
       <c r="G6" s="46" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="2:10">
       <c r="B7" s="102"/>
       <c r="C7" s="89"/>
       <c r="D7" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>61</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>62</v>
       </c>
       <c r="F7" s="39"/>
       <c r="G7" s="47" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I7" s="60" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="2:10">
       <c r="B8" s="102"/>
       <c r="C8" s="89"/>
       <c r="D8" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="13" t="s">
         <v>63</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>64</v>
       </c>
       <c r="F8" s="39"/>
       <c r="G8" s="47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I8" s="60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="2:10">
       <c r="B9" s="102"/>
       <c r="C9" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>65</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>66</v>
       </c>
       <c r="F9" s="39"/>
       <c r="G9" s="47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I9" s="60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="19" thickBot="1">
       <c r="B10" s="103"/>
       <c r="C10" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="48" t="s">
         <v>67</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" s="48" t="s">
-        <v>68</v>
       </c>
       <c r="F10" s="49"/>
       <c r="G10" s="50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I10" s="61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="2:10">
       <c r="B11" s="101" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="44" t="s">
         <v>69</v>
-      </c>
-      <c r="D11" s="44" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" s="44" t="s">
-        <v>70</v>
       </c>
       <c r="F11" s="45"/>
       <c r="G11" s="46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H11" s="90" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I11" s="59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="2:10">
       <c r="B12" s="102"/>
       <c r="C12" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>71</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>72</v>
       </c>
       <c r="F12" s="39"/>
       <c r="G12" s="47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H12" s="91"/>
       <c r="I12" s="60" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="19" thickBot="1">
       <c r="B13" s="102"/>
       <c r="C13" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>73</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>74</v>
       </c>
       <c r="F13" s="39"/>
       <c r="G13" s="47" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H13" s="92"/>
       <c r="I13" s="60" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J13" s="5"/>
     </row>
     <row r="14" spans="2:10">
       <c r="B14" s="102"/>
       <c r="C14" s="89" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="E14" s="13" t="s">
         <v>76</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>77</v>
       </c>
       <c r="F14" s="39"/>
       <c r="G14" s="47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I14" s="60" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="19" thickBot="1">
       <c r="B15" s="103"/>
       <c r="C15" s="100"/>
       <c r="D15" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="48" t="s">
         <v>78</v>
-      </c>
-      <c r="E15" s="48" t="s">
-        <v>79</v>
       </c>
       <c r="F15" s="49"/>
       <c r="G15" s="50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I15" s="61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="2:10">
       <c r="B16" s="101" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="88" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="88" t="s">
-        <v>54</v>
-      </c>
       <c r="D16" s="44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F16" s="88" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G16" s="98" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I16" s="56"/>
     </row>
@@ -8949,10 +8949,10 @@
       <c r="B17" s="102"/>
       <c r="C17" s="89"/>
       <c r="D17" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F17" s="89"/>
       <c r="G17" s="99"/>
@@ -8962,10 +8962,10 @@
       <c r="B18" s="102"/>
       <c r="C18" s="89"/>
       <c r="D18" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F18" s="89"/>
       <c r="G18" s="99"/>
@@ -8974,380 +8974,380 @@
     <row r="19" spans="2:9">
       <c r="B19" s="102"/>
       <c r="C19" s="89" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="E19" s="13" t="s">
         <v>84</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>85</v>
       </c>
       <c r="F19" s="39"/>
       <c r="G19" s="47" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I19" s="60" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="19" thickBot="1">
       <c r="B20" s="103"/>
       <c r="C20" s="100"/>
       <c r="D20" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" s="48" t="s">
         <v>86</v>
-      </c>
-      <c r="E20" s="48" t="s">
-        <v>87</v>
       </c>
       <c r="F20" s="49"/>
       <c r="G20" s="50" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I20" s="61" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="19" thickBot="1">
       <c r="B21" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="C21" s="53" t="s">
+      <c r="D21" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="53" t="s">
         <v>89</v>
-      </c>
-      <c r="D21" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="53" t="s">
-        <v>90</v>
       </c>
       <c r="F21" s="54"/>
       <c r="G21" s="55" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I21" s="62" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="2:9">
       <c r="B22" s="101" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="88" t="s">
-        <v>56</v>
-      </c>
       <c r="D22" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="44" t="s">
         <v>91</v>
-      </c>
-      <c r="E22" s="44" t="s">
-        <v>92</v>
       </c>
       <c r="F22" s="45"/>
       <c r="G22" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I22" s="59" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="2:9">
       <c r="B23" s="102"/>
       <c r="C23" s="89"/>
       <c r="D23" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>93</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>94</v>
       </c>
       <c r="F23" s="39"/>
       <c r="G23" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I23" s="60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="2:9">
       <c r="B24" s="102"/>
       <c r="C24" s="89"/>
       <c r="D24" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>95</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>96</v>
       </c>
       <c r="F24" s="39"/>
       <c r="G24" s="47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I24" s="60" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="2:9">
       <c r="B25" s="102"/>
       <c r="C25" s="89"/>
       <c r="D25" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>97</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>98</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="47" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I25" s="60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="2:9">
       <c r="B26" s="102"/>
       <c r="C26" s="89"/>
       <c r="D26" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F26" s="39"/>
       <c r="G26" s="47" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I26" s="60" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="102"/>
       <c r="C27" s="89"/>
       <c r="D27" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F27" s="39"/>
       <c r="G27" s="47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I27" s="60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="2:9">
       <c r="B28" s="102"/>
       <c r="C28" s="89"/>
       <c r="D28" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" s="13" t="s">
         <v>101</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>102</v>
       </c>
       <c r="F28" s="39"/>
       <c r="G28" s="47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I28" s="60" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="2:9">
       <c r="B29" s="102"/>
       <c r="C29" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="13" t="s">
         <v>103</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>104</v>
       </c>
       <c r="F29" s="39"/>
       <c r="G29" s="47" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I29" s="60" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="2:9" ht="19" thickBot="1">
       <c r="B30" s="103"/>
       <c r="C30" s="48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D30" s="48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E30" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F30" s="49"/>
       <c r="G30" s="50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I30" s="61" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="2:9">
       <c r="B31" s="101" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C31" s="88" t="s">
+      <c r="D31" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="44" t="s">
+      <c r="E31" s="44" t="s">
         <v>115</v>
-      </c>
-      <c r="E31" s="44" t="s">
-        <v>116</v>
       </c>
       <c r="F31" s="45"/>
       <c r="G31" s="46" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I31" s="59" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="2:9">
       <c r="B32" s="102"/>
       <c r="C32" s="89"/>
       <c r="D32" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E32" s="13" t="s">
         <v>117</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>118</v>
       </c>
       <c r="F32" s="39"/>
       <c r="G32" s="47" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I32" s="60" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="2:9">
       <c r="B33" s="102"/>
       <c r="C33" s="89"/>
       <c r="D33" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="E33" s="13" t="s">
         <v>119</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>120</v>
       </c>
       <c r="F33" s="39"/>
       <c r="G33" s="47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I33" s="60" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="2:9">
       <c r="B34" s="102"/>
       <c r="C34" s="89"/>
       <c r="D34" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="E34" s="13" t="s">
         <v>121</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>122</v>
       </c>
       <c r="F34" s="39"/>
       <c r="G34" s="47" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I34" s="60" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="2:9">
       <c r="B35" s="102"/>
       <c r="C35" s="89"/>
       <c r="D35" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E35" s="13" t="s">
         <v>123</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>124</v>
       </c>
       <c r="F35" s="39"/>
       <c r="G35" s="47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I35" s="60" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="2:9">
       <c r="B36" s="102"/>
       <c r="C36" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="E36" s="13" t="s">
         <v>126</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>127</v>
       </c>
       <c r="F36" s="39"/>
       <c r="G36" s="47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I36" s="60" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="2:9">
       <c r="B37" s="102"/>
       <c r="C37" s="89" t="s">
+        <v>127</v>
+      </c>
+      <c r="D37" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D37" s="13" t="s">
-        <v>129</v>
-      </c>
       <c r="E37" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F37" s="39"/>
       <c r="G37" s="47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I37" s="60" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38" spans="2:9">
       <c r="B38" s="102"/>
       <c r="C38" s="89"/>
       <c r="D38" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E38" s="13" t="s">
         <v>130</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>131</v>
       </c>
       <c r="F38" s="39"/>
       <c r="G38" s="47" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I38" s="60" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" spans="2:9">
       <c r="B39" s="102"/>
       <c r="C39" s="89"/>
       <c r="D39" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E39" s="13" t="s">
         <v>132</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="F39" s="39"/>
       <c r="G39" s="47" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I39" s="60" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="19">
@@ -9356,87 +9356,87 @@
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
       <c r="F40" s="40" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G40" s="51" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I40" s="60" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="19" thickBot="1">
       <c r="B41" s="103"/>
       <c r="C41" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="D41" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="E41" s="48" t="s">
         <v>134</v>
-      </c>
-      <c r="D41" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="E41" s="48" t="s">
-        <v>135</v>
       </c>
       <c r="F41" s="49"/>
       <c r="G41" s="50" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I41" s="61" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="2:9">
       <c r="B42" s="101" t="s">
+        <v>135</v>
+      </c>
+      <c r="C42" s="88" t="s">
         <v>136</v>
       </c>
-      <c r="C42" s="88" t="s">
+      <c r="D42" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="D42" s="44" t="s">
+      <c r="E42" s="44" t="s">
         <v>138</v>
-      </c>
-      <c r="E42" s="44" t="s">
-        <v>139</v>
       </c>
       <c r="F42" s="45"/>
       <c r="G42" s="46" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I42" s="59" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43" spans="2:9">
       <c r="B43" s="102"/>
       <c r="C43" s="89"/>
       <c r="D43" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F43" s="39"/>
       <c r="G43" s="47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I43" s="60" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="2:9">
       <c r="B44" s="102"/>
       <c r="C44" s="89"/>
       <c r="D44" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="E44" s="13" t="s">
         <v>141</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>142</v>
       </c>
       <c r="F44" s="39"/>
       <c r="G44" s="47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I44" s="93" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="19">
@@ -9445,10 +9445,10 @@
       <c r="D45" s="13"/>
       <c r="E45" s="13"/>
       <c r="F45" s="40" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G45" s="51" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I45" s="94"/>
     </row>
@@ -9458,10 +9458,10 @@
       <c r="D46" s="13"/>
       <c r="E46" s="13"/>
       <c r="F46" s="40" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G46" s="51" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I46" s="95"/>
     </row>
@@ -9469,108 +9469,108 @@
       <c r="B47" s="102"/>
       <c r="C47" s="89"/>
       <c r="D47" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="E47" s="13" t="s">
         <v>143</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>144</v>
       </c>
       <c r="F47" s="39"/>
       <c r="G47" s="47" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I47" s="60" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="2:9">
       <c r="B48" s="102"/>
       <c r="C48" s="89"/>
       <c r="D48" s="35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F48" s="39"/>
       <c r="G48" s="47" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I48" s="60" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="2:9">
       <c r="B49" s="102"/>
       <c r="C49" s="89"/>
       <c r="D49" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F49" s="39"/>
       <c r="G49" s="47" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I49" s="60" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50" spans="2:9">
       <c r="B50" s="102"/>
       <c r="C50" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="E50" s="13" t="s">
         <v>147</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>148</v>
       </c>
       <c r="F50" s="39"/>
       <c r="G50" s="47" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I50" s="60" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51" spans="2:9">
       <c r="B51" s="102"/>
       <c r="C51" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E51" s="13" t="s">
         <v>149</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>150</v>
       </c>
       <c r="F51" s="39"/>
       <c r="G51" s="47" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I51" s="60" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="2:9" ht="19" thickBot="1">
       <c r="B52" s="102"/>
       <c r="C52" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="E52" s="13" t="s">
         <v>151</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>152</v>
       </c>
       <c r="F52" s="39"/>
       <c r="G52" s="47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I52" s="63" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53" spans="2:9" ht="57">
@@ -9579,13 +9579,13 @@
       <c r="D53" s="13"/>
       <c r="E53" s="13"/>
       <c r="F53" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="G53" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="G53" s="51" t="s">
-        <v>196</v>
-      </c>
       <c r="I53" s="96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="2:9" ht="19">
@@ -9594,10 +9594,10 @@
       <c r="D54" s="13"/>
       <c r="E54" s="13"/>
       <c r="F54" s="40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G54" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I54" s="94"/>
     </row>
@@ -9607,10 +9607,10 @@
       <c r="D55" s="13"/>
       <c r="E55" s="13"/>
       <c r="F55" s="40" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G55" s="51" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I55" s="94"/>
     </row>
@@ -9620,10 +9620,10 @@
       <c r="D56" s="13"/>
       <c r="E56" s="13"/>
       <c r="F56" s="40" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G56" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I56" s="94"/>
     </row>
@@ -9633,10 +9633,10 @@
       <c r="D57" s="13"/>
       <c r="E57" s="13"/>
       <c r="F57" s="40" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G57" s="51" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I57" s="94"/>
     </row>
@@ -9646,10 +9646,10 @@
       <c r="D58" s="13"/>
       <c r="E58" s="13"/>
       <c r="F58" s="40" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G58" s="51" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I58" s="94"/>
     </row>
@@ -9659,10 +9659,10 @@
       <c r="D59" s="13"/>
       <c r="E59" s="13"/>
       <c r="F59" s="40" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G59" s="51" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I59" s="97"/>
     </row>
@@ -9672,13 +9672,13 @@
       <c r="D60" s="13"/>
       <c r="E60" s="13"/>
       <c r="F60" s="40" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G60" s="51" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I60" s="96" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="61" spans="2:9" ht="20" thickBot="1">
@@ -9687,10 +9687,10 @@
       <c r="D61" s="13"/>
       <c r="E61" s="13"/>
       <c r="F61" s="40" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G61" s="51" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I61" s="94"/>
     </row>
@@ -9700,44 +9700,44 @@
       <c r="D62" s="13"/>
       <c r="E62" s="13"/>
       <c r="F62" s="40" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G62" s="51" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I62" s="62" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63" spans="2:9" ht="19" customHeight="1">
       <c r="B63" s="102"/>
       <c r="C63" s="89" t="s">
+        <v>152</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="E63" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="D63" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="E63" s="13" t="s">
-        <v>154</v>
-      </c>
       <c r="F63" s="82" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G63" s="85" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I63" s="96" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="64" spans="2:9" ht="19" customHeight="1">
       <c r="B64" s="102"/>
       <c r="C64" s="89"/>
       <c r="D64" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="E64" s="13" t="s">
         <v>155</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>156</v>
       </c>
       <c r="F64" s="83"/>
       <c r="G64" s="86"/>
@@ -9747,10 +9747,10 @@
       <c r="B65" s="103"/>
       <c r="C65" s="100"/>
       <c r="D65" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E65" s="48" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F65" s="84"/>
       <c r="G65" s="87"/>
@@ -9758,10 +9758,10 @@
     </row>
     <row r="67" spans="2:9">
       <c r="E67" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/dict/dict 코드북 260430.xlsx
+++ b/datasets/dict/dict 코드북 260430.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6441943F-DCBF-9145-B349-1DC22EA1462F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA052DC-52BD-FE4A-BC56-D7F57ED7A030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" xr2:uid="{F4A985C0-B43D-2244-AB7C-DBFAE8B9580A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="531">
   <si>
     <t>e_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4923,14 +4923,33 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>rule_note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>stage'가 'detect'인 경우 'target'은 항상 'raw_sentence'여야 함.
-'stage'가 'verify'인 경우 'target'은 'raw_sentence' 혹은 'token_window'가능함.
+'stage'가 'verify'인 경우 'target'은 'raw_sentence', 'token_window', 'component_right_context' 가능함.
 token_window: 문법 항목 스팬의 앞 뒤 10char 안으로 설정되어 있음. 즉, 이 범위 안에서 verify 정규식 조건을 찾아서 hard fail시킴.
-component_right_context: 'component_id'열의 component 오른쪽 char에 대한 조건을 'pattern'열 항목에 기록한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rule_note</t>
+component_right_context
+선택된 component 시작점 바로 오른쪽 1글자.
+예: '팬데믹'에서 c1='팬데'이면 믹. 다만 오른쪽이 공백이면 공백을 건너뛰고 의미문자를 찾음.
+용도: component 오른쪽 환경을 확인할 때 사용. 단독 hard fail에는 신중히 사용.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(왼쪽 설명에 추가)
+component_text
+선택된 component span 자체의 문자열.
+예: 근데, 텐데, 운데, 런데
+용도: component 자체가 특정 오탐 표면형일 때 hard fail. 
+component_left_context
+선택된 component 시작점 바로 왼쪽 1글자.
+예: '가운데'에서 c1='운데'이면 left_context=가
+용도: component 왼쪽 환경을 확인할 때 사용. 단독 hard fail에는 신중히 사용.
+left_plus_component_text
+선택된 component 바로 왼쪽 1글자 + component_text.  다만 왼쪽이 공백이면 공백을 건너뛰고 의미문자를 찾음.
+예: 가운데 → 가+운데=가운데, 가는데 → 가+는데=가는데
+용도: 가운데/그런데처럼 왼쪽 1글자와 component를 합쳐야 정확히 구별되는 오탐 hard fail.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5800,6 +5819,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5818,12 +5858,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5852,21 +5886,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6730,17 +6749,19 @@
       <c r="G32" s="10"/>
       <c r="H32" s="9"/>
     </row>
-    <row r="33" spans="1:8" ht="162" customHeight="1">
+    <row r="33" spans="1:8" ht="352" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="17" t="s">
         <v>31</v>
       </c>
       <c r="C33" s="68" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
-      <c r="F33" s="11"/>
+      <c r="F33" s="11" t="s">
+        <v>530</v>
+      </c>
       <c r="G33" s="10"/>
       <c r="H33" s="9"/>
     </row>
@@ -6809,7 +6830,7 @@
     <row r="38" spans="1:8" ht="19">
       <c r="A38" s="9"/>
       <c r="B38" s="17" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>37</v>
@@ -8701,10 +8722,10 @@
       <c r="B4" t="s">
         <v>162</v>
       </c>
-      <c r="F4" s="104" t="s">
+      <c r="F4" s="82" t="s">
         <v>185</v>
       </c>
-      <c r="G4" s="104"/>
+      <c r="G4" s="82"/>
       <c r="I4" s="57" t="s">
         <v>220</v>
       </c>
@@ -8731,10 +8752,10 @@
       <c r="I5" s="58"/>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="101" t="s">
+      <c r="B6" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="88" t="s">
+      <c r="C6" s="85" t="s">
         <v>50</v>
       </c>
       <c r="D6" s="44" t="s">
@@ -8752,8 +8773,8 @@
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="102"/>
-      <c r="C7" s="89"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="83"/>
       <c r="D7" s="13" t="s">
         <v>60</v>
       </c>
@@ -8769,8 +8790,8 @@
       </c>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="102"/>
-      <c r="C8" s="89"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="83"/>
       <c r="D8" s="13" t="s">
         <v>62</v>
       </c>
@@ -8786,7 +8807,7 @@
       </c>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="102"/>
+      <c r="B9" s="87"/>
       <c r="C9" s="13" t="s">
         <v>64</v>
       </c>
@@ -8805,7 +8826,7 @@
       </c>
     </row>
     <row r="10" spans="2:10" ht="19" thickBot="1">
-      <c r="B10" s="103"/>
+      <c r="B10" s="88"/>
       <c r="C10" s="48" t="s">
         <v>66</v>
       </c>
@@ -8824,7 +8845,7 @@
       </c>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="101" t="s">
+      <c r="B11" s="86" t="s">
         <v>51</v>
       </c>
       <c r="C11" s="44" t="s">
@@ -8840,7 +8861,7 @@
       <c r="G11" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="H11" s="90" t="s">
+      <c r="H11" s="95" t="s">
         <v>219</v>
       </c>
       <c r="I11" s="59" t="s">
@@ -8848,7 +8869,7 @@
       </c>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="102"/>
+      <c r="B12" s="87"/>
       <c r="C12" s="13" t="s">
         <v>70</v>
       </c>
@@ -8862,13 +8883,13 @@
       <c r="G12" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="H12" s="91"/>
+      <c r="H12" s="96"/>
       <c r="I12" s="60" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="19" thickBot="1">
-      <c r="B13" s="102"/>
+      <c r="B13" s="87"/>
       <c r="C13" s="13" t="s">
         <v>72</v>
       </c>
@@ -8882,15 +8903,15 @@
       <c r="G13" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="H13" s="92"/>
+      <c r="H13" s="97"/>
       <c r="I13" s="60" t="s">
         <v>73</v>
       </c>
       <c r="J13" s="5"/>
     </row>
     <row r="14" spans="2:10">
-      <c r="B14" s="102"/>
-      <c r="C14" s="89" t="s">
+      <c r="B14" s="87"/>
+      <c r="C14" s="83" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="13" t="s">
@@ -8908,8 +8929,8 @@
       </c>
     </row>
     <row r="15" spans="2:10" ht="19" thickBot="1">
-      <c r="B15" s="103"/>
-      <c r="C15" s="100"/>
+      <c r="B15" s="88"/>
+      <c r="C15" s="84"/>
       <c r="D15" s="48" t="s">
         <v>77</v>
       </c>
@@ -8925,10 +8946,10 @@
       </c>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="101" t="s">
+      <c r="B16" s="86" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="88" t="s">
+      <c r="C16" s="85" t="s">
         <v>53</v>
       </c>
       <c r="D16" s="44" t="s">
@@ -8937,43 +8958,43 @@
       <c r="E16" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="88" t="s">
+      <c r="F16" s="85" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="98" t="s">
+      <c r="G16" s="103" t="s">
         <v>187</v>
       </c>
       <c r="I16" s="56"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="102"/>
-      <c r="C17" s="89"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="83"/>
       <c r="D17" s="13" t="s">
         <v>107</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="89"/>
-      <c r="G17" s="99"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="104"/>
       <c r="I17" s="56"/>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="102"/>
-      <c r="C18" s="89"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="83"/>
       <c r="D18" s="13" t="s">
         <v>110</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="F18" s="89"/>
-      <c r="G18" s="99"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="104"/>
       <c r="I18" s="56"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="102"/>
-      <c r="C19" s="89" t="s">
+      <c r="B19" s="87"/>
+      <c r="C19" s="83" t="s">
         <v>82</v>
       </c>
       <c r="D19" s="13" t="s">
@@ -8991,8 +9012,8 @@
       </c>
     </row>
     <row r="20" spans="2:9" ht="19" thickBot="1">
-      <c r="B20" s="103"/>
-      <c r="C20" s="100"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="84"/>
       <c r="D20" s="48" t="s">
         <v>85</v>
       </c>
@@ -9029,10 +9050,10 @@
       </c>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="101" t="s">
+      <c r="B22" s="86" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="88" t="s">
+      <c r="C22" s="85" t="s">
         <v>55</v>
       </c>
       <c r="D22" s="44" t="s">
@@ -9050,8 +9071,8 @@
       </c>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="102"/>
-      <c r="C23" s="89"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="83"/>
       <c r="D23" s="13" t="s">
         <v>92</v>
       </c>
@@ -9067,8 +9088,8 @@
       </c>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="102"/>
-      <c r="C24" s="89"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="83"/>
       <c r="D24" s="13" t="s">
         <v>94</v>
       </c>
@@ -9084,8 +9105,8 @@
       </c>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="102"/>
-      <c r="C25" s="89"/>
+      <c r="B25" s="87"/>
+      <c r="C25" s="83"/>
       <c r="D25" s="13" t="s">
         <v>96</v>
       </c>
@@ -9101,8 +9122,8 @@
       </c>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="102"/>
-      <c r="C26" s="89"/>
+      <c r="B26" s="87"/>
+      <c r="C26" s="83"/>
       <c r="D26" s="13" t="s">
         <v>108</v>
       </c>
@@ -9118,8 +9139,8 @@
       </c>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="102"/>
-      <c r="C27" s="89"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="83"/>
       <c r="D27" s="13" t="s">
         <v>111</v>
       </c>
@@ -9135,8 +9156,8 @@
       </c>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="102"/>
-      <c r="C28" s="89"/>
+      <c r="B28" s="87"/>
+      <c r="C28" s="83"/>
       <c r="D28" s="13" t="s">
         <v>100</v>
       </c>
@@ -9152,7 +9173,7 @@
       </c>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="102"/>
+      <c r="B29" s="87"/>
       <c r="C29" s="13" t="s">
         <v>102</v>
       </c>
@@ -9171,7 +9192,7 @@
       </c>
     </row>
     <row r="30" spans="2:9" ht="19" thickBot="1">
-      <c r="B30" s="103"/>
+      <c r="B30" s="88"/>
       <c r="C30" s="48" t="s">
         <v>104</v>
       </c>
@@ -9190,10 +9211,10 @@
       </c>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="101" t="s">
+      <c r="B31" s="86" t="s">
         <v>112</v>
       </c>
-      <c r="C31" s="88" t="s">
+      <c r="C31" s="85" t="s">
         <v>113</v>
       </c>
       <c r="D31" s="44" t="s">
@@ -9211,8 +9232,8 @@
       </c>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="102"/>
-      <c r="C32" s="89"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="83"/>
       <c r="D32" s="13" t="s">
         <v>116</v>
       </c>
@@ -9228,8 +9249,8 @@
       </c>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="102"/>
-      <c r="C33" s="89"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="83"/>
       <c r="D33" s="13" t="s">
         <v>118</v>
       </c>
@@ -9245,8 +9266,8 @@
       </c>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="102"/>
-      <c r="C34" s="89"/>
+      <c r="B34" s="87"/>
+      <c r="C34" s="83"/>
       <c r="D34" s="13" t="s">
         <v>120</v>
       </c>
@@ -9262,8 +9283,8 @@
       </c>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="102"/>
-      <c r="C35" s="89"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="83"/>
       <c r="D35" s="13" t="s">
         <v>122</v>
       </c>
@@ -9279,7 +9300,7 @@
       </c>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="102"/>
+      <c r="B36" s="87"/>
       <c r="C36" s="13" t="s">
         <v>124</v>
       </c>
@@ -9298,8 +9319,8 @@
       </c>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="102"/>
-      <c r="C37" s="89" t="s">
+      <c r="B37" s="87"/>
+      <c r="C37" s="83" t="s">
         <v>127</v>
       </c>
       <c r="D37" s="13" t="s">
@@ -9317,8 +9338,8 @@
       </c>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="102"/>
-      <c r="C38" s="89"/>
+      <c r="B38" s="87"/>
+      <c r="C38" s="83"/>
       <c r="D38" s="13" t="s">
         <v>129</v>
       </c>
@@ -9334,8 +9355,8 @@
       </c>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="102"/>
-      <c r="C39" s="89"/>
+      <c r="B39" s="87"/>
+      <c r="C39" s="83"/>
       <c r="D39" s="13" t="s">
         <v>131</v>
       </c>
@@ -9351,7 +9372,7 @@
       </c>
     </row>
     <row r="40" spans="2:9" ht="19">
-      <c r="B40" s="102"/>
+      <c r="B40" s="87"/>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
@@ -9366,7 +9387,7 @@
       </c>
     </row>
     <row r="41" spans="2:9" ht="19" thickBot="1">
-      <c r="B41" s="103"/>
+      <c r="B41" s="88"/>
       <c r="C41" s="48" t="s">
         <v>133</v>
       </c>
@@ -9385,10 +9406,10 @@
       </c>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="101" t="s">
+      <c r="B42" s="86" t="s">
         <v>135</v>
       </c>
-      <c r="C42" s="88" t="s">
+      <c r="C42" s="85" t="s">
         <v>136</v>
       </c>
       <c r="D42" s="44" t="s">
@@ -9406,8 +9427,8 @@
       </c>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="102"/>
-      <c r="C43" s="89"/>
+      <c r="B43" s="87"/>
+      <c r="C43" s="83"/>
       <c r="D43" s="13" t="s">
         <v>158</v>
       </c>
@@ -9423,8 +9444,8 @@
       </c>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="102"/>
-      <c r="C44" s="89"/>
+      <c r="B44" s="87"/>
+      <c r="C44" s="83"/>
       <c r="D44" s="13" t="s">
         <v>140</v>
       </c>
@@ -9435,13 +9456,13 @@
       <c r="G44" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="I44" s="93" t="s">
+      <c r="I44" s="98" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="19">
-      <c r="B45" s="102"/>
-      <c r="C45" s="89"/>
+      <c r="B45" s="87"/>
+      <c r="C45" s="83"/>
       <c r="D45" s="13"/>
       <c r="E45" s="13"/>
       <c r="F45" s="40" t="s">
@@ -9450,11 +9471,11 @@
       <c r="G45" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="I45" s="94"/>
+      <c r="I45" s="99"/>
     </row>
     <row r="46" spans="2:9" ht="19">
-      <c r="B46" s="102"/>
-      <c r="C46" s="89"/>
+      <c r="B46" s="87"/>
+      <c r="C46" s="83"/>
       <c r="D46" s="13"/>
       <c r="E46" s="13"/>
       <c r="F46" s="40" t="s">
@@ -9463,11 +9484,11 @@
       <c r="G46" s="51" t="s">
         <v>193</v>
       </c>
-      <c r="I46" s="95"/>
+      <c r="I46" s="100"/>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="102"/>
-      <c r="C47" s="89"/>
+      <c r="B47" s="87"/>
+      <c r="C47" s="83"/>
       <c r="D47" s="13" t="s">
         <v>142</v>
       </c>
@@ -9483,8 +9504,8 @@
       </c>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="102"/>
-      <c r="C48" s="89"/>
+      <c r="B48" s="87"/>
+      <c r="C48" s="83"/>
       <c r="D48" s="35" t="s">
         <v>159</v>
       </c>
@@ -9500,8 +9521,8 @@
       </c>
     </row>
     <row r="49" spans="2:9">
-      <c r="B49" s="102"/>
-      <c r="C49" s="89"/>
+      <c r="B49" s="87"/>
+      <c r="C49" s="83"/>
       <c r="D49" s="13" t="s">
         <v>160</v>
       </c>
@@ -9517,7 +9538,7 @@
       </c>
     </row>
     <row r="50" spans="2:9">
-      <c r="B50" s="102"/>
+      <c r="B50" s="87"/>
       <c r="C50" s="13" t="s">
         <v>146</v>
       </c>
@@ -9536,7 +9557,7 @@
       </c>
     </row>
     <row r="51" spans="2:9">
-      <c r="B51" s="102"/>
+      <c r="B51" s="87"/>
       <c r="C51" s="13" t="s">
         <v>148</v>
       </c>
@@ -9555,7 +9576,7 @@
       </c>
     </row>
     <row r="52" spans="2:9" ht="19" thickBot="1">
-      <c r="B52" s="102"/>
+      <c r="B52" s="87"/>
       <c r="C52" s="13" t="s">
         <v>150</v>
       </c>
@@ -9574,7 +9595,7 @@
       </c>
     </row>
     <row r="53" spans="2:9" ht="57">
-      <c r="B53" s="102"/>
+      <c r="B53" s="87"/>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
       <c r="E53" s="13"/>
@@ -9584,12 +9605,12 @@
       <c r="G53" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="I53" s="96" t="s">
+      <c r="I53" s="101" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="54" spans="2:9" ht="19">
-      <c r="B54" s="102"/>
+      <c r="B54" s="87"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
       <c r="E54" s="13"/>
@@ -9599,10 +9620,10 @@
       <c r="G54" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="I54" s="94"/>
+      <c r="I54" s="99"/>
     </row>
     <row r="55" spans="2:9" ht="19">
-      <c r="B55" s="102"/>
+      <c r="B55" s="87"/>
       <c r="C55" s="13"/>
       <c r="D55" s="13"/>
       <c r="E55" s="13"/>
@@ -9612,10 +9633,10 @@
       <c r="G55" s="51" t="s">
         <v>199</v>
       </c>
-      <c r="I55" s="94"/>
+      <c r="I55" s="99"/>
     </row>
     <row r="56" spans="2:9" ht="19">
-      <c r="B56" s="102"/>
+      <c r="B56" s="87"/>
       <c r="C56" s="13"/>
       <c r="D56" s="13"/>
       <c r="E56" s="13"/>
@@ -9625,10 +9646,10 @@
       <c r="G56" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="I56" s="94"/>
+      <c r="I56" s="99"/>
     </row>
     <row r="57" spans="2:9" ht="19">
-      <c r="B57" s="102"/>
+      <c r="B57" s="87"/>
       <c r="C57" s="13"/>
       <c r="D57" s="13"/>
       <c r="E57" s="13"/>
@@ -9638,10 +9659,10 @@
       <c r="G57" s="51" t="s">
         <v>201</v>
       </c>
-      <c r="I57" s="94"/>
+      <c r="I57" s="99"/>
     </row>
     <row r="58" spans="2:9" ht="38">
-      <c r="B58" s="102"/>
+      <c r="B58" s="87"/>
       <c r="C58" s="13"/>
       <c r="D58" s="13"/>
       <c r="E58" s="13"/>
@@ -9651,10 +9672,10 @@
       <c r="G58" s="51" t="s">
         <v>202</v>
       </c>
-      <c r="I58" s="94"/>
+      <c r="I58" s="99"/>
     </row>
     <row r="59" spans="2:9" ht="20" thickBot="1">
-      <c r="B59" s="102"/>
+      <c r="B59" s="87"/>
       <c r="C59" s="13"/>
       <c r="D59" s="13"/>
       <c r="E59" s="13"/>
@@ -9664,10 +9685,10 @@
       <c r="G59" s="51" t="s">
         <v>203</v>
       </c>
-      <c r="I59" s="97"/>
+      <c r="I59" s="102"/>
     </row>
     <row r="60" spans="2:9" ht="19">
-      <c r="B60" s="102"/>
+      <c r="B60" s="87"/>
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
       <c r="E60" s="13"/>
@@ -9677,12 +9698,12 @@
       <c r="G60" s="51" t="s">
         <v>204</v>
       </c>
-      <c r="I60" s="96" t="s">
+      <c r="I60" s="101" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="61" spans="2:9" ht="20" thickBot="1">
-      <c r="B61" s="102"/>
+      <c r="B61" s="87"/>
       <c r="C61" s="13"/>
       <c r="D61" s="13"/>
       <c r="E61" s="13"/>
@@ -9692,10 +9713,10 @@
       <c r="G61" s="51" t="s">
         <v>205</v>
       </c>
-      <c r="I61" s="94"/>
+      <c r="I61" s="99"/>
     </row>
     <row r="62" spans="2:9" ht="20" thickBot="1">
-      <c r="B62" s="102"/>
+      <c r="B62" s="87"/>
       <c r="C62" s="13"/>
       <c r="D62" s="13"/>
       <c r="E62" s="13"/>
@@ -9710,8 +9731,8 @@
       </c>
     </row>
     <row r="63" spans="2:9" ht="19" customHeight="1">
-      <c r="B63" s="102"/>
-      <c r="C63" s="89" t="s">
+      <c r="B63" s="87"/>
+      <c r="C63" s="83" t="s">
         <v>152</v>
       </c>
       <c r="D63" s="13" t="s">
@@ -9720,41 +9741,41 @@
       <c r="E63" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="F63" s="82" t="s">
+      <c r="F63" s="89" t="s">
         <v>197</v>
       </c>
-      <c r="G63" s="85" t="s">
+      <c r="G63" s="92" t="s">
         <v>196</v>
       </c>
-      <c r="I63" s="96" t="s">
+      <c r="I63" s="101" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="64" spans="2:9" ht="19" customHeight="1">
-      <c r="B64" s="102"/>
-      <c r="C64" s="89"/>
+      <c r="B64" s="87"/>
+      <c r="C64" s="83"/>
       <c r="D64" s="13" t="s">
         <v>154</v>
       </c>
       <c r="E64" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="F64" s="83"/>
-      <c r="G64" s="86"/>
-      <c r="I64" s="94"/>
+      <c r="F64" s="90"/>
+      <c r="G64" s="93"/>
+      <c r="I64" s="99"/>
     </row>
     <row r="65" spans="2:9" ht="19" customHeight="1" thickBot="1">
-      <c r="B65" s="103"/>
-      <c r="C65" s="100"/>
+      <c r="B65" s="88"/>
+      <c r="C65" s="84"/>
       <c r="D65" s="48" t="s">
         <v>161</v>
       </c>
       <c r="E65" s="48" t="s">
         <v>156</v>
       </c>
-      <c r="F65" s="84"/>
-      <c r="G65" s="87"/>
-      <c r="I65" s="97"/>
+      <c r="F65" s="91"/>
+      <c r="G65" s="94"/>
+      <c r="I65" s="102"/>
     </row>
     <row r="67" spans="2:9">
       <c r="E67" s="1" t="s">
@@ -9766,6 +9787,22 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="F63:F65"/>
+    <mergeCell ref="G63:G65"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="I44:I46"/>
+    <mergeCell ref="I53:I59"/>
+    <mergeCell ref="I60:I61"/>
+    <mergeCell ref="I63:I65"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="B42:B65"/>
+    <mergeCell ref="C22:C28"/>
+    <mergeCell ref="B22:B30"/>
+    <mergeCell ref="B31:B41"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="C37:C39"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="C42:C49"/>
@@ -9775,22 +9812,6 @@
     <mergeCell ref="C16:C18"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="B16:B20"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="B42:B65"/>
-    <mergeCell ref="C22:C28"/>
-    <mergeCell ref="B22:B30"/>
-    <mergeCell ref="B31:B41"/>
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="F63:F65"/>
-    <mergeCell ref="G63:G65"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="I44:I46"/>
-    <mergeCell ref="I53:I59"/>
-    <mergeCell ref="I60:I61"/>
-    <mergeCell ref="I63:I65"/>
-    <mergeCell ref="G16:G18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/dict/dict 코드북 260430.xlsx
+++ b/datasets/dict/dict 코드북 260430.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA052DC-52BD-FE4A-BC56-D7F57ED7A030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB6F863-494A-0748-9149-A9B57C0E0988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" xr2:uid="{F4A985C0-B43D-2244-AB7C-DBFAE8B9580A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="543">
   <si>
     <t>e_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -99,10 +99,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>e_comp_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>is_required</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -139,10 +135,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>y/n</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>pattern</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -211,17 +203,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>불연속 패턴을 정책적으로 허용할지 명시.
-disconti_allowed=n이면 gap 후보 생성 금지(sheet2 gap이 있어도 무시)
-disconti_allowed=y이면 sheet2 gap 적용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>verify_ruleset_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">정규형. 리포팅/디버깅 표준명으로 사용함. LLM질문 시에도 명확한 명칭을 정규형으로 LLM에게 전달함.  </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -700,15 +682,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>필수성분의 ID를 부여함. 복수개이면 다음 순서로 부여함: c1;c2;c3;....</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>다음 수식으로 자동 생성함: "=rs_" &amp; e_id &amp; "_d01"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>polyset_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4719,23 +4693,6 @@
 조사- pt001, 연결어미- ce001, 종결어미- fe001, 의존어 구성(연결표현)- dc001, 의존어 구성(종결표현)- df001, 선어말어미- pf001, 관형사형어미- ae001</t>
   </si>
   <si>
-    <t>문법항목의 모든 구성 성분에 ID 부여. 이 ID로 sheet2와 매칭될 예정임.
-복수개이면 다음 순서로 부여함: c1;c2;c3;.... 
-e_comp_id(예: c1;c2;c3)를 파싱해서 성분 수를 계산하고, 그 값이 1이면 disconti 후보 생성 로직을 스킵함.
-성분 수1개에 대해 sheet2 row count가 1이어야 하며 2이상이면 error출력함.</t>
-  </si>
-  <si>
-    <t>문법항목 고유 ID. sheet1과 매치하기 위한 용도임.</t>
-  </si>
-  <si>
-    <t>구성성분이 필수성분인지 혹은 선택적으로 나타나는 성분인지 기록 
-y- 구성성분이 필수 성분임. 문법항목으로 사용되기 위해 정말! 100% 나타나야만 할 때 표기. recall을 높이기 위해 사용할 예정임.
-n- 구성성분이 선택적으로 나타나는 성분임.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">문법항목 성분의 일반적인 발현 순서. 한국어는 문장 순서 변형이 자유로우므로 사용 시에는 최소한의 조건으로 다루어야 함. </t>
-  </si>
-  <si>
     <t>→ 즉 “아무 문법항목에나 special을 다 때려 넣는 구조”가 아니라, 사전의 comp_surf 옵션 자체가 힌트로 작동한다.</t>
   </si>
   <si>
@@ -4787,14 +4744,6 @@
     <t>5) 팀 운영 가이드: 신규 문법항목 추가 절차(실무용)</t>
   </si>
   <si>
-    <t xml:space="preserve">다의의미 처리를 위한 항목으로 b그룹은 반드시 polyset_id를 부여함 
-(a그룹은 polyset_id를 부여하지 않음)
-다의어의 경우, 
-예) 다의어 까지1(범위의 끝 지점이나 한계를 나타낸다), 까지2(현재의 상태나 정도에서 더해지거나 더 나아감을 나타낸다), 까지3(정상적인 정도를 지나침을 나타낸다)의 경우, ps_kkaji를 기입하여 묶음.
-a그룹은 빈칸으로 두기. </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>c</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4815,33 +4764,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sheet2 rule_components</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>문법항목 구성요소의 규칙을 설정함.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sheet1 "e_comp_id"의 문법항목 구성성분 중 순서대로 표기함. c1, c2,...</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>규칙 탐색 우선순위.
-0으로 처리할 경우 앵커를 사용하지 마라는 신호임.
-필수 성분(is_required=y) 우선으로 설정하여 후보 폭발을 막아야 함. 
-가장 희소하고, 오탐이 적고, 패턴을 잘 대표하는 성분”을 1순위 앵커로 둠.
-“콘텐츠 단어(명사/동사 어근)” &gt; 조사/어미(“을/를/에/에서/하다”)
-표면 변형이 적은 것 우선(후보가 난잡해질 수 있음)
-오탐(FP) 유발 가능성이 낮은 것 우선.
-불연속에서 ‘멀리 떨어져도’ 비교적 안정적인 성분 우선</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>대부분 문법항목은 anchor_rank=1만 있어도 충분함.
-필요하면 2개 앵커까지 허용 가능.
-anchor_rank=1 (주 앵커)
-anchor_rank=2 (보조 앵커)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4852,14 +4775,6 @@
   </si>
   <si>
     <t>sheet3 detect_rules</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">규칙 묶음. 문맥 규칙/검증 규칙 등을 세트로 관리. rs_(e_id)_d/v01,rs_(e_id)_d/v02,... </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">규칙 묶음 내에서 순서 설정. 규칙 고유 ID. r_(e_id)_d/v01,r_(e_id)_d/v02,... </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4872,17 +4787,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>stage 범주등: detect, verify
-detect- 후보를 “만든다”(Recall 우선)
-목적: 놓치지 않기(FN 감소)
-행동: 가능한 매칭을 넓게 잡아서 CandidateSpan들을 생성
-verify- hard fail인 경우 후보를 제거함. (Precision 회복)
-목적: detect에서 생긴 FP 제거
-행동: 강한 금지 규칙(hard_fail=true)로 후보를 폐기(discard)
-lemma/POS/조사·어미 제약, 최소한의 문법적 조건 등으로 확실한 경우에만 hard fail을 제거함</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>인접한 성분 간 gap 허용치의 최소값. 해당 성분과 다음 성분 사이 gap.
 참고로 우리 코딩에는 'min_gap_to_next', 'max_gap_to_next' 외에도 문법항목 구성 요소를 찾는 범위가 하나 더 있음. 아래와 같음.
 1. detect 정규식 match 발생
@@ -4907,10 +4811,6 @@
   </si>
   <si>
     <t>bridge_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>문법요소 중 'ㄴ/은'에는 adnominal_n. 주의: 'ㄴ/은/는'은 안 됨.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4950,6 +4850,168 @@
 선택된 component 바로 왼쪽 1글자 + component_text.  다만 왼쪽이 공백이면 공백을 건너뛰고 의미문자를 찾음.
 예: 가운데 → 가+운데=가운데, 가는데 → 가+는데=가는데
 용도: 가운데/그런데처럼 왼쪽 1글자와 component를 합쳐야 정확히 구별되는 오탐 hard fail.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ps_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">규칙 검색과 인코더 입력에 사용하는 unit id.
+a,b,c그룹 모두 부여해야 한다. 
+c그룹 같이 다의의미가 있는 경우 가장 처음 다의의미의 e_id로 ps_id를 정한다. 
+예로, ce002,ce003이 폴리셋으로 묶인다면 ps_ce002로 이름을 정한다.
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">items시트와 연결할 때 쓰인다. items시트의 'ps_id'와 연결한다.. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>primary_e_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a, b그룹이면 단독 폴리셋이므로 해당 e_id를 기록한다.
+c그룹이면 폴리셋을 구성하는 복수의 e_id중 오름차순 가장 첫 e_id를 적는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>member_e_ids</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폴리셋을 구성하는 문법항목 e_id를 기록한다. 
+a, b그룹은 한 개이고 c그룹은 복수개이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">브릿지 종류:
+adnominal_n: 문법항목 구성요소 중 'ㄴ/은'에 사용한다. 주의: 'ㄴ/은/는'은 안 됨.
+nde: ps_ce002(ㄴ/은/는데) 전용 브릿지임.
+thing
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적용되는 bridge id를 기록한다.
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sheet2 polysets</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ps_canonical_form</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폴리셋의 공통 canonical form을 기록한다. 
+a,b그룹은 items시트의 canonical_form과 같음 
+c그룹의 경우에는 items시트의 canonical_form에서 마지막 순번 숫자를 제거함.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a,b그룹은 정규형을 기록한다. 
+c그룹은 정규형과 의미순번을 더한다. 
+예: ㄴ/은/는데1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>불연속 패턴을 정책적으로 허용할지 명시.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ps_comp_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">문법항목의 모든 구성 성분에 ID 부여. 이 ID로 구성성분이 필요할 경우 매칭될 예정임.
+복수개이면 다음 순서로 부여함: c1;c2;c3;.... </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gloss_intro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인코더 훈련 입력의 text_b에 쓰이는 부분임. 
+예) text_b: "다음 의미를 포함하는 연결어미": glos1;gloss2
+의 "다음 의미를 포함하는 연결어미:" 부분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sheet3 rule_components</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comp_surf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>polysets시트의 ps_canonical_form와 같은 값(형식)을 기록한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>items시트와 연결할 때 쓰인다. items시트의 'ps_id'와 연결한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">문법 항목의 각 구성성분을 기록한다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구성성분이 필수성분인지 혹은 선택적으로 나타나는 성분인지 기록 
+y- 구성성분이 필수 성분임.
+n- 구성성분이 선택적으로 나타나는 성분임.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>규칙 탐색 우선순위.
+숫자가 작을수록 중요한 앵커로 처리함.
+숫자는 0부터 정수로 입력 가능.
+필수 성분(is_required=y) 우선으로 설정하여 후보 폭발을 막아야 함. 
+가장 희소하고, 오탐이 적고, 패턴을 잘 대표하는 성분”을 1순위 앵커로 둠.
+“콘텐츠 단어(명사/동사 어근)” &gt; 조사/어미(“을/를/에/에서/하다”)
+표면 변형이 적은 것 우선(후보가 난잡해질 수 있음)
+오탐(FP) 유발 가능성이 낮은 것 우선.
+불연속에서 ‘멀리 떨어져도’ 비교적 안정적인 성분 우선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대부분 문법항목은 anchor_rank=0만 있어도 충분함.
+필요하면 2개 앵커까지 허용 가능.
+anchor_rank=0 (주 앵커)
+anchor_rank=1 (보조 앵커)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문법항목 성분의 일반적인 발현 순서. 한국어는 문장 순서 변형이 자유로우므로 사용 시에는 최소한의 조건으로 다루어야 함. 
+1부터 시작하는 정수를 입력함.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">규칙 묶음. 문맥 규칙/검증 규칙 등을 세트로 관리. rs_ps_(e_id)_d/v01,rs_ps_(e_id)_d/v02,... </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">규칙 묶음 내에서 순서 설정. 규칙 고유 ID. r_ps_(e_id)_d/v01,r_ps_(e_id)_d/v02,... </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage 범주: detect, verify
+detect- 후보를 “만든다”
+목적: 놓치지 않기(recall1 달성)
+verify- hard fail인 경우 후보를 제거함. (Precision 회복)
+목적: detect에서 생긴 FP 제거
+행동: 강한 금지 규칙(hard_fail=true)로 후보를 폐기(discard)
+최소한의 형태적 조건 등으로 확실한 경우에만 hard fail을 제거함</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5058,7 +5120,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5101,6 +5163,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="35">
     <border>
@@ -5572,7 +5640,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5819,73 +5887,79 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6222,7 +6296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E809B31-950A-8043-B762-4F555FA10734}">
-  <dimension ref="A1:AX65"/>
+  <dimension ref="A1:AX77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="2" customWidth="1"/>
@@ -6238,19 +6312,19 @@
   <sheetData>
     <row r="1" spans="1:50" s="4" customFormat="1" ht="38">
       <c r="A1" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>8</v>
@@ -6259,7 +6333,7 @@
         <v>9</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I1" s="8"/>
     </row>
@@ -6320,7 +6394,7 @@
     <row r="3" spans="1:50" ht="40" customHeight="1" thickBot="1">
       <c r="A3" s="26"/>
       <c r="B3" s="67" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="C3" s="27"/>
       <c r="D3" s="27"/>
@@ -6335,14 +6409,14 @@
         <v>0</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
       <c r="F4" s="24"/>
       <c r="G4" s="25"/>
       <c r="H4" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:50" ht="84" customHeight="1">
@@ -6351,7 +6425,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>44</v>
+        <v>524</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -6365,7 +6439,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="72" t="s">
-        <v>522</v>
+        <v>504</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>6</v>
@@ -6392,20 +6466,20 @@
       <c r="B8" s="78"/>
       <c r="C8" s="74"/>
       <c r="D8" s="13" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="11"/>
       <c r="G8" s="38"/>
       <c r="H8" s="9"/>
     </row>
-    <row r="9" spans="1:50" ht="165" customHeight="1">
+    <row r="9" spans="1:50" ht="95">
       <c r="A9" s="9"/>
       <c r="B9" s="37" t="s">
-        <v>184</v>
+        <v>512</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
@@ -6416,7 +6490,7 @@
     <row r="10" spans="1:50" ht="67" customHeight="1">
       <c r="A10" s="9"/>
       <c r="B10" s="37" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="13"/>
@@ -6428,7 +6502,7 @@
     <row r="11" spans="1:50" ht="67" customHeight="1">
       <c r="A11" s="9"/>
       <c r="B11" s="37" t="s">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="13"/>
@@ -6437,34 +6511,34 @@
       <c r="G11" s="38"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:50" ht="57">
+    <row r="12" spans="1:50" ht="19">
       <c r="A12" s="9"/>
       <c r="B12" s="12" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>42</v>
+        <v>495</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="11" t="s">
-        <v>24</v>
+        <v>178</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:50" ht="108" customHeight="1">
+    <row r="13" spans="1:50" ht="19">
       <c r="A13" s="9"/>
       <c r="B13" s="12" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="11" t="s">
-        <v>182</v>
+        <v>42</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="9"/>
@@ -6472,42 +6546,36 @@
     <row r="14" spans="1:50" ht="19">
       <c r="A14" s="9"/>
       <c r="B14" s="12" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
-      <c r="F14" s="11" t="s">
-        <v>183</v>
-      </c>
+      <c r="F14" s="11"/>
       <c r="G14" s="10"/>
       <c r="H14" s="9"/>
     </row>
-    <row r="15" spans="1:50" ht="19">
+    <row r="15" spans="1:50" ht="41" customHeight="1">
       <c r="A15" s="9"/>
-      <c r="B15" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>507</v>
-      </c>
+      <c r="B15" s="106" t="s">
+        <v>521</v>
+      </c>
+      <c r="C15" s="9"/>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
-      <c r="F15" s="11" t="s">
-        <v>46</v>
-      </c>
+      <c r="F15" s="11"/>
       <c r="G15" s="10"/>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="1:50" ht="19">
+    <row r="16" spans="1:50">
       <c r="A16" s="9"/>
-      <c r="B16" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>508</v>
+      <c r="B16" s="105" t="s">
+        <v>512</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>514</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
@@ -6515,13 +6583,13 @@
       <c r="G16" s="10"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="17" spans="1:8" ht="40" customHeight="1">
+    <row r="17" spans="1:8" ht="38">
       <c r="A17" s="9"/>
-      <c r="B17" s="66" t="s">
-        <v>509</v>
+      <c r="B17" s="105" t="s">
+        <v>515</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
@@ -6529,13 +6597,13 @@
       <c r="G17" s="10"/>
       <c r="H17" s="9"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" ht="38">
       <c r="A18" s="9"/>
-      <c r="B18" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="34" t="s">
-        <v>483</v>
+      <c r="B18" s="105" t="s">
+        <v>517</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>518</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
@@ -6543,26 +6611,24 @@
       <c r="G18" s="10"/>
       <c r="H18" s="9"/>
     </row>
-    <row r="19" spans="1:8" ht="19">
+    <row r="19" spans="1:8" ht="57">
       <c r="A19" s="9"/>
-      <c r="B19" s="14" t="s">
-        <v>12</v>
+      <c r="B19" s="105" t="s">
+        <v>522</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
-      <c r="F19" s="11" t="s">
-        <v>27</v>
-      </c>
+      <c r="F19" s="11"/>
       <c r="G19" s="10"/>
       <c r="H19" s="9"/>
     </row>
     <row r="20" spans="1:8" ht="19">
       <c r="A20" s="9"/>
-      <c r="B20" s="14" t="s">
-        <v>524</v>
+      <c r="B20" s="105" t="s">
+        <v>22</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>525</v>
@@ -6573,57 +6639,55 @@
       <c r="G20" s="10"/>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="1:8" ht="40" customHeight="1">
+    <row r="21" spans="1:8" ht="38">
       <c r="A21" s="9"/>
-      <c r="B21" s="75" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="79" t="s">
-        <v>484</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>2</v>
-      </c>
+      <c r="B21" s="105" t="s">
+        <v>526</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="D21" s="13"/>
       <c r="E21" s="13"/>
       <c r="F21" s="11"/>
       <c r="G21" s="10"/>
       <c r="H21" s="9"/>
     </row>
-    <row r="22" spans="1:8" ht="40" customHeight="1">
+    <row r="22" spans="1:8" ht="19">
       <c r="A22" s="9"/>
-      <c r="B22" s="75"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="13" t="s">
-        <v>3</v>
-      </c>
+      <c r="B22" s="105" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="D22" s="13"/>
       <c r="E22" s="13"/>
       <c r="F22" s="11"/>
       <c r="G22" s="10"/>
       <c r="H22" s="9"/>
     </row>
-    <row r="23" spans="1:8" ht="178" customHeight="1">
+    <row r="23" spans="1:8" ht="19">
       <c r="A23" s="9"/>
-      <c r="B23" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>512</v>
+      <c r="B23" s="105" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>496</v>
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
       <c r="F23" s="11"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="9" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="38">
+      <c r="H23" s="9"/>
+    </row>
+    <row r="24" spans="1:8" ht="57">
       <c r="A24" s="9"/>
-      <c r="B24" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>485</v>
+      <c r="B24" s="105" t="s">
+        <v>528</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>530</v>
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
@@ -6631,61 +6695,44 @@
       <c r="G24" s="10"/>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="1:8" ht="76">
+    <row r="25" spans="1:8">
       <c r="A25" s="9"/>
-      <c r="B25" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>514</v>
-      </c>
+      <c r="B25" s="105" t="s">
+        <v>529</v>
+      </c>
+      <c r="C25" s="9"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
-      <c r="F25" s="11" t="s">
-        <v>47</v>
-      </c>
+      <c r="F25" s="11"/>
       <c r="G25" s="10"/>
       <c r="H25" s="9"/>
     </row>
-    <row r="26" spans="1:8" ht="199" customHeight="1">
+    <row r="26" spans="1:8">
       <c r="A26" s="9"/>
-      <c r="B26" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>520</v>
-      </c>
+      <c r="B26" s="105"/>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
-      <c r="F26" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="F26" s="11"/>
       <c r="G26" s="10"/>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8" ht="60" customHeight="1">
+    <row r="27" spans="1:8">
       <c r="A27" s="9"/>
-      <c r="B27" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="B27" s="105"/>
+      <c r="C27" s="9"/>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
-      <c r="F27" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="F27" s="11"/>
       <c r="G27" s="10"/>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" spans="1:8" ht="145" customHeight="1">
+    <row r="28" spans="1:8" ht="40" customHeight="1">
       <c r="A28" s="9"/>
-      <c r="B28" s="65" t="s">
-        <v>515</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>518</v>
+      <c r="B28" s="66" t="s">
+        <v>531</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>498</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
@@ -6695,11 +6742,11 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="9"/>
-      <c r="B29" s="17" t="s">
-        <v>0</v>
+      <c r="B29" s="14" t="s">
+        <v>512</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>483</v>
+        <v>534</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
@@ -6707,27 +6754,29 @@
       <c r="G29" s="10"/>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" ht="19">
       <c r="A30" s="9"/>
-      <c r="B30" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="34" t="s">
-        <v>516</v>
+      <c r="B30" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>533</v>
       </c>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
-      <c r="F30" s="11"/>
+      <c r="F30" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="G30" s="10"/>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" ht="19">
       <c r="A31" s="9"/>
-      <c r="B31" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" s="34" t="s">
-        <v>517</v>
+      <c r="B31" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>535</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
@@ -6735,127 +6784,136 @@
       <c r="G31" s="10"/>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8" ht="183" customHeight="1">
+    <row r="32" spans="1:8" ht="114">
       <c r="A32" s="9"/>
-      <c r="B32" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" s="64" t="s">
-        <v>519</v>
+      <c r="B32" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>520</v>
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
-      <c r="F32" s="11"/>
+      <c r="F32" s="11" t="s">
+        <v>519</v>
+      </c>
       <c r="G32" s="10"/>
       <c r="H32" s="9"/>
     </row>
-    <row r="33" spans="1:8" ht="352" customHeight="1">
+    <row r="33" spans="1:8" ht="40" customHeight="1">
       <c r="A33" s="9"/>
-      <c r="B33" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="68" t="s">
-        <v>529</v>
-      </c>
-      <c r="D33" s="13"/>
+      <c r="B33" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="79" t="s">
+        <v>536</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>2</v>
+      </c>
       <c r="E33" s="13"/>
-      <c r="F33" s="11" t="s">
-        <v>530</v>
-      </c>
+      <c r="F33" s="11"/>
       <c r="G33" s="10"/>
       <c r="H33" s="9"/>
     </row>
-    <row r="34" spans="1:8" ht="57">
+    <row r="34" spans="1:8" ht="40" customHeight="1">
       <c r="A34" s="9"/>
-      <c r="B34" s="17" t="s">
-        <v>526</v>
-      </c>
-      <c r="C34" s="68" t="s">
-        <v>527</v>
-      </c>
-      <c r="D34" s="13"/>
+      <c r="B34" s="75"/>
+      <c r="C34" s="79"/>
+      <c r="D34" s="13" t="s">
+        <v>3</v>
+      </c>
       <c r="E34" s="13"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
       <c r="H34" s="9"/>
     </row>
-    <row r="35" spans="1:8" ht="108" customHeight="1">
+    <row r="35" spans="1:8" ht="178" customHeight="1">
       <c r="A35" s="9"/>
-      <c r="B35" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>521</v>
+      <c r="B35" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>537</v>
       </c>
       <c r="D35" s="13"/>
-      <c r="E35" s="13" t="s">
-        <v>30</v>
-      </c>
+      <c r="E35" s="13"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8" ht="19">
+      <c r="H35" s="9" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="57">
       <c r="A36" s="9"/>
-      <c r="B36" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>181</v>
+      <c r="B36" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>539</v>
       </c>
       <c r="D36" s="13"/>
-      <c r="E36" s="13" t="s">
-        <v>33</v>
-      </c>
+      <c r="E36" s="13"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
       <c r="H36" s="9"/>
     </row>
-    <row r="37" spans="1:8" ht="19">
+    <row r="37" spans="1:8" ht="76">
       <c r="A37" s="9"/>
-      <c r="B37" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>36</v>
+      <c r="B37" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>499</v>
       </c>
       <c r="D37" s="13"/>
-      <c r="E37" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F37" s="11"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="11" t="s">
+        <v>43</v>
+      </c>
       <c r="G37" s="10"/>
       <c r="H37" s="9"/>
     </row>
-    <row r="38" spans="1:8" ht="19">
+    <row r="38" spans="1:8" ht="199" customHeight="1">
       <c r="A38" s="9"/>
-      <c r="B38" s="17" t="s">
-        <v>528</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>37</v>
+      <c r="B38" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>502</v>
       </c>
       <c r="D38" s="13"/>
-      <c r="E38" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F38" s="11"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="G38" s="10"/>
       <c r="H38" s="9"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" ht="60" customHeight="1">
       <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
+      <c r="B39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>44</v>
+      </c>
       <c r="D39" s="13"/>
       <c r="E39" s="13"/>
-      <c r="F39" s="11"/>
+      <c r="F39" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="G39" s="10"/>
       <c r="H39" s="9"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" ht="145" customHeight="1">
       <c r="A40" s="9"/>
-      <c r="B40" s="16"/>
-      <c r="C40" s="9"/>
+      <c r="B40" s="65" t="s">
+        <v>500</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>501</v>
+      </c>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
       <c r="F40" s="11"/>
@@ -6864,8 +6922,12 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="9"/>
-      <c r="B41" s="16"/>
-      <c r="C41" s="9"/>
+      <c r="B41" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>534</v>
+      </c>
       <c r="D41" s="13"/>
       <c r="E41" s="13"/>
       <c r="F41" s="11"/>
@@ -6874,8 +6936,12 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="9"/>
-      <c r="B42" s="16"/>
-      <c r="C42" s="9"/>
+      <c r="B42" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" s="34" t="s">
+        <v>540</v>
+      </c>
       <c r="D42" s="13"/>
       <c r="E42" s="13"/>
       <c r="F42" s="11"/>
@@ -6884,88 +6950,129 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="9"/>
-      <c r="B43" s="16"/>
-      <c r="C43" s="9"/>
+      <c r="B43" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="34" t="s">
+        <v>541</v>
+      </c>
       <c r="D43" s="13"/>
       <c r="E43" s="13"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
       <c r="H43" s="9"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" ht="144">
       <c r="A44" s="9"/>
-      <c r="B44" s="16"/>
-      <c r="C44" s="9"/>
+      <c r="B44" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" s="64" t="s">
+        <v>542</v>
+      </c>
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
       <c r="H44" s="9"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" ht="323">
       <c r="A45" s="9"/>
-      <c r="B45" s="16"/>
-      <c r="C45" s="9"/>
+      <c r="B45" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" s="68" t="s">
+        <v>510</v>
+      </c>
       <c r="D45" s="13"/>
       <c r="E45" s="13"/>
-      <c r="F45" s="11"/>
+      <c r="F45" s="11" t="s">
+        <v>511</v>
+      </c>
       <c r="G45" s="10"/>
       <c r="H45" s="9"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" ht="57">
       <c r="A46" s="9"/>
-      <c r="B46" s="16"/>
-      <c r="C46" s="9"/>
+      <c r="B46" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="C46" s="68" t="s">
+        <v>508</v>
+      </c>
       <c r="D46" s="13"/>
       <c r="E46" s="13"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
       <c r="H46" s="9"/>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" ht="108" customHeight="1">
       <c r="A47" s="9"/>
-      <c r="B47" s="16"/>
-      <c r="C47" s="9"/>
+      <c r="B47" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>503</v>
+      </c>
       <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
+      <c r="E47" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
       <c r="H47" s="9"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" ht="19">
       <c r="A48" s="9"/>
-      <c r="B48" s="16"/>
-      <c r="C48" s="9"/>
+      <c r="B48" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>177</v>
+      </c>
       <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
+      <c r="E48" s="13" t="s">
+        <v>31</v>
+      </c>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
       <c r="H48" s="9"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" ht="19">
       <c r="A49" s="9"/>
-      <c r="B49" s="16"/>
-      <c r="C49" s="9"/>
+      <c r="B49" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>34</v>
+      </c>
       <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
+      <c r="E49" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
       <c r="H49" s="9"/>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" ht="19">
       <c r="A50" s="9"/>
-      <c r="B50" s="16"/>
-      <c r="C50" s="9"/>
+      <c r="B50" s="17" t="s">
+        <v>509</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>35</v>
+      </c>
       <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
+      <c r="E50" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
       <c r="H50" s="9"/>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="9"/>
-      <c r="B51" s="16"/>
-      <c r="C51" s="9"/>
+      <c r="B51" s="9"/>
       <c r="D51" s="13"/>
       <c r="E51" s="13"/>
       <c r="F51" s="11"/>
@@ -7112,13 +7219,133 @@
       <c r="G65" s="10"/>
       <c r="H65" s="9"/>
     </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="9"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="9"/>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="9"/>
+      <c r="B67" s="16"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="9"/>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="9"/>
+      <c r="B68" s="16"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="10"/>
+      <c r="H68" s="9"/>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="9"/>
+      <c r="B69" s="16"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="10"/>
+      <c r="H69" s="9"/>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="9"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="10"/>
+      <c r="H70" s="9"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="9"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="10"/>
+      <c r="H71" s="9"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="9"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="10"/>
+      <c r="H72" s="9"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="9"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="13"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="10"/>
+      <c r="H73" s="9"/>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="9"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="10"/>
+      <c r="H74" s="9"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="9"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="10"/>
+      <c r="H75" s="9"/>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="9"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="13"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="10"/>
+      <c r="H76" s="9"/>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="9"/>
+      <c r="B77" s="16"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="10"/>
+      <c r="H77" s="9"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="C6:C8"/>
-    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B33:B34"/>
     <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="C33:C34"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7136,7 +7363,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B1">
         <v>260222</v>
@@ -7144,207 +7371,207 @@
     </row>
     <row r="2" spans="1:2">
       <c r="B2" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="27">
       <c r="B6" s="31" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" s="33" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" s="5" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="B12" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="33" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="27">
       <c r="B26" s="31" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="20">
       <c r="B28" s="32" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="5" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" s="5" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="5" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" s="33" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" s="5" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" s="33" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" s="33" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" s="5" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="72" spans="2:2">
       <c r="B72" s="33" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" s="33" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" s="33" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="82" spans="2:2">
       <c r="B82" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="84" spans="2:2">
       <c r="B84" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="88" spans="2:2" ht="20">
       <c r="B88" s="32" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
     </row>
     <row r="89" spans="2:2" ht="20">
@@ -7352,532 +7579,532 @@
     </row>
     <row r="90" spans="2:2">
       <c r="B90" s="5" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
     <row r="92" spans="2:2">
       <c r="B92" s="33" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
     <row r="94" spans="2:2">
       <c r="B94" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="95" spans="2:2">
       <c r="B95" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" s="5" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="101" spans="2:2">
       <c r="B101" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" s="5" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" s="33" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" s="33" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="119" spans="2:2">
       <c r="B119" s="33" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" s="5" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" s="33" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="127" spans="2:2">
       <c r="B127" s="33" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" spans="2:2">
       <c r="B129" s="33" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="131" spans="2:2">
       <c r="B131" s="5" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="2:2">
       <c r="B133" s="33" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="135" spans="2:2">
       <c r="B135" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="137" spans="2:2">
       <c r="B137" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="141" spans="2:2" ht="20">
       <c r="B141" s="32" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="143" spans="2:2">
       <c r="B143" s="5" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="145" spans="2:2">
       <c r="B145" s="33" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="147" spans="2:2">
       <c r="B147" s="5" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="149" spans="2:2">
       <c r="B149" s="33" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="151" spans="2:2">
       <c r="B151" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="153" spans="2:2">
       <c r="B153" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="155" spans="2:2">
       <c r="B155" s="5" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="157" spans="2:2">
       <c r="B157" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="159" spans="2:2">
       <c r="B159" s="33" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="160" spans="2:2">
       <c r="B160" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="162" spans="2:2">
       <c r="B162" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="164" spans="2:2">
       <c r="B164" s="33" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="165" spans="2:2">
       <c r="B165" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="167" spans="2:2">
       <c r="B167" s="33" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="169" spans="2:2">
       <c r="B169" s="5" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="171" spans="2:2">
       <c r="B171" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="173" spans="2:2">
       <c r="B173" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="177" spans="2:2" ht="20">
       <c r="B177" s="32" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="179" spans="2:2">
       <c r="B179" s="5" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="181" spans="2:2">
       <c r="B181" s="33" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
     <row r="183" spans="2:2">
       <c r="B183" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="185" spans="2:2">
       <c r="B185" s="5" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="187" spans="2:2">
       <c r="B187" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="189" spans="2:2">
       <c r="B189" s="33" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="191" spans="2:2">
       <c r="B191" s="33" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="33" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="33" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="199" spans="2:2">
       <c r="B199" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="201" spans="2:2">
       <c r="B201" s="5" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="203" spans="2:2">
       <c r="B203" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="205" spans="2:2">
       <c r="B205" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="207" spans="2:2">
       <c r="B207" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="211" spans="2:2" ht="27">
       <c r="B211" s="31" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="213" spans="2:2" ht="20">
       <c r="B213" s="32" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="215" spans="2:2">
       <c r="B215" s="5" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="217" spans="2:2">
       <c r="B217" s="5" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="219" spans="2:2">
       <c r="B219" s="5" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="221" spans="2:2">
       <c r="B221" s="5" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="223" spans="2:2">
       <c r="B223" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
     </row>
     <row r="225" spans="2:2" ht="20">
       <c r="B225" s="32" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="227" spans="2:2">
       <c r="B227" s="33" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="229" spans="2:2">
       <c r="B229" s="33" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="231" spans="2:2">
       <c r="B231" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="233" spans="2:2" ht="20">
       <c r="B233" s="32" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="235" spans="2:2">
       <c r="B235" s="33" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="237" spans="2:2">
       <c r="B237" s="33" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="239" spans="2:2">
       <c r="B239" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="241" spans="2:2">
       <c r="B241" s="33" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="243" spans="2:2">
       <c r="B243" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="245" spans="2:2" ht="20">
       <c r="B245" s="32" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="247" spans="2:2">
       <c r="B247" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="249" spans="2:2">
       <c r="B249" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="251" spans="2:2">
       <c r="B251" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="253" spans="2:2" ht="20">
       <c r="B253" s="32" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="255" spans="2:2">
       <c r="B255" s="33" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="257" spans="2:2">
       <c r="B257" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="259" spans="2:2" ht="20">
       <c r="B259" s="32" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="261" spans="2:2">
       <c r="B261" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="263" spans="2:2">
       <c r="B263" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="267" spans="2:2" ht="27">
       <c r="B267" s="31" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="269" spans="2:2">
       <c r="B269" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="271" spans="2:2">
       <c r="B271" s="33" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="273" spans="2:2">
       <c r="B273" s="33" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="279" spans="2:2">
       <c r="B279" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="281" spans="2:2">
       <c r="B281" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
     <row r="283" spans="2:2">
       <c r="B283" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="287" spans="2:2" ht="27">
       <c r="B287" s="31" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
     </row>
     <row r="289" spans="2:2">
       <c r="B289" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="291" spans="2:2">
       <c r="B291" s="5" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="293" spans="2:2">
       <c r="B293" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="295" spans="2:2">
       <c r="B295" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="300" spans="2:2">
       <c r="B300" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="302" spans="2:2">
       <c r="B302" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
     </row>
     <row r="304" spans="2:2">
       <c r="B304" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="305" spans="2:2">
       <c r="B305" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -7894,7 +8121,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B1">
         <v>260222</v>
@@ -7902,667 +8129,667 @@
     </row>
     <row r="2" spans="1:2">
       <c r="B2" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="27">
       <c r="B6" s="31" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" s="5" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="B12" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="27">
       <c r="B20" s="31" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="20">
       <c r="B22" s="32" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="5" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" s="33" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="30" spans="2:2" ht="20">
       <c r="B30" s="32" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
     </row>
     <row r="46" spans="2:2" ht="20">
       <c r="B46" s="32" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="5" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" s="5" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" s="5" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" s="5" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="69" spans="2:2" ht="20">
       <c r="B69" s="32" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
     <row r="81" spans="2:2" ht="20">
       <c r="B81" s="32" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
     </row>
     <row r="85" spans="2:2">
       <c r="B85" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
     </row>
     <row r="87" spans="2:2">
       <c r="B87" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="91" spans="2:2">
       <c r="B91" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
     </row>
     <row r="93" spans="2:2">
       <c r="B93" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="97" spans="2:2" ht="27">
       <c r="B97" s="31" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="101" spans="2:2" ht="20">
       <c r="B101" s="32" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="117" spans="2:2" ht="20">
       <c r="B117" s="32" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="119" spans="2:2">
       <c r="B119" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
     </row>
     <row r="127" spans="2:2">
       <c r="B127" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="129" spans="2:2" ht="20">
       <c r="B129" s="32" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="131" spans="2:2">
       <c r="B131" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="133" spans="2:2">
       <c r="B133" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="135" spans="2:2">
       <c r="B135" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
     </row>
     <row r="137" spans="2:2">
       <c r="B137" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="139" spans="2:2" ht="20">
       <c r="B139" s="32" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
     </row>
     <row r="141" spans="2:2">
       <c r="B141" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
     </row>
     <row r="143" spans="2:2">
       <c r="B143" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="2:2">
       <c r="B145" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="2:2" ht="27">
       <c r="B149" s="31" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="2:2" ht="20">
       <c r="B151" s="32" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="153" spans="2:2">
       <c r="B153" s="5" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="155" spans="2:2">
       <c r="B155" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="157" spans="2:2">
       <c r="B157" s="5" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="159" spans="2:2">
       <c r="B159" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="161" spans="2:2">
       <c r="B161" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
     </row>
     <row r="163" spans="2:2">
       <c r="B163" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="165" spans="2:2">
       <c r="B165" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
     </row>
     <row r="167" spans="2:2" ht="20">
       <c r="B167" s="32" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="169" spans="2:2">
       <c r="B169" s="5" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="171" spans="2:2">
       <c r="B171" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
     </row>
     <row r="173" spans="2:2">
       <c r="B173" s="5" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="175" spans="2:2">
       <c r="B175" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="177" spans="2:2">
       <c r="B177" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="179" spans="2:2">
       <c r="B179" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="180" spans="2:2">
       <c r="B180" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
     </row>
     <row r="182" spans="2:2">
       <c r="B182" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="184" spans="2:2">
       <c r="B184" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="186" spans="2:2" ht="20">
       <c r="B186" s="32" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="188" spans="2:2">
       <c r="B188" s="5" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="190" spans="2:2">
       <c r="B190" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="192" spans="2:2">
       <c r="B192" s="5" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="198" spans="2:2">
       <c r="B198" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="200" spans="2:2" ht="20">
       <c r="B200" s="32" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
     </row>
     <row r="202" spans="2:2">
       <c r="B202" s="5" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="204" spans="2:2">
       <c r="B204" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="206" spans="2:2">
       <c r="B206" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
     </row>
     <row r="208" spans="2:2">
       <c r="B208" s="5" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="210" spans="2:2">
       <c r="B210" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="212" spans="2:2">
       <c r="B212" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="213" spans="2:2">
       <c r="B213" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="215" spans="2:2">
       <c r="B215" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
     </row>
     <row r="219" spans="2:2" ht="27">
       <c r="B219" s="31" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
     </row>
     <row r="221" spans="2:2">
       <c r="B221" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
     </row>
     <row r="223" spans="2:2">
       <c r="B223" s="5" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
     </row>
     <row r="225" spans="2:2">
       <c r="B225" s="5" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="227" spans="2:2">
       <c r="B227" s="5" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
     </row>
     <row r="229" spans="2:2">
       <c r="B229" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
     </row>
     <row r="231" spans="2:2">
       <c r="B231" s="33" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
     </row>
     <row r="233" spans="2:2">
       <c r="B233" s="33" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
     </row>
     <row r="235" spans="2:2">
       <c r="B235" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
     </row>
     <row r="237" spans="2:2">
       <c r="B237" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="239" spans="2:2">
       <c r="B239" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
     </row>
     <row r="241" spans="2:2">
       <c r="B241" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="245" spans="2:2" ht="27">
       <c r="B245" s="31" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
     </row>
     <row r="247" spans="2:2" ht="20">
       <c r="B247" s="32" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="249" spans="2:2">
       <c r="B249" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
     </row>
     <row r="250" spans="2:2">
       <c r="B250" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="251" spans="2:2">
       <c r="B251" s="5" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="253" spans="2:2" ht="20">
       <c r="B253" s="32" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="255" spans="2:2">
       <c r="B255" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
     </row>
     <row r="256" spans="2:2">
       <c r="B256" s="5" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="258" spans="2:2" ht="20">
       <c r="B258" s="32" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="260" spans="2:2">
       <c r="B260" s="33" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
     </row>
     <row r="261" spans="2:2">
       <c r="B261" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="262" spans="2:2">
       <c r="B262" s="5" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -8584,89 +8811,89 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="36" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="10" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="10" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="2:8">
       <c r="B10" s="10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="2:8">
       <c r="B11" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="90" customHeight="1">
       <c r="B16" s="80" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C16" s="80"/>
       <c r="D16" s="80"/>
@@ -8677,7 +8904,7 @@
     </row>
     <row r="18" spans="2:5" ht="114" customHeight="1">
       <c r="B18" s="81" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C18" s="81"/>
       <c r="D18" s="81"/>
@@ -8714,1079 +8941,1095 @@
   <sheetData>
     <row r="2" spans="2:10">
       <c r="B2" s="33" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="19" thickBot="1"/>
     <row r="4" spans="2:10">
       <c r="B4" t="s">
-        <v>162</v>
-      </c>
-      <c r="F4" s="82" t="s">
-        <v>185</v>
-      </c>
-      <c r="G4" s="82"/>
+        <v>158</v>
+      </c>
+      <c r="F4" s="104" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" s="104"/>
       <c r="I4" s="57" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="20" thickBot="1">
       <c r="B5" s="42" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F5" s="43" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="G5" s="42" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="I5" s="58"/>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="86" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="85" t="s">
-        <v>50</v>
+      <c r="B6" s="101" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="88" t="s">
+        <v>46</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F6" s="45"/>
       <c r="G6" s="46" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="87"/>
-      <c r="C7" s="83"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="89"/>
       <c r="D7" s="13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F7" s="39"/>
       <c r="G7" s="47" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="I7" s="60" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="87"/>
-      <c r="C8" s="83"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="89"/>
       <c r="D8" s="13" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F8" s="39"/>
       <c r="G8" s="47" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I8" s="60" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="87"/>
+      <c r="B9" s="102"/>
       <c r="C9" s="13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F9" s="39"/>
       <c r="G9" s="47" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I9" s="60" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="19" thickBot="1">
-      <c r="B10" s="88"/>
+      <c r="B10" s="103"/>
       <c r="C10" s="48" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E10" s="48" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F10" s="49"/>
       <c r="G10" s="50" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I10" s="61" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="86" t="s">
-        <v>51</v>
+      <c r="B11" s="101" t="s">
+        <v>47</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F11" s="45"/>
       <c r="G11" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="H11" s="95" t="s">
-        <v>219</v>
+        <v>65</v>
+      </c>
+      <c r="H11" s="90" t="s">
+        <v>213</v>
       </c>
       <c r="I11" s="59" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="87"/>
+      <c r="B12" s="102"/>
       <c r="C12" s="13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F12" s="39"/>
       <c r="G12" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="H12" s="96"/>
+        <v>67</v>
+      </c>
+      <c r="H12" s="91"/>
       <c r="I12" s="60" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="19" thickBot="1">
-      <c r="B13" s="87"/>
+      <c r="B13" s="102"/>
       <c r="C13" s="13" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F13" s="39"/>
       <c r="G13" s="47" t="s">
-        <v>73</v>
-      </c>
-      <c r="H13" s="97"/>
+        <v>69</v>
+      </c>
+      <c r="H13" s="92"/>
       <c r="I13" s="60" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J13" s="5"/>
     </row>
     <row r="14" spans="2:10">
-      <c r="B14" s="87"/>
-      <c r="C14" s="83" t="s">
-        <v>74</v>
+      <c r="B14" s="102"/>
+      <c r="C14" s="89" t="s">
+        <v>70</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F14" s="39"/>
       <c r="G14" s="47" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I14" s="60" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="19" thickBot="1">
-      <c r="B15" s="88"/>
-      <c r="C15" s="84"/>
+      <c r="B15" s="103"/>
+      <c r="C15" s="100"/>
       <c r="D15" s="48" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E15" s="48" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F15" s="49"/>
       <c r="G15" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="I15" s="61" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10">
+      <c r="B16" s="101" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="88" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="88" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="98" t="s">
+        <v>181</v>
+      </c>
+      <c r="I16" s="56"/>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="102"/>
+      <c r="C17" s="89"/>
+      <c r="D17" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="89"/>
+      <c r="G17" s="99"/>
+      <c r="I17" s="56"/>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="102"/>
+      <c r="C18" s="89"/>
+      <c r="D18" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="89"/>
+      <c r="G18" s="99"/>
+      <c r="I18" s="56"/>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="102"/>
+      <c r="C19" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="I15" s="61" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10">
-      <c r="B16" s="86" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="44" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" s="44" t="s">
+      <c r="D19" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="103" t="s">
-        <v>187</v>
-      </c>
-      <c r="I16" s="56"/>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" s="87"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" s="13" t="s">
+      <c r="E19" s="13" t="s">
         <v>80</v>
-      </c>
-      <c r="F17" s="83"/>
-      <c r="G17" s="104"/>
-      <c r="I17" s="56"/>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="87"/>
-      <c r="C18" s="83"/>
-      <c r="D18" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="F18" s="83"/>
-      <c r="G18" s="104"/>
-      <c r="I18" s="56"/>
-    </row>
-    <row r="19" spans="2:9">
-      <c r="B19" s="87"/>
-      <c r="C19" s="83" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>84</v>
       </c>
       <c r="F19" s="39"/>
       <c r="G19" s="47" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="I19" s="60" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="19" thickBot="1">
-      <c r="B20" s="88"/>
-      <c r="C20" s="84"/>
+      <c r="B20" s="103"/>
+      <c r="C20" s="100"/>
       <c r="D20" s="48" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E20" s="48" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F20" s="49"/>
       <c r="G20" s="50" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I20" s="61" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="19" thickBot="1">
       <c r="B21" s="52" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F21" s="54"/>
       <c r="G21" s="55" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I21" s="62" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="86" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="85" t="s">
-        <v>55</v>
+      <c r="B22" s="101" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="88" t="s">
+        <v>51</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F22" s="45"/>
       <c r="G22" s="46" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I22" s="59" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="87"/>
-      <c r="C23" s="83"/>
+      <c r="B23" s="102"/>
+      <c r="C23" s="89"/>
       <c r="D23" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F23" s="39"/>
       <c r="G23" s="47" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="I23" s="60" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="87"/>
-      <c r="C24" s="83"/>
+      <c r="B24" s="102"/>
+      <c r="C24" s="89"/>
       <c r="D24" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F24" s="39"/>
       <c r="G24" s="47" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I24" s="60" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="87"/>
-      <c r="C25" s="83"/>
+      <c r="B25" s="102"/>
+      <c r="C25" s="89"/>
       <c r="D25" s="13" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="47" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I25" s="60" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="87"/>
-      <c r="C26" s="83"/>
+      <c r="B26" s="102"/>
+      <c r="C26" s="89"/>
       <c r="D26" s="13" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F26" s="39"/>
       <c r="G26" s="47" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="I26" s="60" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="87"/>
-      <c r="C27" s="83"/>
+      <c r="B27" s="102"/>
+      <c r="C27" s="89"/>
       <c r="D27" s="13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F27" s="39"/>
       <c r="G27" s="47" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I27" s="60" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="87"/>
-      <c r="C28" s="83"/>
+      <c r="B28" s="102"/>
+      <c r="C28" s="89"/>
       <c r="D28" s="13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F28" s="39"/>
       <c r="G28" s="47" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I28" s="60" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="87"/>
+      <c r="B29" s="102"/>
       <c r="C29" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F29" s="39"/>
       <c r="G29" s="47" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I29" s="60" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="2:9" ht="19" thickBot="1">
-      <c r="B30" s="88"/>
+      <c r="B30" s="103"/>
       <c r="C30" s="48" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D30" s="48" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E30" s="48" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F30" s="49"/>
       <c r="G30" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="I30" s="61" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
+      <c r="B31" s="101" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" s="88" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="61" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9">
-      <c r="B31" s="86" t="s">
-        <v>112</v>
-      </c>
-      <c r="C31" s="85" t="s">
-        <v>113</v>
-      </c>
       <c r="D31" s="44" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F31" s="45"/>
       <c r="G31" s="46" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I31" s="59" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="87"/>
-      <c r="C32" s="83"/>
+      <c r="B32" s="102"/>
+      <c r="C32" s="89"/>
       <c r="D32" s="13" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F32" s="39"/>
       <c r="G32" s="47" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I32" s="60" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="87"/>
-      <c r="C33" s="83"/>
+      <c r="B33" s="102"/>
+      <c r="C33" s="89"/>
       <c r="D33" s="13" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F33" s="39"/>
       <c r="G33" s="47" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I33" s="60" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="87"/>
-      <c r="C34" s="83"/>
+      <c r="B34" s="102"/>
+      <c r="C34" s="89"/>
       <c r="D34" s="13" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F34" s="39"/>
       <c r="G34" s="47" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I34" s="60" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="87"/>
-      <c r="C35" s="83"/>
+      <c r="B35" s="102"/>
+      <c r="C35" s="89"/>
       <c r="D35" s="13" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F35" s="39"/>
       <c r="G35" s="47" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="I35" s="60" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="87"/>
+      <c r="B36" s="102"/>
       <c r="C36" s="13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F36" s="39"/>
       <c r="G36" s="47" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I36" s="60" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="87"/>
-      <c r="C37" s="83" t="s">
-        <v>127</v>
+      <c r="B37" s="102"/>
+      <c r="C37" s="89" t="s">
+        <v>123</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F37" s="39"/>
       <c r="G37" s="47" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I37" s="60" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="87"/>
-      <c r="C38" s="83"/>
+      <c r="B38" s="102"/>
+      <c r="C38" s="89"/>
       <c r="D38" s="13" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F38" s="39"/>
       <c r="G38" s="47" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I38" s="60" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="87"/>
-      <c r="C39" s="83"/>
+      <c r="B39" s="102"/>
+      <c r="C39" s="89"/>
       <c r="D39" s="13" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F39" s="39"/>
       <c r="G39" s="47" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I39" s="60" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="19">
-      <c r="B40" s="87"/>
+      <c r="B40" s="102"/>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
       <c r="F40" s="40" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G40" s="51" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="I40" s="60" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="19" thickBot="1">
-      <c r="B41" s="88"/>
+      <c r="B41" s="103"/>
       <c r="C41" s="48" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D41" s="48" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E41" s="48" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F41" s="49"/>
       <c r="G41" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="I41" s="61" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9">
+      <c r="B42" s="101" t="s">
+        <v>131</v>
+      </c>
+      <c r="C42" s="88" t="s">
+        <v>132</v>
+      </c>
+      <c r="D42" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="E42" s="44" t="s">
         <v>134</v>
-      </c>
-      <c r="I41" s="61" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9">
-      <c r="B42" s="86" t="s">
-        <v>135</v>
-      </c>
-      <c r="C42" s="85" t="s">
-        <v>136</v>
-      </c>
-      <c r="D42" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="E42" s="44" t="s">
-        <v>138</v>
       </c>
       <c r="F42" s="45"/>
       <c r="G42" s="46" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="I42" s="59" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="87"/>
-      <c r="C43" s="83"/>
+      <c r="B43" s="102"/>
+      <c r="C43" s="89"/>
       <c r="D43" s="13" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F43" s="39"/>
       <c r="G43" s="47" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I43" s="60" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="87"/>
-      <c r="C44" s="83"/>
+      <c r="B44" s="102"/>
+      <c r="C44" s="89"/>
       <c r="D44" s="13" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F44" s="39"/>
       <c r="G44" s="47" t="s">
-        <v>141</v>
-      </c>
-      <c r="I44" s="98" t="s">
-        <v>141</v>
+        <v>137</v>
+      </c>
+      <c r="I44" s="93" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="19">
-      <c r="B45" s="87"/>
-      <c r="C45" s="83"/>
+      <c r="B45" s="102"/>
+      <c r="C45" s="89"/>
       <c r="D45" s="13"/>
       <c r="E45" s="13"/>
       <c r="F45" s="40" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G45" s="51" t="s">
-        <v>192</v>
-      </c>
-      <c r="I45" s="99"/>
+        <v>186</v>
+      </c>
+      <c r="I45" s="94"/>
     </row>
     <row r="46" spans="2:9" ht="19">
-      <c r="B46" s="87"/>
-      <c r="C46" s="83"/>
+      <c r="B46" s="102"/>
+      <c r="C46" s="89"/>
       <c r="D46" s="13"/>
       <c r="E46" s="13"/>
       <c r="F46" s="40" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G46" s="51" t="s">
-        <v>193</v>
-      </c>
-      <c r="I46" s="100"/>
+        <v>187</v>
+      </c>
+      <c r="I46" s="95"/>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="87"/>
-      <c r="C47" s="83"/>
+      <c r="B47" s="102"/>
+      <c r="C47" s="89"/>
       <c r="D47" s="13" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F47" s="39"/>
       <c r="G47" s="47" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="I47" s="60" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="87"/>
-      <c r="C48" s="83"/>
+      <c r="B48" s="102"/>
+      <c r="C48" s="89"/>
       <c r="D48" s="35" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F48" s="39"/>
       <c r="G48" s="47" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="I48" s="60" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="49" spans="2:9">
-      <c r="B49" s="87"/>
-      <c r="C49" s="83"/>
+      <c r="B49" s="102"/>
+      <c r="C49" s="89"/>
       <c r="D49" s="13" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F49" s="39"/>
       <c r="G49" s="47" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="I49" s="60" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50" spans="2:9">
-      <c r="B50" s="87"/>
+      <c r="B50" s="102"/>
       <c r="C50" s="13" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F50" s="39"/>
       <c r="G50" s="47" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I50" s="60" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="51" spans="2:9">
-      <c r="B51" s="87"/>
+      <c r="B51" s="102"/>
       <c r="C51" s="13" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F51" s="39"/>
       <c r="G51" s="47" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I51" s="60" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="52" spans="2:9" ht="19" thickBot="1">
-      <c r="B52" s="87"/>
+      <c r="B52" s="102"/>
       <c r="C52" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F52" s="39"/>
       <c r="G52" s="47" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I52" s="63" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="2:9" ht="57">
-      <c r="B53" s="87"/>
+      <c r="B53" s="102"/>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
       <c r="E53" s="13"/>
       <c r="F53" s="40" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G53" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="I53" s="101" t="s">
-        <v>145</v>
+        <v>189</v>
+      </c>
+      <c r="I53" s="96" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="2:9" ht="19">
-      <c r="B54" s="87"/>
+      <c r="B54" s="102"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
       <c r="E54" s="13"/>
       <c r="F54" s="40" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G54" s="51" t="s">
-        <v>198</v>
-      </c>
-      <c r="I54" s="99"/>
+        <v>192</v>
+      </c>
+      <c r="I54" s="94"/>
     </row>
     <row r="55" spans="2:9" ht="19">
-      <c r="B55" s="87"/>
+      <c r="B55" s="102"/>
       <c r="C55" s="13"/>
       <c r="D55" s="13"/>
       <c r="E55" s="13"/>
       <c r="F55" s="40" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G55" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="I55" s="99"/>
+        <v>193</v>
+      </c>
+      <c r="I55" s="94"/>
     </row>
     <row r="56" spans="2:9" ht="19">
-      <c r="B56" s="87"/>
+      <c r="B56" s="102"/>
       <c r="C56" s="13"/>
       <c r="D56" s="13"/>
       <c r="E56" s="13"/>
       <c r="F56" s="40" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="G56" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="I56" s="99"/>
+        <v>194</v>
+      </c>
+      <c r="I56" s="94"/>
     </row>
     <row r="57" spans="2:9" ht="19">
-      <c r="B57" s="87"/>
+      <c r="B57" s="102"/>
       <c r="C57" s="13"/>
       <c r="D57" s="13"/>
       <c r="E57" s="13"/>
       <c r="F57" s="40" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="G57" s="51" t="s">
-        <v>201</v>
-      </c>
-      <c r="I57" s="99"/>
+        <v>195</v>
+      </c>
+      <c r="I57" s="94"/>
     </row>
     <row r="58" spans="2:9" ht="38">
-      <c r="B58" s="87"/>
+      <c r="B58" s="102"/>
       <c r="C58" s="13"/>
       <c r="D58" s="13"/>
       <c r="E58" s="13"/>
       <c r="F58" s="40" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G58" s="51" t="s">
-        <v>202</v>
-      </c>
-      <c r="I58" s="99"/>
+        <v>196</v>
+      </c>
+      <c r="I58" s="94"/>
     </row>
     <row r="59" spans="2:9" ht="20" thickBot="1">
-      <c r="B59" s="87"/>
+      <c r="B59" s="102"/>
       <c r="C59" s="13"/>
       <c r="D59" s="13"/>
       <c r="E59" s="13"/>
       <c r="F59" s="40" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G59" s="51" t="s">
-        <v>203</v>
-      </c>
-      <c r="I59" s="102"/>
+        <v>197</v>
+      </c>
+      <c r="I59" s="97"/>
     </row>
     <row r="60" spans="2:9" ht="19">
-      <c r="B60" s="87"/>
+      <c r="B60" s="102"/>
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
       <c r="E60" s="13"/>
       <c r="F60" s="40" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="G60" s="51" t="s">
-        <v>204</v>
-      </c>
-      <c r="I60" s="101" t="s">
-        <v>222</v>
+        <v>198</v>
+      </c>
+      <c r="I60" s="96" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="61" spans="2:9" ht="20" thickBot="1">
-      <c r="B61" s="87"/>
+      <c r="B61" s="102"/>
       <c r="C61" s="13"/>
       <c r="D61" s="13"/>
       <c r="E61" s="13"/>
       <c r="F61" s="40" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="G61" s="51" t="s">
-        <v>205</v>
-      </c>
-      <c r="I61" s="99"/>
+        <v>199</v>
+      </c>
+      <c r="I61" s="94"/>
     </row>
     <row r="62" spans="2:9" ht="20" thickBot="1">
-      <c r="B62" s="87"/>
+      <c r="B62" s="102"/>
       <c r="C62" s="13"/>
       <c r="D62" s="13"/>
       <c r="E62" s="13"/>
       <c r="F62" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="G62" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="I62" s="62" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" ht="19" customHeight="1">
+      <c r="B63" s="102"/>
+      <c r="C63" s="89" t="s">
+        <v>148</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="F63" s="82" t="s">
+        <v>191</v>
+      </c>
+      <c r="G63" s="85" t="s">
+        <v>190</v>
+      </c>
+      <c r="I63" s="96" t="s">
         <v>215</v>
       </c>
-      <c r="G62" s="51" t="s">
-        <v>206</v>
-      </c>
-      <c r="I62" s="62" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="2:9" ht="19" customHeight="1">
-      <c r="B63" s="87"/>
-      <c r="C63" s="83" t="s">
+    </row>
+    <row r="64" spans="2:9" ht="19" customHeight="1">
+      <c r="B64" s="102"/>
+      <c r="C64" s="89"/>
+      <c r="D64" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="F64" s="83"/>
+      <c r="G64" s="86"/>
+      <c r="I64" s="94"/>
+    </row>
+    <row r="65" spans="2:9" ht="19" customHeight="1" thickBot="1">
+      <c r="B65" s="103"/>
+      <c r="C65" s="100"/>
+      <c r="D65" s="48" t="s">
+        <v>157</v>
+      </c>
+      <c r="E65" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="D63" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="E63" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="F63" s="89" t="s">
-        <v>197</v>
-      </c>
-      <c r="G63" s="92" t="s">
-        <v>196</v>
-      </c>
-      <c r="I63" s="101" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9" ht="19" customHeight="1">
-      <c r="B64" s="87"/>
-      <c r="C64" s="83"/>
-      <c r="D64" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="F64" s="90"/>
-      <c r="G64" s="93"/>
-      <c r="I64" s="99"/>
-    </row>
-    <row r="65" spans="2:9" ht="19" customHeight="1" thickBot="1">
-      <c r="B65" s="88"/>
-      <c r="C65" s="84"/>
-      <c r="D65" s="48" t="s">
-        <v>161</v>
-      </c>
-      <c r="E65" s="48" t="s">
-        <v>156</v>
-      </c>
-      <c r="F65" s="91"/>
-      <c r="G65" s="94"/>
-      <c r="I65" s="102"/>
+      <c r="F65" s="84"/>
+      <c r="G65" s="87"/>
+      <c r="I65" s="97"/>
     </row>
     <row r="67" spans="2:9">
       <c r="E67" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C42:C49"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="B16:B20"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="B42:B65"/>
+    <mergeCell ref="C22:C28"/>
+    <mergeCell ref="B22:B30"/>
+    <mergeCell ref="B31:B41"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="C37:C39"/>
     <mergeCell ref="F63:F65"/>
     <mergeCell ref="G63:G65"/>
     <mergeCell ref="F16:F18"/>
@@ -9796,22 +10039,6 @@
     <mergeCell ref="I60:I61"/>
     <mergeCell ref="I63:I65"/>
     <mergeCell ref="G16:G18"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="B42:B65"/>
-    <mergeCell ref="C22:C28"/>
-    <mergeCell ref="B22:B30"/>
-    <mergeCell ref="B31:B41"/>
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C42:C49"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="B16:B20"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/dict/dict 코드북 260430.xlsx
+++ b/datasets/dict/dict 코드북 260430.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB6F863-494A-0748-9149-A9B57C0E0988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3E8D85-6E81-DB41-8802-79D939ED94E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" xr2:uid="{F4A985C0-B43D-2244-AB7C-DBFAE8B9580A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="546">
   <si>
     <t>e_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -100,10 +100,6 @@
   </si>
   <si>
     <t>is_required</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(상위 범주)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -675,10 +671,6 @@
   </si>
   <si>
     <t>NNG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>낮을수록 먼저 적용(강한 금지 룰은 우선), 예) 10, 20, 30,...</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4771,10 +4763,6 @@
     <t>문법항목 성분의 순서를 하드 제약/소프트 제약으로 쓸 것인지 결정. 한국어는 문장 순서 변형이 자유로우므로 최소한의 100% 고정적이지 않으면 flex로 둘 것.
 fx- fixed, 
 fl- flex</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sheet3 detect_rules</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4818,38 +4806,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">target'의 'component_right_context' 범주에 사용되는 열 항목. 
-'target'열 항목이 'component_right_context'일 경우 'component_id'의 오른쪽 char 조건을 'pattern'에 기록한다. </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rule_note</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stage'가 'detect'인 경우 'target'은 항상 'raw_sentence'여야 함.
-'stage'가 'verify'인 경우 'target'은 'raw_sentence', 'token_window', 'component_right_context' 가능함.
-token_window: 문법 항목 스팬의 앞 뒤 10char 안으로 설정되어 있음. 즉, 이 범위 안에서 verify 정규식 조건을 찾아서 hard fail시킴.
-component_right_context
-선택된 component 시작점 바로 오른쪽 1글자.
-예: '팬데믹'에서 c1='팬데'이면 믹. 다만 오른쪽이 공백이면 공백을 건너뛰고 의미문자를 찾음.
-용도: component 오른쪽 환경을 확인할 때 사용. 단독 hard fail에는 신중히 사용.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(왼쪽 설명에 추가)
-component_text
-선택된 component span 자체의 문자열.
-예: 근데, 텐데, 운데, 런데
-용도: component 자체가 특정 오탐 표면형일 때 hard fail. 
-component_left_context
-선택된 component 시작점 바로 왼쪽 1글자.
-예: '가운데'에서 c1='운데'이면 left_context=가
-용도: component 왼쪽 환경을 확인할 때 사용. 단독 hard fail에는 신중히 사용.
-left_plus_component_text
-선택된 component 바로 왼쪽 1글자 + component_text.  다만 왼쪽이 공백이면 공백을 건너뛰고 의미문자를 찾음.
-예: 가운데 → 가+운데=가운데, 가는데 → 가+는데=가는데
-용도: 가운데/그런데처럼 왼쪽 1글자와 component를 합쳐야 정확히 구별되는 오탐 hard fail.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -5012,6 +4969,73 @@
 목적: detect에서 생긴 FP 제거
 행동: 강한 금지 규칙(hard_fail=true)로 후보를 폐기(discard)
 최소한의 형태적 조건 등으로 확실한 경우에만 hard fail을 제거함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sheet4 detect_rules</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">target'의 'component_right_context', 'component_left_context' 범주에 사용되는 열 항목. 
+'target'열 항목이 'component_right_context'일 경우 'component_id'의 오른쪽 char 조건을 'pattern'에 기록한다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>context_chars</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage'가 'detect'인 경우 'target'은 항상 'raw_sentence'여야 함.
+'stage'가 'verify'인 경우 'target'은 'raw_sentence', 'token_window', 'component_right_context' 가능함.
+token_window: 문법 항목 스팬의 앞 뒤 10char 안으로 설정되어 있음. 즉, 이 범위 안에서 verify 정규식 조건을 찾아서 hard fail시킴.
+component_right_context
+  선택된 component 끝 오른쪽의 non-space 문자 N개.
+  N은 detect_rules.context_chars, 기본값 1.
+  N개보다 부족하면 가능한 만큼 반환한다.
+용도: component 오른쪽 환경을 확인할 때 사용. 단독 hard fail에는 신중히 사용.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(왼쪽 설명에 추가)
+component_text
+선택된 component span 자체의 문자열. 
+예: 'ㄴ/은/는데'의 경우, 근데, 텐데, 운데, 런데
+용도: component 자체가 특정 오탐 표면형일 때 hard fail 시킬 수 있음.
+component_left_context
+  선택된 component 시작점 왼쪽의 non-space 문자 N개.
+  N은 context_chars, 기본값 1.
+  N개보다 부족하면 가능한 만큼 반환한다.
+용도: component 오른쪽 환경을 확인할 때 사용. 단독 hard fail에는 신중히 사용.
+left_plus_component_text
+선택된 component 바로 왼쪽 N글자 + component_text. 다만 왼쪽이 공백이면 공백을 건너뛰고 의미문자를 찾음.
+예: 가운데 → 가+운데=가운데, 가는데 → 가+는데=가는데
+용도: 가운데/그런데처럼 왼쪽 1글자와 component를 합쳐야 정확히 구별되는 오탐 hard fail.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적용 대상: 
+component_left_context
+component_right_context
+left_plus_component_text
+context_chars 없음/blank → 1
+지정가능 범위: 1 &lt;= context_chars &lt;= 20
+적용 예:
+다"고 말했다
+c1=고
+context_chars=2
+component_left_context = 다"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>낮을수록 먼저 적용, 예) 10, 20, 30,...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to_codex_note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코덱스에게 전달할 메모</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5640,7 +5664,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5689,9 +5713,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -5719,9 +5740,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -5847,15 +5865,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -6296,58 +6305,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E809B31-950A-8043-B762-4F555FA10734}">
-  <dimension ref="A1:AX77"/>
+  <dimension ref="A1:AW79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="80.42578125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="83.85546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" customWidth="1"/>
-    <col min="8" max="8" width="74" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="80.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="83.85546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="7" max="7" width="74" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" s="4" customFormat="1" ht="38">
+    <row r="1" spans="1:49" s="4" customFormat="1" ht="38">
       <c r="A1" s="7" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="8"/>
-    </row>
-    <row r="2" spans="1:50" s="6" customFormat="1" ht="39" thickBot="1">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="8"/>
+    </row>
+    <row r="2" spans="1:49" s="6" customFormat="1" ht="39" thickBot="1">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="18"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="17"/>
+      <c r="H2"/>
       <c r="I2"/>
       <c r="J2"/>
       <c r="K2"/>
@@ -6389,963 +6394,697 @@
       <c r="AU2"/>
       <c r="AV2"/>
       <c r="AW2"/>
-      <c r="AX2"/>
-    </row>
-    <row r="3" spans="1:50" ht="40" customHeight="1" thickBot="1">
-      <c r="A3" s="26"/>
-      <c r="B3" s="67" t="s">
-        <v>474</v>
-      </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="30"/>
-    </row>
-    <row r="4" spans="1:50" ht="57">
-      <c r="A4" s="21"/>
-      <c r="B4" s="22" t="s">
+    </row>
+    <row r="3" spans="1:49" ht="40" customHeight="1" thickBot="1">
+      <c r="A3" s="65" t="s">
+        <v>472</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="28"/>
+    </row>
+    <row r="4" spans="1:49" ht="57">
+      <c r="A4" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>475</v>
-      </c>
-      <c r="D4" s="23"/>
+      <c r="B4" s="23" t="s">
+        <v>473</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
       <c r="E4" s="23"/>
       <c r="F4" s="24"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="21" t="s">
+      <c r="G4" s="20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:49" ht="84" customHeight="1">
+      <c r="A5" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="9"/>
+    </row>
+    <row r="6" spans="1:49" ht="40" customHeight="1">
+      <c r="A6" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>501</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="9"/>
+    </row>
+    <row r="7" spans="1:49" ht="40" customHeight="1">
+      <c r="A7" s="72"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="13"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="9"/>
+    </row>
+    <row r="8" spans="1:49" ht="40" customHeight="1">
+      <c r="A8" s="73"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="9"/>
+    </row>
+    <row r="9" spans="1:49" ht="95">
+      <c r="A9" s="35" t="s">
+        <v>506</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="9"/>
+    </row>
+    <row r="10" spans="1:49" ht="67" customHeight="1">
+      <c r="A10" s="35" t="s">
+        <v>492</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="9"/>
+    </row>
+    <row r="11" spans="1:49" ht="67" customHeight="1">
+      <c r="A11" s="35" t="s">
+        <v>502</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="9"/>
+    </row>
+    <row r="12" spans="1:49" ht="19">
+      <c r="A12" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="9"/>
+    </row>
+    <row r="13" spans="1:49" ht="19">
+      <c r="A13" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="9"/>
+    </row>
+    <row r="14" spans="1:49" ht="19">
+      <c r="A14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="9"/>
+    </row>
+    <row r="15" spans="1:49" ht="41" customHeight="1">
+      <c r="A15" s="101" t="s">
+        <v>515</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="9"/>
+    </row>
+    <row r="16" spans="1:49">
+      <c r="A16" s="100" t="s">
+        <v>506</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>508</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="9"/>
+    </row>
+    <row r="17" spans="1:7" ht="38">
+      <c r="A17" s="100" t="s">
+        <v>509</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="9"/>
+    </row>
+    <row r="18" spans="1:7" ht="38">
+      <c r="A18" s="100" t="s">
+        <v>511</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="9"/>
+    </row>
+    <row r="19" spans="1:7" ht="57">
+      <c r="A19" s="100" t="s">
+        <v>516</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="9"/>
+    </row>
+    <row r="20" spans="1:7" ht="19">
+      <c r="A20" s="100" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="9"/>
+    </row>
+    <row r="21" spans="1:7" ht="38">
+      <c r="A21" s="100" t="s">
+        <v>520</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="9"/>
+    </row>
+    <row r="22" spans="1:7" ht="19">
+      <c r="A22" s="100" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="9"/>
+    </row>
+    <row r="23" spans="1:7" ht="19">
+      <c r="A23" s="100" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="9"/>
+    </row>
+    <row r="24" spans="1:7" ht="57">
+      <c r="A24" s="100" t="s">
+        <v>522</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="9"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="100" t="s">
+        <v>523</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="9"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="100"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="9"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="100"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="9"/>
+    </row>
+    <row r="28" spans="1:7" ht="40" customHeight="1">
+      <c r="A28" s="64" t="s">
+        <v>525</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="9"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>528</v>
+      </c>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="9"/>
+    </row>
+    <row r="30" spans="1:7" ht="19">
+      <c r="A30" s="14" t="s">
+        <v>526</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="10"/>
+      <c r="G30" s="9"/>
+    </row>
+    <row r="31" spans="1:7" ht="19">
+      <c r="A31" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="9"/>
+    </row>
+    <row r="32" spans="1:7" ht="114">
+      <c r="A32" s="14" t="s">
+        <v>503</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="F32" s="10"/>
+      <c r="G32" s="9"/>
+    </row>
+    <row r="33" spans="1:7" ht="40" customHeight="1">
+      <c r="A33" s="70" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>530</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="13"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="9"/>
+    </row>
+    <row r="34" spans="1:7" ht="40" customHeight="1">
+      <c r="A34" s="70"/>
+      <c r="B34" s="74"/>
+      <c r="C34" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="13"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="9"/>
+    </row>
+    <row r="35" spans="1:7" ht="178" customHeight="1">
+      <c r="A35" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>531</v>
+      </c>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="9" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="57">
+      <c r="A36" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>533</v>
+      </c>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="9"/>
+    </row>
+    <row r="37" spans="1:7" ht="76">
+      <c r="A37" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="10"/>
+      <c r="G37" s="9"/>
+    </row>
+    <row r="38" spans="1:7" ht="199" customHeight="1">
+      <c r="A38" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>499</v>
+      </c>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="10"/>
+      <c r="G38" s="9"/>
+    </row>
+    <row r="39" spans="1:7" ht="60" customHeight="1">
+      <c r="A39" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" s="10"/>
+      <c r="G39" s="9"/>
+    </row>
+    <row r="40" spans="1:7" ht="145" customHeight="1">
+      <c r="A40" s="63" t="s">
+        <v>537</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="9"/>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="B41" s="32" t="s">
+        <v>528</v>
+      </c>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="9"/>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="16" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="5" spans="1:50" ht="84" customHeight="1">
-      <c r="A5" s="9"/>
-      <c r="B5" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="9"/>
-    </row>
-    <row r="6" spans="1:50" ht="40" customHeight="1">
-      <c r="A6" s="69"/>
-      <c r="B6" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="72" t="s">
+      <c r="B42" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="9"/>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B43" s="32" t="s">
+        <v>535</v>
+      </c>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="9"/>
+    </row>
+    <row r="44" spans="1:7" ht="144">
+      <c r="A44" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B44" s="62" t="s">
+        <v>536</v>
+      </c>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="9"/>
+    </row>
+    <row r="45" spans="1:7" ht="342">
+      <c r="A45" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" s="66" t="s">
+        <v>540</v>
+      </c>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="11" t="s">
+        <v>541</v>
+      </c>
+      <c r="F45" s="10"/>
+      <c r="G45" s="9"/>
+    </row>
+    <row r="46" spans="1:7" ht="57">
+      <c r="A46" s="16" t="s">
         <v>504</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="9"/>
-    </row>
-    <row r="7" spans="1:50" ht="40" customHeight="1">
-      <c r="A7" s="70"/>
-      <c r="B7" s="77"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="9"/>
-    </row>
-    <row r="8" spans="1:50" ht="40" customHeight="1">
-      <c r="A8" s="71"/>
-      <c r="B8" s="78"/>
-      <c r="C8" s="74"/>
-      <c r="D8" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="9"/>
-    </row>
-    <row r="9" spans="1:50" ht="95">
-      <c r="A9" s="9"/>
-      <c r="B9" s="37" t="s">
-        <v>512</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" spans="1:50" ht="67" customHeight="1">
-      <c r="A10" s="9"/>
-      <c r="B10" s="37" t="s">
-        <v>494</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11" spans="1:50" ht="67" customHeight="1">
-      <c r="A11" s="9"/>
-      <c r="B11" s="37" t="s">
+      <c r="B46" s="66" t="s">
+        <v>538</v>
+      </c>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="9"/>
+    </row>
+    <row r="47" spans="1:7" ht="247">
+      <c r="A47" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="B47" s="66" t="s">
+        <v>542</v>
+      </c>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="9"/>
+    </row>
+    <row r="48" spans="1:7" ht="108" customHeight="1">
+      <c r="A48" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48" s="11"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="9"/>
+    </row>
+    <row r="49" spans="1:7" ht="19">
+      <c r="A49" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E49" s="11"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="9"/>
+    </row>
+    <row r="50" spans="1:7" ht="19">
+      <c r="A50" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E50" s="11"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="9"/>
+    </row>
+    <row r="51" spans="1:7" ht="19">
+      <c r="A51" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="9"/>
+    </row>
+    <row r="52" spans="1:7" ht="19">
+      <c r="A52" s="16" t="s">
         <v>505</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="9"/>
-    </row>
-    <row r="12" spans="1:50" ht="19">
-      <c r="A12" s="9"/>
-      <c r="B12" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="9"/>
-    </row>
-    <row r="13" spans="1:50" ht="19">
-      <c r="A13" s="9"/>
-      <c r="B13" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>496</v>
-      </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="9"/>
-    </row>
-    <row r="14" spans="1:50" ht="19">
-      <c r="A14" s="9"/>
-      <c r="B14" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="9"/>
-    </row>
-    <row r="15" spans="1:50" ht="41" customHeight="1">
-      <c r="A15" s="9"/>
-      <c r="B15" s="106" t="s">
-        <v>521</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="9"/>
-    </row>
-    <row r="16" spans="1:50">
-      <c r="A16" s="9"/>
-      <c r="B16" s="105" t="s">
-        <v>512</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>514</v>
-      </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8" ht="38">
-      <c r="A17" s="9"/>
-      <c r="B17" s="105" t="s">
-        <v>515</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>516</v>
-      </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8" ht="38">
-      <c r="A18" s="9"/>
-      <c r="B18" s="105" t="s">
-        <v>517</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8" ht="57">
-      <c r="A19" s="9"/>
-      <c r="B19" s="105" t="s">
-        <v>522</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8" ht="19">
-      <c r="A20" s="9"/>
-      <c r="B20" s="105" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8" ht="38">
-      <c r="A21" s="9"/>
-      <c r="B21" s="105" t="s">
-        <v>526</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8" ht="19">
-      <c r="A22" s="9"/>
-      <c r="B22" s="105" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8" ht="19">
-      <c r="A23" s="9"/>
-      <c r="B23" s="105" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>496</v>
-      </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8" ht="57">
-      <c r="A24" s="9"/>
-      <c r="B24" s="105" t="s">
-        <v>528</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="9"/>
-      <c r="B25" s="105" t="s">
-        <v>529</v>
-      </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="9"/>
-      <c r="B26" s="105"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="9"/>
-      <c r="B27" s="105"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:8" ht="40" customHeight="1">
-      <c r="A28" s="9"/>
-      <c r="B28" s="66" t="s">
-        <v>531</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="9"/>
-      <c r="B29" s="14" t="s">
-        <v>512</v>
-      </c>
-      <c r="C29" s="34" t="s">
-        <v>534</v>
-      </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:8" ht="19">
-      <c r="A30" s="9"/>
-      <c r="B30" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>533</v>
-      </c>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G30" s="10"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:8" ht="19">
-      <c r="A31" s="9"/>
-      <c r="B31" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:8" ht="114">
-      <c r="A32" s="9"/>
-      <c r="B32" s="14" t="s">
-        <v>506</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="11" t="s">
-        <v>519</v>
-      </c>
-      <c r="G32" s="10"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8" ht="40" customHeight="1">
-      <c r="A33" s="9"/>
-      <c r="B33" s="75" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" s="79" t="s">
-        <v>536</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E33" s="13"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8" ht="40" customHeight="1">
-      <c r="A34" s="9"/>
-      <c r="B34" s="75"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E34" s="13"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8" ht="178" customHeight="1">
-      <c r="A35" s="9"/>
-      <c r="B35" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>537</v>
-      </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="9" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="57">
-      <c r="A36" s="9"/>
-      <c r="B36" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>539</v>
-      </c>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8" ht="76">
-      <c r="A37" s="9"/>
-      <c r="B37" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>499</v>
-      </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="G37" s="10"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8" ht="199" customHeight="1">
-      <c r="A38" s="9"/>
-      <c r="B38" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>502</v>
-      </c>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G38" s="10"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8" ht="60" customHeight="1">
-      <c r="A39" s="9"/>
-      <c r="B39" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G39" s="10"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8" ht="145" customHeight="1">
-      <c r="A40" s="9"/>
-      <c r="B40" s="65" t="s">
-        <v>500</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>501</v>
-      </c>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="9"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="9"/>
-      <c r="B41" s="17" t="s">
-        <v>512</v>
-      </c>
-      <c r="C41" s="34" t="s">
-        <v>534</v>
-      </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="9"/>
-      <c r="B42" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C42" s="34" t="s">
-        <v>540</v>
-      </c>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="9"/>
-      <c r="B43" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="34" t="s">
-        <v>541</v>
-      </c>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="9"/>
-    </row>
-    <row r="44" spans="1:8" ht="144">
-      <c r="A44" s="9"/>
-      <c r="B44" s="17" t="s">
+      <c r="B52" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C44" s="64" t="s">
-        <v>542</v>
-      </c>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="9"/>
-    </row>
-    <row r="45" spans="1:8" ht="323">
-      <c r="A45" s="9"/>
-      <c r="B45" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C45" s="68" t="s">
-        <v>510</v>
-      </c>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="11" t="s">
-        <v>511</v>
-      </c>
-      <c r="G45" s="10"/>
-      <c r="H45" s="9"/>
-    </row>
-    <row r="46" spans="1:8" ht="57">
-      <c r="A46" s="9"/>
-      <c r="B46" s="17" t="s">
-        <v>507</v>
-      </c>
-      <c r="C46" s="68" t="s">
-        <v>508</v>
-      </c>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="9"/>
-    </row>
-    <row r="47" spans="1:8" ht="108" customHeight="1">
-      <c r="A47" s="9"/>
-      <c r="B47" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>503</v>
-      </c>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F47" s="11"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="9"/>
-    </row>
-    <row r="48" spans="1:8" ht="19">
-      <c r="A48" s="9"/>
-      <c r="B48" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F48" s="11"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="9"/>
-    </row>
-    <row r="49" spans="1:8" ht="19">
-      <c r="A49" s="9"/>
-      <c r="B49" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="F49" s="11"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="9"/>
-    </row>
-    <row r="50" spans="1:8" ht="19">
-      <c r="A50" s="9"/>
-      <c r="B50" s="17" t="s">
-        <v>509</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F50" s="11"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="9"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="9"/>
-      <c r="B52" s="16"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="9"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="9"/>
-      <c r="B53" s="16"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="9"/>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="9"/>
-      <c r="B54" s="16"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="9"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="9"/>
-      <c r="B55" s="16"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="9"/>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="9"/>
-      <c r="B56" s="16"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="9"/>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="9"/>
-      <c r="B57" s="16"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="9"/>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="9"/>
-      <c r="B58" s="16"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="9"/>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="9"/>
-      <c r="B59" s="16"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="9"/>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="9"/>
-      <c r="B60" s="16"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="9"/>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="9"/>
-      <c r="B61" s="16"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="9"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="9"/>
-      <c r="B62" s="16"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="9"/>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="9"/>
-      <c r="B63" s="16"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="9"/>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="9"/>
-      <c r="B64" s="16"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="10"/>
-      <c r="H64" s="9"/>
-    </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="9"/>
-      <c r="B65" s="16"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="9"/>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="9"/>
-      <c r="B66" s="16"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="10"/>
-      <c r="H66" s="9"/>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="9"/>
-      <c r="B67" s="16"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="10"/>
-      <c r="H67" s="9"/>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="9"/>
-      <c r="B68" s="16"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="9"/>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="9"/>
-      <c r="B69" s="16"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="10"/>
-      <c r="H69" s="9"/>
-    </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="9"/>
-      <c r="B70" s="16"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="9"/>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="9"/>
-      <c r="B71" s="16"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="10"/>
-      <c r="H71" s="9"/>
-    </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="9"/>
-      <c r="B72" s="16"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="10"/>
-      <c r="H72" s="9"/>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="9"/>
-      <c r="B73" s="16"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="10"/>
-      <c r="H73" s="9"/>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="9"/>
-      <c r="B74" s="16"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="9"/>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="9"/>
-      <c r="B75" s="16"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="10"/>
-      <c r="H75" s="9"/>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="9"/>
-      <c r="B76" s="16"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="10"/>
-      <c r="H76" s="9"/>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="9"/>
-      <c r="B77" s="16"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="10"/>
-      <c r="H77" s="9"/>
-    </row>
+      <c r="E52" s="11"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="9"/>
+    </row>
+    <row r="53" spans="1:7" s="5" customFormat="1"/>
+    <row r="54" spans="1:7" s="5" customFormat="1"/>
+    <row r="55" spans="1:7" s="5" customFormat="1"/>
+    <row r="56" spans="1:7" s="5" customFormat="1"/>
+    <row r="57" spans="1:7" s="5" customFormat="1"/>
+    <row r="58" spans="1:7" s="5" customFormat="1"/>
+    <row r="59" spans="1:7" s="5" customFormat="1"/>
+    <row r="60" spans="1:7" s="5" customFormat="1"/>
+    <row r="61" spans="1:7" s="5" customFormat="1"/>
+    <row r="62" spans="1:7" s="5" customFormat="1"/>
+    <row r="63" spans="1:7" s="5" customFormat="1"/>
+    <row r="64" spans="1:7" s="5" customFormat="1"/>
+    <row r="65" s="5" customFormat="1"/>
+    <row r="66" s="5" customFormat="1"/>
+    <row r="67" s="5" customFormat="1"/>
+    <row r="68" s="5" customFormat="1"/>
+    <row r="69" s="5" customFormat="1"/>
+    <row r="70" s="5" customFormat="1"/>
+    <row r="71" s="5" customFormat="1"/>
+    <row r="72" s="5" customFormat="1"/>
+    <row r="73" s="5" customFormat="1"/>
+    <row r="74" s="5" customFormat="1"/>
+    <row r="75" s="5" customFormat="1"/>
+    <row r="76" s="5" customFormat="1"/>
+    <row r="77" s="5" customFormat="1"/>
+    <row r="78" s="5" customFormat="1"/>
+    <row r="79" s="5" customFormat="1"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="A33:A34"/>
     <mergeCell ref="A6:A8"/>
-    <mergeCell ref="C6:C8"/>
     <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C33:C34"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7363,7 +7102,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B1">
         <v>260222</v>
@@ -7371,740 +7110,740 @@
     </row>
     <row r="2" spans="1:2">
       <c r="B2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="27">
-      <c r="B6" s="31" t="s">
-        <v>223</v>
+      <c r="B6" s="29" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="B8" s="33" t="s">
-        <v>224</v>
+      <c r="B8" s="31" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="B12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" spans="2:2">
-      <c r="B18" s="33" t="s">
-        <v>229</v>
+      <c r="B18" s="31" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="27">
-      <c r="B26" s="31" t="s">
-        <v>232</v>
+      <c r="B26" s="29" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="20">
-      <c r="B28" s="32" t="s">
-        <v>464</v>
+      <c r="B28" s="30" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="5" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="52" spans="2:2">
-      <c r="B52" s="33" t="s">
-        <v>240</v>
+      <c r="B52" s="31" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" s="5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="31" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="31" t="s">
         <v>241</v>
-      </c>
-    </row>
-    <row r="56" spans="2:2">
-      <c r="B56" s="33" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2">
-      <c r="B58" s="33" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="31" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="31" t="s">
         <v>249</v>
-      </c>
-    </row>
-    <row r="72" spans="2:2">
-      <c r="B72" s="33" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2">
-      <c r="B74" s="33" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="80" spans="2:2">
-      <c r="B80" s="33" t="s">
-        <v>254</v>
+      <c r="B80" s="31" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="2:2">
       <c r="B82" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="84" spans="2:2">
       <c r="B84" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="88" spans="2:2" ht="20">
-      <c r="B88" s="32" t="s">
-        <v>465</v>
+      <c r="B88" s="30" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="89" spans="2:2" ht="20">
-      <c r="B89" s="32"/>
+      <c r="B89" s="30"/>
     </row>
     <row r="90" spans="2:2">
       <c r="B90" s="5" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="92" spans="2:2">
-      <c r="B92" s="33" t="s">
-        <v>467</v>
+      <c r="B92" s="31" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="94" spans="2:2">
       <c r="B94" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="95" spans="2:2">
       <c r="B95" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="101" spans="2:2">
       <c r="B101" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107" s="31" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109" s="31" t="s">
         <v>261</v>
-      </c>
-    </row>
-    <row r="107" spans="2:2">
-      <c r="B107" s="33" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="109" spans="2:2">
-      <c r="B109" s="33" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="119" spans="2:2">
-      <c r="B119" s="33" t="s">
-        <v>268</v>
+      <c r="B119" s="31" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2">
+      <c r="B125" s="31" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2">
+      <c r="B127" s="31" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="125" spans="2:2">
-      <c r="B125" s="33" t="s">
+    <row r="129" spans="2:2">
+      <c r="B129" s="31" t="s">
         <v>270</v>
-      </c>
-    </row>
-    <row r="127" spans="2:2">
-      <c r="B127" s="33" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="129" spans="2:2">
-      <c r="B129" s="33" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="131" spans="2:2">
       <c r="B131" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="133" spans="2:2">
-      <c r="B133" s="33" t="s">
-        <v>274</v>
+      <c r="B133" s="31" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="135" spans="2:2">
       <c r="B135" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="137" spans="2:2">
       <c r="B137" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="141" spans="2:2" ht="20">
-      <c r="B141" s="32" t="s">
-        <v>277</v>
+      <c r="B141" s="30" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="143" spans="2:2">
       <c r="B143" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="145" spans="2:2">
-      <c r="B145" s="33" t="s">
-        <v>278</v>
+      <c r="B145" s="31" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="147" spans="2:2">
       <c r="B147" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="149" spans="2:2">
-      <c r="B149" s="33" t="s">
-        <v>279</v>
+      <c r="B149" s="31" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="151" spans="2:2">
       <c r="B151" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="153" spans="2:2">
       <c r="B153" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="155" spans="2:2">
       <c r="B155" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="157" spans="2:2">
       <c r="B157" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="159" spans="2:2">
-      <c r="B159" s="33" t="s">
-        <v>283</v>
+      <c r="B159" s="31" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="160" spans="2:2">
       <c r="B160" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="162" spans="2:2">
       <c r="B162" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="164" spans="2:2">
-      <c r="B164" s="33" t="s">
-        <v>286</v>
+      <c r="B164" s="31" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="165" spans="2:2">
       <c r="B165" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="167" spans="2:2">
-      <c r="B167" s="33" t="s">
-        <v>288</v>
+      <c r="B167" s="31" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="169" spans="2:2">
       <c r="B169" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="171" spans="2:2">
       <c r="B171" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="173" spans="2:2">
       <c r="B173" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="177" spans="2:2" ht="20">
-      <c r="B177" s="32" t="s">
-        <v>292</v>
+      <c r="B177" s="30" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="179" spans="2:2">
       <c r="B179" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="181" spans="2:2">
-      <c r="B181" s="33" t="s">
-        <v>293</v>
+      <c r="B181" s="31" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="183" spans="2:2">
       <c r="B183" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="185" spans="2:2">
       <c r="B185" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="187" spans="2:2">
       <c r="B187" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2">
+      <c r="B189" s="31" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2">
+      <c r="B191" s="31" t="s">
         <v>295</v>
-      </c>
-    </row>
-    <row r="189" spans="2:2">
-      <c r="B189" s="33" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="191" spans="2:2">
-      <c r="B191" s="33" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="31" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="31" t="s">
         <v>298</v>
-      </c>
-    </row>
-    <row r="195" spans="2:2">
-      <c r="B195" s="33" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="197" spans="2:2">
-      <c r="B197" s="33" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="199" spans="2:2">
       <c r="B199" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="201" spans="2:2">
       <c r="B201" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="203" spans="2:2">
       <c r="B203" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="205" spans="2:2">
       <c r="B205" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="207" spans="2:2">
       <c r="B207" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2" ht="27">
+      <c r="B211" s="29" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="213" spans="2:2" ht="20">
+      <c r="B213" s="30" t="s">
         <v>304</v>
-      </c>
-    </row>
-    <row r="211" spans="2:2" ht="27">
-      <c r="B211" s="31" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="213" spans="2:2" ht="20">
-      <c r="B213" s="32" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="215" spans="2:2">
       <c r="B215" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="217" spans="2:2">
       <c r="B217" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="219" spans="2:2">
       <c r="B219" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="221" spans="2:2">
       <c r="B221" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="223" spans="2:2">
       <c r="B223" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="225" spans="2:2" ht="20">
-      <c r="B225" s="32" t="s">
+      <c r="B225" s="30" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2">
+      <c r="B227" s="31" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="229" spans="2:2">
+      <c r="B229" s="31" t="s">
         <v>311</v>
-      </c>
-    </row>
-    <row r="227" spans="2:2">
-      <c r="B227" s="33" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="229" spans="2:2">
-      <c r="B229" s="33" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="231" spans="2:2">
       <c r="B231" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="233" spans="2:2" ht="20">
+      <c r="B233" s="30" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="235" spans="2:2">
+      <c r="B235" s="31" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="233" spans="2:2" ht="20">
-      <c r="B233" s="32" t="s">
+    <row r="237" spans="2:2">
+      <c r="B237" s="31" t="s">
         <v>315</v>
-      </c>
-    </row>
-    <row r="235" spans="2:2">
-      <c r="B235" s="33" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="237" spans="2:2">
-      <c r="B237" s="33" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="239" spans="2:2">
       <c r="B239" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="241" spans="2:2">
-      <c r="B241" s="33" t="s">
-        <v>319</v>
+      <c r="B241" s="31" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="243" spans="2:2">
       <c r="B243" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="245" spans="2:2" ht="20">
-      <c r="B245" s="32" t="s">
-        <v>321</v>
+      <c r="B245" s="30" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="247" spans="2:2">
       <c r="B247" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="249" spans="2:2">
       <c r="B249" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="251" spans="2:2">
       <c r="B251" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="253" spans="2:2" ht="20">
+      <c r="B253" s="30" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="255" spans="2:2">
+      <c r="B255" s="31" t="s">
         <v>324</v>
-      </c>
-    </row>
-    <row r="253" spans="2:2" ht="20">
-      <c r="B253" s="32" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="255" spans="2:2">
-      <c r="B255" s="33" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="257" spans="2:2">
       <c r="B257" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="259" spans="2:2" ht="20">
-      <c r="B259" s="32" t="s">
-        <v>328</v>
+      <c r="B259" s="30" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="261" spans="2:2">
       <c r="B261" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="263" spans="2:2">
       <c r="B263" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="267" spans="2:2" ht="27">
-      <c r="B267" s="31" t="s">
-        <v>331</v>
+      <c r="B267" s="29" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="269" spans="2:2">
       <c r="B269" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="271" spans="2:2">
+      <c r="B271" s="31" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="273" spans="2:2">
+      <c r="B273" s="31" t="s">
         <v>332</v>
-      </c>
-    </row>
-    <row r="271" spans="2:2">
-      <c r="B271" s="33" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="273" spans="2:2">
-      <c r="B273" s="33" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="279" spans="2:2">
       <c r="B279" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="281" spans="2:2">
       <c r="B281" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="283" spans="2:2">
       <c r="B283" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="287" spans="2:2" ht="27">
-      <c r="B287" s="31" t="s">
-        <v>477</v>
+      <c r="B287" s="29" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="289" spans="2:2">
       <c r="B289" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="291" spans="2:2">
       <c r="B291" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="293" spans="2:2">
       <c r="B293" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="295" spans="2:2">
       <c r="B295" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="300" spans="2:2">
       <c r="B300" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="302" spans="2:2">
       <c r="B302" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="304" spans="2:2">
       <c r="B304" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="305" spans="2:2">
       <c r="B305" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -8121,7 +7860,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B1">
         <v>260222</v>
@@ -8129,667 +7868,667 @@
     </row>
     <row r="2" spans="1:2">
       <c r="B2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="27">
-      <c r="B6" s="31" t="s">
-        <v>351</v>
+      <c r="B6" s="29" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="B12" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="27">
-      <c r="B20" s="31" t="s">
-        <v>480</v>
+      <c r="B20" s="29" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="20">
-      <c r="B22" s="32" t="s">
-        <v>356</v>
+      <c r="B22" s="30" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="26" spans="2:2">
-      <c r="B26" s="33" t="s">
-        <v>358</v>
+      <c r="B26" s="31" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="30" spans="2:2" ht="20">
-      <c r="B30" s="32" t="s">
-        <v>360</v>
+      <c r="B30" s="30" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="46" spans="2:2" ht="20">
-      <c r="B46" s="32" t="s">
-        <v>367</v>
+      <c r="B46" s="30" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="69" spans="2:2" ht="20">
-      <c r="B69" s="32" t="s">
-        <v>381</v>
+      <c r="B69" s="30" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="81" spans="2:2" ht="20">
-      <c r="B81" s="32" t="s">
-        <v>386</v>
+      <c r="B81" s="30" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="85" spans="2:2">
       <c r="B85" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="87" spans="2:2">
       <c r="B87" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="91" spans="2:2">
       <c r="B91" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="93" spans="2:2">
       <c r="B93" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="97" spans="2:2" ht="27">
-      <c r="B97" s="31" t="s">
-        <v>391</v>
+      <c r="B97" s="29" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="101" spans="2:2" ht="20">
-      <c r="B101" s="32" t="s">
-        <v>393</v>
+      <c r="B101" s="30" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="117" spans="2:2" ht="20">
-      <c r="B117" s="32" t="s">
-        <v>401</v>
+      <c r="B117" s="30" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="119" spans="2:2">
       <c r="B119" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="127" spans="2:2">
       <c r="B127" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="129" spans="2:2" ht="20">
-      <c r="B129" s="32" t="s">
-        <v>406</v>
+      <c r="B129" s="30" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="131" spans="2:2">
       <c r="B131" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="133" spans="2:2">
       <c r="B133" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="135" spans="2:2">
       <c r="B135" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="137" spans="2:2">
       <c r="B137" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="139" spans="2:2" ht="20">
-      <c r="B139" s="32" t="s">
-        <v>410</v>
+      <c r="B139" s="30" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="141" spans="2:2">
       <c r="B141" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="143" spans="2:2">
       <c r="B143" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="2:2">
       <c r="B145" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" ht="27">
+      <c r="B149" s="29" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" ht="20">
+      <c r="B151" s="30" t="s">
         <v>412</v>
-      </c>
-    </row>
-    <row r="149" spans="2:2" ht="27">
-      <c r="B149" s="31" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="151" spans="2:2" ht="20">
-      <c r="B151" s="32" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="153" spans="2:2">
       <c r="B153" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="155" spans="2:2">
       <c r="B155" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="157" spans="2:2">
       <c r="B157" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="159" spans="2:2">
       <c r="B159" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="161" spans="2:2">
       <c r="B161" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="163" spans="2:2">
       <c r="B163" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="165" spans="2:2">
       <c r="B165" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="167" spans="2:2" ht="20">
-      <c r="B167" s="32" t="s">
-        <v>422</v>
+      <c r="B167" s="30" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="169" spans="2:2">
       <c r="B169" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="171" spans="2:2">
       <c r="B171" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="173" spans="2:2">
       <c r="B173" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="175" spans="2:2">
       <c r="B175" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="177" spans="2:2">
       <c r="B177" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="179" spans="2:2">
       <c r="B179" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="180" spans="2:2">
       <c r="B180" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="182" spans="2:2">
       <c r="B182" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="184" spans="2:2">
       <c r="B184" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="186" spans="2:2" ht="20">
-      <c r="B186" s="32" t="s">
-        <v>428</v>
+      <c r="B186" s="30" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="188" spans="2:2">
       <c r="B188" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="190" spans="2:2">
       <c r="B190" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="192" spans="2:2">
       <c r="B192" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="198" spans="2:2">
       <c r="B198" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="200" spans="2:2" ht="20">
-      <c r="B200" s="32" t="s">
-        <v>433</v>
+      <c r="B200" s="30" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="202" spans="2:2">
       <c r="B202" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="204" spans="2:2">
       <c r="B204" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="206" spans="2:2">
       <c r="B206" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="208" spans="2:2">
       <c r="B208" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="210" spans="2:2">
       <c r="B210" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="212" spans="2:2">
       <c r="B212" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="213" spans="2:2">
       <c r="B213" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="215" spans="2:2">
       <c r="B215" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="219" spans="2:2" ht="27">
-      <c r="B219" s="31" t="s">
-        <v>492</v>
+      <c r="B219" s="29" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="221" spans="2:2">
       <c r="B221" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="223" spans="2:2">
       <c r="B223" s="5" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="225" spans="2:2">
       <c r="B225" s="5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="227" spans="2:2">
       <c r="B227" s="5" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="229" spans="2:2">
       <c r="B229" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="231" spans="2:2">
+      <c r="B231" s="31" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="233" spans="2:2">
+      <c r="B233" s="31" t="s">
         <v>444</v>
-      </c>
-    </row>
-    <row r="231" spans="2:2">
-      <c r="B231" s="33" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="233" spans="2:2">
-      <c r="B233" s="33" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="235" spans="2:2">
       <c r="B235" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="237" spans="2:2">
       <c r="B237" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="239" spans="2:2">
       <c r="B239" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="241" spans="2:2">
       <c r="B241" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="245" spans="2:2" ht="27">
+      <c r="B245" s="29" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="247" spans="2:2" ht="20">
+      <c r="B247" s="30" t="s">
         <v>450</v>
-      </c>
-    </row>
-    <row r="245" spans="2:2" ht="27">
-      <c r="B245" s="31" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="247" spans="2:2" ht="20">
-      <c r="B247" s="32" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="249" spans="2:2">
       <c r="B249" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="250" spans="2:2">
       <c r="B250" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="251" spans="2:2">
       <c r="B251" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="253" spans="2:2" ht="20">
-      <c r="B253" s="32" t="s">
-        <v>456</v>
+      <c r="B253" s="30" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="255" spans="2:2">
       <c r="B255" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="256" spans="2:2">
       <c r="B256" s="5" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="258" spans="2:2" ht="20">
+      <c r="B258" s="30" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="260" spans="2:2">
+      <c r="B260" s="31" t="s">
         <v>458</v>
-      </c>
-    </row>
-    <row r="258" spans="2:2" ht="20">
-      <c r="B258" s="32" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="260" spans="2:2">
-      <c r="B260" s="33" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="261" spans="2:2">
       <c r="B261" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="262" spans="2:2">
       <c r="B262" s="5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -8810,105 +8549,105 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
-      <c r="B2" s="36" t="s">
-        <v>173</v>
+      <c r="B2" s="34" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>163</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>165</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="10" spans="2:8">
       <c r="B10" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="2:8">
       <c r="B11" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="90" customHeight="1">
-      <c r="B16" s="80" t="s">
-        <v>219</v>
-      </c>
-      <c r="C16" s="80"/>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="80"/>
-      <c r="G16" s="80"/>
-      <c r="H16" s="80"/>
+      <c r="B16" s="75" t="s">
+        <v>217</v>
+      </c>
+      <c r="C16" s="75"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="75"/>
     </row>
     <row r="18" spans="2:5" ht="114" customHeight="1">
-      <c r="B18" s="81" t="s">
-        <v>220</v>
-      </c>
-      <c r="C18" s="81"/>
-      <c r="D18" s="81"/>
-      <c r="E18" s="81"/>
+      <c r="B18" s="76" t="s">
+        <v>218</v>
+      </c>
+      <c r="C18" s="76"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8930,7 +8669,7 @@
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16" style="41" customWidth="1"/>
+    <col min="6" max="6" width="16" style="39" customWidth="1"/>
     <col min="7" max="7" width="14.5703125" style="1" customWidth="1"/>
     <col min="8" max="8" width="27.28515625" customWidth="1"/>
     <col min="9" max="9" width="22.85546875" bestFit="1" customWidth="1"/>
@@ -8940,1076 +8679,1076 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10">
-      <c r="B2" s="33" t="s">
-        <v>217</v>
+      <c r="B2" s="31" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="19" thickBot="1"/>
     <row r="4" spans="2:10">
       <c r="B4" t="s">
-        <v>158</v>
-      </c>
-      <c r="F4" s="104" t="s">
+        <v>157</v>
+      </c>
+      <c r="F4" s="99" t="s">
+        <v>177</v>
+      </c>
+      <c r="G4" s="99"/>
+      <c r="I4" s="55" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="20" thickBot="1">
+      <c r="B5" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="G5" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="I5" s="56"/>
+    </row>
+    <row r="6" spans="2:10">
+      <c r="B6" s="96" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="83" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="F6" s="43"/>
+      <c r="G6" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="I6" s="57" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" s="97"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="37"/>
+      <c r="G7" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="I7" s="58" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="B8" s="97"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="37"/>
+      <c r="G8" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="B9" s="97"/>
+      <c r="C9" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="37"/>
+      <c r="G9" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="58" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="19" thickBot="1">
+      <c r="B10" s="98"/>
+      <c r="C10" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="47"/>
+      <c r="G10" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="59" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="B11" s="96" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="43"/>
+      <c r="G11" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="85" t="s">
+        <v>211</v>
+      </c>
+      <c r="I11" s="57" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10">
+      <c r="B12" s="97"/>
+      <c r="C12" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="37"/>
+      <c r="G12" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="86"/>
+      <c r="I12" s="58" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" ht="19" thickBot="1">
+      <c r="B13" s="97"/>
+      <c r="C13" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="37"/>
+      <c r="G13" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="H13" s="87"/>
+      <c r="I13" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="B14" s="97"/>
+      <c r="C14" s="84" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="37"/>
+      <c r="G14" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14" s="58" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="19" thickBot="1">
+      <c r="B15" s="98"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="47"/>
+      <c r="G15" s="48" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15" s="59" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10">
+      <c r="B16" s="96" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="83" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="83" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="93" t="s">
         <v>179</v>
       </c>
-      <c r="G4" s="104"/>
-      <c r="I4" s="57" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" ht="20" thickBot="1">
-      <c r="B5" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" s="42" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="43" t="s">
-        <v>211</v>
-      </c>
-      <c r="G5" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="I5" s="58"/>
-    </row>
-    <row r="6" spans="2:10">
-      <c r="B6" s="101" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="88" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>176</v>
-      </c>
-      <c r="F6" s="45"/>
-      <c r="G6" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="I6" s="59" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10">
-      <c r="B7" s="102"/>
-      <c r="C7" s="89"/>
-      <c r="D7" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="39"/>
-      <c r="G7" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="I7" s="60" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="B8" s="102"/>
-      <c r="C8" s="89"/>
-      <c r="D8" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="39"/>
-      <c r="G8" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="I8" s="60" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10">
-      <c r="B9" s="102"/>
-      <c r="C9" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="39"/>
-      <c r="G9" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="I9" s="60" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" ht="19" thickBot="1">
-      <c r="B10" s="103"/>
-      <c r="C10" s="48" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" s="48" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" s="49"/>
-      <c r="G10" s="50" t="s">
-        <v>63</v>
-      </c>
-      <c r="I10" s="61" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10">
-      <c r="B11" s="101" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="44" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="44" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="44" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" s="45"/>
-      <c r="G11" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11" s="90" t="s">
-        <v>213</v>
-      </c>
-      <c r="I11" s="59" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10">
-      <c r="B12" s="102"/>
-      <c r="C12" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="H12" s="91"/>
-      <c r="I12" s="60" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" ht="19" thickBot="1">
-      <c r="B13" s="102"/>
-      <c r="C13" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F13" s="39"/>
-      <c r="G13" s="47" t="s">
-        <v>69</v>
-      </c>
-      <c r="H13" s="92"/>
-      <c r="I13" s="60" t="s">
-        <v>69</v>
-      </c>
-      <c r="J13" s="5"/>
-    </row>
-    <row r="14" spans="2:10">
-      <c r="B14" s="102"/>
-      <c r="C14" s="89" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F14" s="39"/>
-      <c r="G14" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="I14" s="60" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" ht="19" thickBot="1">
-      <c r="B15" s="103"/>
-      <c r="C15" s="100"/>
-      <c r="D15" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" s="49"/>
-      <c r="G15" s="50" t="s">
-        <v>74</v>
-      </c>
-      <c r="I15" s="61" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10">
-      <c r="B16" s="101" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="88" t="s">
+      <c r="I16" s="54"/>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="97"/>
+      <c r="C17" s="84"/>
+      <c r="D17" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="84"/>
+      <c r="G17" s="94"/>
+      <c r="I17" s="54"/>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="97"/>
+      <c r="C18" s="84"/>
+      <c r="D18" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="84"/>
+      <c r="G18" s="94"/>
+      <c r="I18" s="54"/>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="97"/>
+      <c r="C19" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="37"/>
+      <c r="G19" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" s="58" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="19" thickBot="1">
+      <c r="B20" s="98"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" s="47"/>
+      <c r="G20" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="I20" s="59" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="19" thickBot="1">
+      <c r="B21" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="52"/>
+      <c r="G21" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="I21" s="60" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="96" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="44" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" s="44" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="88" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16" s="98" t="s">
-        <v>181</v>
-      </c>
-      <c r="I16" s="56"/>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" s="102"/>
-      <c r="C17" s="89"/>
-      <c r="D17" s="13" t="s">
+      <c r="C22" s="83" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="F22" s="43"/>
+      <c r="G22" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="I22" s="57" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23" s="97"/>
+      <c r="C23" s="84"/>
+      <c r="D23" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" s="37"/>
+      <c r="G23" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="I23" s="58" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24" s="97"/>
+      <c r="C24" s="84"/>
+      <c r="D24" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" s="37"/>
+      <c r="G24" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="I24" s="58" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="B25" s="97"/>
+      <c r="C25" s="84"/>
+      <c r="D25" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F25" s="37"/>
+      <c r="G25" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="I25" s="58" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="B26" s="97"/>
+      <c r="C26" s="84"/>
+      <c r="D26" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17" s="89"/>
-      <c r="G17" s="99"/>
-      <c r="I17" s="56"/>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="102"/>
-      <c r="C18" s="89"/>
-      <c r="D18" s="13" t="s">
+      <c r="E26" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="F26" s="37"/>
+      <c r="G26" s="45" t="s">
+        <v>216</v>
+      </c>
+      <c r="I26" s="58" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
+      <c r="B27" s="97"/>
+      <c r="C27" s="84"/>
+      <c r="D27" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F18" s="89"/>
-      <c r="G18" s="99"/>
-      <c r="I18" s="56"/>
-    </row>
-    <row r="19" spans="2:9">
-      <c r="B19" s="102"/>
-      <c r="C19" s="89" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F19" s="39"/>
-      <c r="G19" s="47" t="s">
-        <v>80</v>
-      </c>
-      <c r="I19" s="60" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" ht="19" thickBot="1">
-      <c r="B20" s="103"/>
-      <c r="C20" s="100"/>
-      <c r="D20" s="48" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" s="49"/>
-      <c r="G20" s="50" t="s">
-        <v>82</v>
-      </c>
-      <c r="I20" s="61" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" ht="19" thickBot="1">
-      <c r="B21" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" s="53" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" s="53" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="F21" s="54"/>
-      <c r="G21" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I21" s="62" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="101" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" s="88" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="E22" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="F22" s="45"/>
-      <c r="G22" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="I22" s="59" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9">
-      <c r="B23" s="102"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="F23" s="39"/>
-      <c r="G23" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="I23" s="60" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9">
-      <c r="B24" s="102"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F24" s="39"/>
-      <c r="G24" s="47" t="s">
-        <v>91</v>
-      </c>
-      <c r="I24" s="60" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9">
-      <c r="B25" s="102"/>
-      <c r="C25" s="89"/>
-      <c r="D25" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F25" s="39"/>
-      <c r="G25" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="I25" s="60" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9">
-      <c r="B26" s="102"/>
-      <c r="C26" s="89"/>
-      <c r="D26" s="13" t="s">
+      <c r="E27" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="37"/>
+      <c r="G27" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="I27" s="58" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9">
+      <c r="B28" s="97"/>
+      <c r="C28" s="84"/>
+      <c r="D28" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F28" s="37"/>
+      <c r="G28" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="I28" s="58" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9">
+      <c r="B29" s="97"/>
+      <c r="C29" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F29" s="37"/>
+      <c r="G29" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="I29" s="58" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" ht="19" thickBot="1">
+      <c r="B30" s="98"/>
+      <c r="C30" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="E30" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="E26" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="F26" s="39"/>
-      <c r="G26" s="47" t="s">
-        <v>218</v>
-      </c>
-      <c r="I26" s="60" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9">
-      <c r="B27" s="102"/>
-      <c r="C27" s="89"/>
-      <c r="D27" s="13" t="s">
+      <c r="F30" s="47"/>
+      <c r="G30" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="I30" s="59" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
+      <c r="B31" s="96" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="F27" s="39"/>
-      <c r="G27" s="47" t="s">
-        <v>95</v>
-      </c>
-      <c r="I27" s="60" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9">
-      <c r="B28" s="102"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="F28" s="39"/>
-      <c r="G28" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="I28" s="60" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9">
-      <c r="B29" s="102"/>
-      <c r="C29" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="F29" s="39"/>
-      <c r="G29" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="I29" s="60" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" ht="19" thickBot="1">
-      <c r="B30" s="103"/>
-      <c r="C30" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="E30" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="F30" s="49"/>
-      <c r="G30" s="50" t="s">
-        <v>105</v>
-      </c>
-      <c r="I30" s="61" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9">
-      <c r="B31" s="101" t="s">
+      <c r="C31" s="83" t="s">
         <v>108</v>
       </c>
-      <c r="C31" s="88" t="s">
+      <c r="D31" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="D31" s="44" t="s">
+      <c r="E31" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="E31" s="44" t="s">
+      <c r="F31" s="43"/>
+      <c r="G31" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="I31" s="57" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
+      <c r="B32" s="97"/>
+      <c r="C32" s="84"/>
+      <c r="D32" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="F31" s="45"/>
-      <c r="G31" s="46" t="s">
-        <v>111</v>
-      </c>
-      <c r="I31" s="59" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9">
-      <c r="B32" s="102"/>
-      <c r="C32" s="89"/>
-      <c r="D32" s="13" t="s">
+      <c r="E32" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="F32" s="37"/>
+      <c r="G32" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="I32" s="58" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33" s="97"/>
+      <c r="C33" s="84"/>
+      <c r="D33" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="F32" s="39"/>
-      <c r="G32" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="I32" s="60" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9">
-      <c r="B33" s="102"/>
-      <c r="C33" s="89"/>
-      <c r="D33" s="13" t="s">
+      <c r="E33" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="F33" s="37"/>
+      <c r="G33" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="I33" s="58" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9">
+      <c r="B34" s="97"/>
+      <c r="C34" s="84"/>
+      <c r="D34" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="F33" s="39"/>
-      <c r="G33" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="I33" s="60" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9">
-      <c r="B34" s="102"/>
-      <c r="C34" s="89"/>
-      <c r="D34" s="13" t="s">
+      <c r="E34" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="F34" s="37"/>
+      <c r="G34" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="I34" s="58" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9">
+      <c r="B35" s="97"/>
+      <c r="C35" s="84"/>
+      <c r="D35" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="F34" s="39"/>
-      <c r="G34" s="47" t="s">
-        <v>117</v>
-      </c>
-      <c r="I34" s="60" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9">
-      <c r="B35" s="102"/>
-      <c r="C35" s="89"/>
-      <c r="D35" s="13" t="s">
+      <c r="E35" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="F35" s="37"/>
+      <c r="G35" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="I35" s="58" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9">
+      <c r="B36" s="97"/>
+      <c r="C36" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="F35" s="39"/>
-      <c r="G35" s="47" t="s">
-        <v>119</v>
-      </c>
-      <c r="I35" s="60" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9">
-      <c r="B36" s="102"/>
-      <c r="C36" s="13" t="s">
+      <c r="D36" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="E36" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="F36" s="37"/>
+      <c r="G36" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="I36" s="58" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9">
+      <c r="B37" s="97"/>
+      <c r="C37" s="84" t="s">
         <v>122</v>
       </c>
-      <c r="F36" s="39"/>
-      <c r="G36" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="I36" s="60" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9">
-      <c r="B37" s="102"/>
-      <c r="C37" s="89" t="s">
+      <c r="D37" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="E37" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="F37" s="37"/>
+      <c r="G37" s="45" t="s">
+        <v>152</v>
+      </c>
+      <c r="I37" s="58" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9">
+      <c r="B38" s="97"/>
+      <c r="C38" s="84"/>
+      <c r="D38" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="E37" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="F37" s="39"/>
-      <c r="G37" s="47" t="s">
-        <v>153</v>
-      </c>
-      <c r="I37" s="60" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9">
-      <c r="B38" s="102"/>
-      <c r="C38" s="89"/>
-      <c r="D38" s="13" t="s">
+      <c r="E38" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="F38" s="37"/>
+      <c r="G38" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="I38" s="58" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9">
+      <c r="B39" s="97"/>
+      <c r="C39" s="84"/>
+      <c r="D39" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="F38" s="39"/>
-      <c r="G38" s="47" t="s">
-        <v>126</v>
-      </c>
-      <c r="I38" s="60" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9">
-      <c r="B39" s="102"/>
-      <c r="C39" s="89"/>
-      <c r="D39" s="13" t="s">
+      <c r="E39" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="F39" s="39"/>
-      <c r="G39" s="47" t="s">
-        <v>128</v>
-      </c>
-      <c r="I39" s="60" t="s">
-        <v>128</v>
+      <c r="F39" s="37"/>
+      <c r="G39" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="I39" s="58" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="19">
-      <c r="B40" s="102"/>
+      <c r="B40" s="97"/>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
-      <c r="F40" s="40" t="s">
-        <v>183</v>
-      </c>
-      <c r="G40" s="51" t="s">
-        <v>182</v>
-      </c>
-      <c r="I40" s="60" t="s">
+      <c r="F40" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="G40" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="I40" s="58" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" ht="19" thickBot="1">
+      <c r="B41" s="98"/>
+      <c r="C41" s="46" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="41" spans="2:9" ht="19" thickBot="1">
-      <c r="B41" s="103"/>
-      <c r="C41" s="48" t="s">
+      <c r="D41" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="E41" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="D41" s="48" t="s">
+      <c r="F41" s="47"/>
+      <c r="G41" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="E41" s="48" t="s">
+      <c r="I41" s="59" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9">
+      <c r="B42" s="96" t="s">
         <v>130</v>
       </c>
-      <c r="F41" s="49"/>
-      <c r="G41" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="I41" s="61" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9">
-      <c r="B42" s="101" t="s">
+      <c r="C42" s="83" t="s">
         <v>131</v>
       </c>
-      <c r="C42" s="88" t="s">
+      <c r="D42" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="D42" s="44" t="s">
+      <c r="E42" s="42" t="s">
         <v>133</v>
       </c>
-      <c r="E42" s="44" t="s">
+      <c r="F42" s="43"/>
+      <c r="G42" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="I42" s="57" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9">
+      <c r="B43" s="97"/>
+      <c r="C43" s="84"/>
+      <c r="D43" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="E43" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="F42" s="45"/>
-      <c r="G42" s="46" t="s">
+      <c r="F43" s="37"/>
+      <c r="G43" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="I42" s="59" t="s">
+      <c r="I43" s="58" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="43" spans="2:9">
-      <c r="B43" s="102"/>
-      <c r="C43" s="89"/>
-      <c r="D43" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="E43" s="13" t="s">
+    <row r="44" spans="2:9">
+      <c r="B44" s="97"/>
+      <c r="C44" s="84"/>
+      <c r="D44" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="F43" s="39"/>
-      <c r="G43" s="47" t="s">
-        <v>135</v>
-      </c>
-      <c r="I43" s="60" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9">
-      <c r="B44" s="102"/>
-      <c r="C44" s="89"/>
-      <c r="D44" s="13" t="s">
+      <c r="E44" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E44" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F44" s="39"/>
-      <c r="G44" s="47" t="s">
-        <v>137</v>
-      </c>
-      <c r="I44" s="93" t="s">
-        <v>137</v>
+      <c r="F44" s="37"/>
+      <c r="G44" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="I44" s="88" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="19">
-      <c r="B45" s="102"/>
-      <c r="C45" s="89"/>
+      <c r="B45" s="97"/>
+      <c r="C45" s="84"/>
       <c r="D45" s="13"/>
       <c r="E45" s="13"/>
-      <c r="F45" s="40" t="s">
+      <c r="F45" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="G45" s="49" t="s">
         <v>184</v>
       </c>
-      <c r="G45" s="51" t="s">
-        <v>186</v>
-      </c>
-      <c r="I45" s="94"/>
+      <c r="I45" s="89"/>
     </row>
     <row r="46" spans="2:9" ht="19">
-      <c r="B46" s="102"/>
-      <c r="C46" s="89"/>
+      <c r="B46" s="97"/>
+      <c r="C46" s="84"/>
       <c r="D46" s="13"/>
       <c r="E46" s="13"/>
-      <c r="F46" s="40" t="s">
+      <c r="F46" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="G46" s="49" t="s">
         <v>185</v>
       </c>
-      <c r="G46" s="51" t="s">
-        <v>187</v>
-      </c>
-      <c r="I46" s="95"/>
+      <c r="I46" s="90"/>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="102"/>
-      <c r="C47" s="89"/>
+      <c r="B47" s="97"/>
+      <c r="C47" s="84"/>
       <c r="D47" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="E47" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="E47" s="13" t="s">
+      <c r="F47" s="37"/>
+      <c r="G47" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="I47" s="58" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9">
+      <c r="B48" s="97"/>
+      <c r="C48" s="84"/>
+      <c r="D48" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="E48" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="F47" s="39"/>
-      <c r="G47" s="47" t="s">
+      <c r="F48" s="37"/>
+      <c r="G48" s="45" t="s">
         <v>139</v>
       </c>
-      <c r="I47" s="60" t="s">
+      <c r="I48" s="58" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="48" spans="2:9">
-      <c r="B48" s="102"/>
-      <c r="C48" s="89"/>
-      <c r="D48" s="35" t="s">
+    <row r="49" spans="2:9">
+      <c r="B49" s="97"/>
+      <c r="C49" s="84"/>
+      <c r="D49" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="E48" s="13" t="s">
+      <c r="E49" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="F48" s="39"/>
-      <c r="G48" s="47" t="s">
+      <c r="F49" s="37"/>
+      <c r="G49" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="I48" s="60" t="s">
+      <c r="I49" s="58" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="49" spans="2:9">
-      <c r="B49" s="102"/>
-      <c r="C49" s="89"/>
-      <c r="D49" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="E49" s="13" t="s">
+    <row r="50" spans="2:9">
+      <c r="B50" s="97"/>
+      <c r="C50" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="F49" s="39"/>
-      <c r="G49" s="47" t="s">
+      <c r="D50" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="I49" s="60" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="50" spans="2:9">
-      <c r="B50" s="102"/>
-      <c r="C50" s="13" t="s">
+      <c r="E50" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="F50" s="37"/>
+      <c r="G50" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="E50" s="13" t="s">
+      <c r="I50" s="58" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9">
+      <c r="B51" s="97"/>
+      <c r="C51" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="F50" s="39"/>
-      <c r="G50" s="47" t="s">
+      <c r="D51" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="I50" s="60" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9">
-      <c r="B51" s="102"/>
-      <c r="C51" s="13" t="s">
+      <c r="E51" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="F51" s="37"/>
+      <c r="G51" s="45" t="s">
         <v>144</v>
       </c>
-      <c r="E51" s="13" t="s">
+      <c r="I51" s="58" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" ht="19" thickBot="1">
+      <c r="B52" s="97"/>
+      <c r="C52" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="F51" s="39"/>
-      <c r="G51" s="47" t="s">
+      <c r="D52" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="I51" s="60" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9" ht="19" thickBot="1">
-      <c r="B52" s="102"/>
-      <c r="C52" s="13" t="s">
+      <c r="E52" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="F52" s="37"/>
+      <c r="G52" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="E52" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="F52" s="39"/>
-      <c r="G52" s="47" t="s">
-        <v>147</v>
-      </c>
-      <c r="I52" s="63" t="s">
-        <v>147</v>
+      <c r="I52" s="61" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="2:9" ht="57">
-      <c r="B53" s="102"/>
+      <c r="B53" s="97"/>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
       <c r="E53" s="13"/>
-      <c r="F53" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="G53" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="I53" s="96" t="s">
-        <v>141</v>
+      <c r="F53" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="G53" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="I53" s="91" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="2:9" ht="19">
-      <c r="B54" s="102"/>
+      <c r="B54" s="97"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
       <c r="E54" s="13"/>
-      <c r="F54" s="40" t="s">
-        <v>201</v>
-      </c>
-      <c r="G54" s="51" t="s">
-        <v>192</v>
-      </c>
-      <c r="I54" s="94"/>
+      <c r="F54" s="38" t="s">
+        <v>199</v>
+      </c>
+      <c r="G54" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="I54" s="89"/>
     </row>
     <row r="55" spans="2:9" ht="19">
-      <c r="B55" s="102"/>
+      <c r="B55" s="97"/>
       <c r="C55" s="13"/>
       <c r="D55" s="13"/>
       <c r="E55" s="13"/>
-      <c r="F55" s="40" t="s">
-        <v>202</v>
-      </c>
-      <c r="G55" s="51" t="s">
-        <v>193</v>
-      </c>
-      <c r="I55" s="94"/>
+      <c r="F55" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="G55" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="I55" s="89"/>
     </row>
     <row r="56" spans="2:9" ht="19">
-      <c r="B56" s="102"/>
+      <c r="B56" s="97"/>
       <c r="C56" s="13"/>
       <c r="D56" s="13"/>
       <c r="E56" s="13"/>
-      <c r="F56" s="40" t="s">
-        <v>203</v>
-      </c>
-      <c r="G56" s="51" t="s">
-        <v>194</v>
-      </c>
-      <c r="I56" s="94"/>
+      <c r="F56" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="G56" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="I56" s="89"/>
     </row>
     <row r="57" spans="2:9" ht="19">
-      <c r="B57" s="102"/>
+      <c r="B57" s="97"/>
       <c r="C57" s="13"/>
       <c r="D57" s="13"/>
       <c r="E57" s="13"/>
-      <c r="F57" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="G57" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="I57" s="94"/>
+      <c r="F57" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="G57" s="49" t="s">
+        <v>193</v>
+      </c>
+      <c r="I57" s="89"/>
     </row>
     <row r="58" spans="2:9" ht="38">
-      <c r="B58" s="102"/>
+      <c r="B58" s="97"/>
       <c r="C58" s="13"/>
       <c r="D58" s="13"/>
       <c r="E58" s="13"/>
-      <c r="F58" s="40" t="s">
-        <v>205</v>
-      </c>
-      <c r="G58" s="51" t="s">
-        <v>196</v>
-      </c>
-      <c r="I58" s="94"/>
+      <c r="F58" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="G58" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="I58" s="89"/>
     </row>
     <row r="59" spans="2:9" ht="20" thickBot="1">
-      <c r="B59" s="102"/>
+      <c r="B59" s="97"/>
       <c r="C59" s="13"/>
       <c r="D59" s="13"/>
       <c r="E59" s="13"/>
-      <c r="F59" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="G59" s="51" t="s">
-        <v>197</v>
-      </c>
-      <c r="I59" s="97"/>
+      <c r="F59" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="G59" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="I59" s="92"/>
     </row>
     <row r="60" spans="2:9" ht="19">
-      <c r="B60" s="102"/>
+      <c r="B60" s="97"/>
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
       <c r="E60" s="13"/>
-      <c r="F60" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="G60" s="51" t="s">
-        <v>198</v>
-      </c>
-      <c r="I60" s="96" t="s">
-        <v>216</v>
+      <c r="F60" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="G60" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="I60" s="91" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="61" spans="2:9" ht="20" thickBot="1">
-      <c r="B61" s="102"/>
+      <c r="B61" s="97"/>
       <c r="C61" s="13"/>
       <c r="D61" s="13"/>
       <c r="E61" s="13"/>
-      <c r="F61" s="40" t="s">
-        <v>208</v>
-      </c>
-      <c r="G61" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="I61" s="94"/>
+      <c r="F61" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="G61" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="I61" s="89"/>
     </row>
     <row r="62" spans="2:9" ht="20" thickBot="1">
-      <c r="B62" s="102"/>
+      <c r="B62" s="97"/>
       <c r="C62" s="13"/>
       <c r="D62" s="13"/>
       <c r="E62" s="13"/>
-      <c r="F62" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="G62" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="I62" s="62" t="s">
-        <v>57</v>
+      <c r="F62" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="G62" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="I62" s="60" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="2:9" ht="19" customHeight="1">
-      <c r="B63" s="102"/>
-      <c r="C63" s="89" t="s">
+      <c r="B63" s="97"/>
+      <c r="C63" s="84" t="s">
+        <v>147</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="E63" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="D63" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="E63" s="13" t="s">
+      <c r="F63" s="77" t="s">
+        <v>189</v>
+      </c>
+      <c r="G63" s="80" t="s">
+        <v>188</v>
+      </c>
+      <c r="I63" s="91" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" ht="19" customHeight="1">
+      <c r="B64" s="97"/>
+      <c r="C64" s="84"/>
+      <c r="D64" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="F63" s="82" t="s">
-        <v>191</v>
-      </c>
-      <c r="G63" s="85" t="s">
-        <v>190</v>
-      </c>
-      <c r="I63" s="96" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9" ht="19" customHeight="1">
-      <c r="B64" s="102"/>
-      <c r="C64" s="89"/>
-      <c r="D64" s="13" t="s">
+      <c r="E64" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="E64" s="13" t="s">
+      <c r="F64" s="78"/>
+      <c r="G64" s="81"/>
+      <c r="I64" s="89"/>
+    </row>
+    <row r="65" spans="2:9" ht="19" customHeight="1" thickBot="1">
+      <c r="B65" s="98"/>
+      <c r="C65" s="95"/>
+      <c r="D65" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="E65" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="F64" s="83"/>
-      <c r="G64" s="86"/>
-      <c r="I64" s="94"/>
-    </row>
-    <row r="65" spans="2:9" ht="19" customHeight="1" thickBot="1">
-      <c r="B65" s="103"/>
-      <c r="C65" s="100"/>
-      <c r="D65" s="48" t="s">
-        <v>157</v>
-      </c>
-      <c r="E65" s="48" t="s">
-        <v>152</v>
-      </c>
-      <c r="F65" s="84"/>
-      <c r="G65" s="87"/>
-      <c r="I65" s="97"/>
+      <c r="F65" s="79"/>
+      <c r="G65" s="82"/>
+      <c r="I65" s="92"/>
     </row>
     <row r="67" spans="2:9">
       <c r="E67" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
